--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -41,20 +41,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -765,11 +765,11 @@
       <c r="C4" s="3" t="n">
         <v>437.3</v>
       </c>
-      <c r="D4" s="10" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>17.2</v>
+      <c r="D4" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>1.3</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>24.2</v>
@@ -778,10 +778,10 @@
         <v>14</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>22.4</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>4.2</v>
@@ -793,32 +793,32 @@
       <c r="M4" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="N4" s="8" t="n">
+      <c r="N4" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>87</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>30</v>
+        <v>2.6</v>
+      </c>
+      <c r="Q4" s="8" t="n">
+        <v>22.6</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>27</v>
+        <v>27.8</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>63.7</v>
       </c>
-      <c r="U4" s="8" t="n">
+      <c r="U4" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>21.1</v>
+        <v>22.2</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24</v>
@@ -827,7 +827,7 @@
         <v>27.5</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>9.699999999999999</v>
@@ -846,19 +846,19 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="D5" s="10" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>18.7</v>
+        <v>18.2</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>5.7</v>
+        <v>57.2</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>16.3</v>
@@ -876,19 +876,19 @@
         <v>19.1</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>18</v>
+        <v>0.6</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>90</v>
+        <v>96.2</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>2.3</v>
+        <v>24.3</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>20.5</v>
+        <v>22.5</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>19.1</v>
@@ -897,13 +897,13 @@
         <v>21.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>87.8</v>
+        <v>82.8</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>60.6</v>
+        <v>61.6</v>
       </c>
       <c r="W5" s="3" t="n">
         <v>18.9</v>
@@ -912,7 +912,7 @@
         <v>20.7</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>3.6</v>
@@ -931,9 +931,9 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>438.6</v>
-      </c>
-      <c r="D6" s="10" t="n">
+        <v>431.6</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>31.4</v>
       </c>
       <c r="E6" s="3" t="n">
@@ -943,23 +943,25 @@
         <v>25.6</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>17.8</v>
+        <v>12.8</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J6" s="3" t="n"/>
+      <c r="J6" s="3" t="n">
+        <v>3.6</v>
+      </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>60.6</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="M6" s="8" t="n">
-        <v>19</v>
+      <c r="M6" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>21.1</v>
@@ -968,7 +970,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>29.8</v>
@@ -982,7 +984,7 @@
       <c r="T6" s="3" t="n">
         <v>61.9</v>
       </c>
-      <c r="U6" s="8" t="n">
+      <c r="U6" s="3" t="n">
         <v>16</v>
       </c>
       <c r="V6" s="3" t="n">
@@ -995,10 +997,10 @@
         <v>26.5</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>11.9</v>
+        <v>11.1</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1016,20 +1018,20 @@
       <c r="C7" s="3" t="n">
         <v>437.3</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="E7" s="11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>85</v>
+      <c r="E7" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>25</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="8" t="n">
-        <v>14.8</v>
+      <c r="H7" s="3" t="n">
+        <v>4.2</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>3.4</v>
@@ -1038,25 +1040,25 @@
         <v>4.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L7" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="N7" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="N7" s="8" t="n">
-        <v>17.3</v>
-      </c>
       <c r="O7" s="3" t="n">
-        <v>872.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q7" s="3" t="n">
-        <v>31.9</v>
+      <c r="Q7" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>23.9</v>
@@ -1065,25 +1067,25 @@
         <v>24.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>52.1</v>
+        <v>5.1</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>27.6</v>
+        <v>6.6</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>4.1</v>
+        <v>24.1</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>27.8</v>
+        <v>2.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>75.2</v>
+        <v>5.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1099,46 +1101,46 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>297.2</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>19.8</v>
+        <v>0.4</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>0.4</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>26.2</v>
+        <v>86.2</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>17.2</v>
+        <v>12.2</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.1</v>
+        <v>4.4</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>18.5</v>
+        <v>24.5</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M8" s="3" t="n">
-        <v>18.6</v>
+      <c r="M8" s="8" t="n">
+        <v>865.6</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>87.2</v>
+        <v>82.7</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>21.8</v>
+        <v>2.8</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>26.6</v>
@@ -1153,22 +1155,22 @@
         <v>95.40000000000001</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>24</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>212.4</v>
+        <v>22.8</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>90.2</v>
+        <v>96.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>2.9</v>
+        <v>8.9</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1184,25 +1186,23 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>6663.1</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>192.5</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>22.5</v>
-      </c>
+        <v>6.6</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="F9" s="11" t="n"/>
       <c r="G9" s="3" t="n">
-        <v>60.1</v>
+        <v>611.1</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>80.5</v>
+        <v>86.5</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>11.2</v>
+        <v>4.4</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>15.5</v>
@@ -1214,7 +1214,7 @@
         <v>94.3</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>87.8</v>
+        <v>82.8</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>96.3</v>
@@ -1223,7 +1223,7 @@
         <v>440.9</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>4.4</v>
+        <v>12.9</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>138.8</v>
@@ -1232,7 +1232,7 @@
         <v>11.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>344.1</v>
+        <v>31.9</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>360.9</v>
@@ -1244,13 +1244,13 @@
         <v>126.1</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>29.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>2.8</v>
@@ -1269,38 +1269,40 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>333.3</v>
+        <v>333.2</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>30.5</v>
       </c>
-      <c r="E10" s="9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="F10" s="9" t="n">
+      <c r="E10" s="10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F10" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>16.1</v>
+        <v>1.6</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K10" s="3" t="n"/>
+        <v>3.4</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>44.7</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M10" s="8" t="n">
-        <v>17.6</v>
+      <c r="M10" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>19.3</v>
+        <v>1.3</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>88.2</v>
@@ -1309,31 +1311,31 @@
         <v>2.6</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>27.8</v>
+        <v>82.2</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>26.4</v>
+        <v>2.6</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v>11.7</v>
+        <v>2.2</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>0.4</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>25.2</v>
+        <v>25.8</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>22.6</v>
+        <v>2.6</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>80.5</v>
+        <v>806.5</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>6.6</v>
@@ -1352,19 +1354,19 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>445</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F11" s="10" t="n">
+        <v>445.6</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="F11" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>18.2</v>
@@ -1373,7 +1375,7 @@
         <v>2</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>31.3</v>
+        <v>3.3</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0</v>
@@ -1384,7 +1386,9 @@
       <c r="M11" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="N11" s="3" t="n"/>
+      <c r="N11" s="3" t="n">
+        <v>10.7</v>
+      </c>
       <c r="O11" s="3" t="n">
         <v>87.90000000000001</v>
       </c>
@@ -1394,14 +1398,14 @@
       <c r="Q11" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="R11" s="8" t="n">
+      <c r="R11" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>31.9</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>5.7</v>
@@ -1412,11 +1416,11 @@
       <c r="W11" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="X11" s="8" t="n">
+      <c r="X11" s="3" t="n">
         <v>30.9</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>97.5</v>
+        <v>9.5</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>0.8</v>
@@ -1437,17 +1441,17 @@
       <c r="C12" s="3" t="n">
         <v>383.6</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F12" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>8.5</v>
+        <v>84.5</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>18</v>
@@ -1468,18 +1472,18 @@
         <v>19.3</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>61.1</v>
+        <v>21.5</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>88.40000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="R12" s="8" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="Q12" s="8" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="R12" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="S12" s="3" t="n">
@@ -1489,13 +1493,13 @@
         <v>85.40000000000001</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>5.3</v>
+        <v>53.3</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>24.7</v>
+        <v>4.4</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>24.4</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>30.4</v>
@@ -1504,7 +1508,7 @@
         <v>97.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1520,22 +1524,22 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>256.7</v>
-      </c>
-      <c r="D13" s="10" t="n">
+        <v>356.1</v>
+      </c>
+      <c r="D13" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E13" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="F13" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>17.6</v>
+        <v>12.6</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.5</v>
@@ -1544,7 +1548,7 @@
         <v>2.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>20</v>
@@ -1553,22 +1557,22 @@
         <v>18.8</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>21.5</v>
+        <v>20.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" s="8" t="n">
         <v>28.6</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="S13" s="3" t="n">
-        <v>32.7</v>
+      <c r="S13" s="8" t="n">
+        <v>24.7</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>83.59999999999999</v>
@@ -1576,17 +1580,17 @@
       <c r="U13" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="V13" s="8" t="n">
+      <c r="V13" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>93.8</v>
+        <v>43.2</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>44.4</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>2.2</v>
@@ -1605,22 +1609,22 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>374</v>
-      </c>
-      <c r="D14" s="10" t="n">
+        <v>340.8</v>
+      </c>
+      <c r="D14" s="3" t="n">
         <v>32.5</v>
       </c>
-      <c r="E14" s="10" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="F14" s="10" t="n">
+      <c r="E14" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F14" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="G14" s="3" t="n">
-        <v>12.9</v>
+      <c r="G14" s="8" t="n">
+        <v>22.9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>17.2</v>
+        <v>12.2</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>2.8</v>
@@ -1629,16 +1633,16 @@
         <v>3.3</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>19.8</v>
+        <v>57.2</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>29.8</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>18.7</v>
+        <v>18.2</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>20.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>89.90000000000001</v>
@@ -1650,10 +1654,10 @@
         <v>30.6</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>22.6</v>
+        <v>2.6</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>22.3</v>
+        <v>2.3</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>50.9</v>
@@ -1671,7 +1675,7 @@
         <v>24.5</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>93.40000000000001</v>
+        <v>93</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>1.8</v>
@@ -1692,14 +1696,14 @@
       <c r="C15" s="3" t="n">
         <v>433.5</v>
       </c>
-      <c r="D15" s="10" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F15" s="10" t="n">
-        <v>24.9</v>
+      <c r="D15" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>44.1</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>9.300000000000001</v>
@@ -1714,16 +1718,16 @@
         <v>3.4</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>20.4</v>
+        <v>26.4</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="N15" s="8" t="n">
-        <v>20.8</v>
+        <v>0.9</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>11.3</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>88.8</v>
@@ -1747,19 +1751,19 @@
         <v>14.1</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>24.5</v>
+        <v>4.5</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>74</v>
+        <v>11.5</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0.7</v>
+        <v>7.2</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1775,13 +1779,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1992.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>149.9</v>
+        <v>7.8</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>99.09999999999999</v>
+        <v>929.1</v>
       </c>
       <c r="F16" s="10" t="n">
         <v>124.7</v>
@@ -1802,47 +1806,49 @@
         <v>6</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>100.9</v>
+        <v>160.9</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>918.6</v>
-      </c>
-      <c r="N16" s="3" t="n"/>
+        <v>94.59999999999999</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>21122.2</v>
+      </c>
       <c r="O16" s="3" t="n">
-        <v>0.4</v>
+        <v>11.1</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>12.9</v>
+        <v>8.9</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>142.8</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>83</v>
+        <v>23.7</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>445.1</v>
+        <v>42.5</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>368.7</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>53.1</v>
+        <v>533.4</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>120.8</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>451.1</v>
+        <v>46.4</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>315.1</v>
+        <v>7.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>455.1</v>
+        <v>45.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1857,8 +1863,12 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>399.2</v>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+3986
+</t>
+        </is>
       </c>
       <c r="D17" s="10" t="n">
         <v>30</v>
@@ -1867,19 +1877,19 @@
         <v>19.8</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>24.9</v>
+        <v>14.4</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>10.2</v>
+        <v>0.1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>18.1</v>
+        <v>12.4</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="n">
@@ -1889,7 +1899,7 @@
         <v>18.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>88.8</v>
@@ -1901,30 +1911,32 @@
         <v>28.6</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>24.6</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>28.5</v>
+        <v>22.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>73.7</v>
+        <v>3.7</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V17" s="3" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v>42.8</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>43.2</v>
+        <v>23</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="Z17" s="3" t="n"/>
+        <v>1.9</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>2.7</v>
+      </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1939,58 +1951,58 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>137.3</v>
+        <v>43.2</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>30.8</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>24.9</v>
+        <v>12</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>64.40000000000001</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>81.8</v>
+        <v>11.2</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>17.7</v>
+        <v>12.7</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>21.9</v>
+        <v>82</v>
+      </c>
+      <c r="P18" s="8" t="n">
+        <v>42.9</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>0.2</v>
+        <v>23.1</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>6.1</v>
+        <v>63.1</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>4.4</v>
@@ -2005,10 +2017,14 @@
         <v>31</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="Z18" s="3" t="n">
-        <v>2.6</v>
+        <v>24.1</v>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+8 179
+</t>
+        </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2036,9 +2052,9 @@
         <v>25.5</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H19" s="8" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="I19" s="3" t="n">
@@ -2048,16 +2064,16 @@
         <v>3.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>21.5</v>
+        <v>0.8</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>87.5</v>
@@ -2069,7 +2085,7 @@
         <v>31.8</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>94.2</v>
+        <v>24.2</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>25.3</v>
@@ -2081,19 +2097,27 @@
         <v>21.7</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>25.8</v>
+        <v>85.8</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>23.3</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y19" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Z19" s="3" t="n">
-        <v>6.2</v>
+        <v>2</v>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+44
+</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+818
+</t>
+        </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2109,34 +2133,39 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>256.8</v>
-      </c>
-      <c r="D20" s="11" t="n">
-        <v>41.3</v>
+        <v>3561.5</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>19.2</v>
+        <v>19.8</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>13.5</v>
+        <v>23.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+1 8 4
+7
+</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>82.8</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>18.8</v>
@@ -2145,13 +2174,13 @@
         <v>20.9</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>89</v>
+        <v>21.1</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>25.5</v>
+        <v>6.5</v>
+      </c>
+      <c r="Q20" s="8" t="n">
+        <v>535.2</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>21.5</v>
@@ -2160,7 +2189,7 @@
         <v>23.1</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>70.7</v>
+        <v>20.8</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>9.5</v>
@@ -2172,10 +2201,10 @@
         <v>20.5</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>67.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="Z20" s="3" t="n"/>
       <c r="AA20" s="3" t="inlineStr">
@@ -2195,7 +2224,7 @@
         <v>433.5</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>30.8</v>
+        <v>30.2</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>18.4</v>
@@ -2203,11 +2232,9 @@
       <c r="F21" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="G21" s="3" t="n"/>
       <c r="H21" s="3" t="n">
-        <v>17.4</v>
+        <v>12.4</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>2.2</v>
@@ -2216,13 +2243,13 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>11.3</v>
+        <v>18.3</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>18.8</v>
@@ -2237,28 +2264,32 @@
         <v>30.1</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>21.7</v>
+        <v>41.7</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>51</v>
+        <v>531</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>24.3</v>
+        <v>44.3</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X21" s="3" t="n">
-        <v>955.9</v>
+        <v>2.4</v>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+8111
+</t>
+        </is>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>250.4</v>
+        <v>850.1</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>4.5</v>
@@ -2277,22 +2308,22 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>374</v>
+        <v>34</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>34.8</v>
+        <v>31.2</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>24.5</v>
+        <v>12.2</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>84.5</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>15.3</v>
+        <v>0.2</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>2.1</v>
@@ -2304,16 +2335,16 @@
         <v>3.7</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>17.6</v>
+        <v>12.5</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>87.5</v>
+        <v>1.5</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>87</v>
+        <v>872</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>2.6</v>
@@ -2328,22 +2359,22 @@
         <v>24.2</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>56.4</v>
+        <v>568.1</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>21.2</v>
+        <v>21.8</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>21.6</v>
+        <v>4.6</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>85.5</v>
+        <v>5.5</v>
       </c>
       <c r="Z22" s="3" t="n">
         <v>3.6</v>
@@ -2362,76 +2393,76 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>374</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>24.5</v>
+        <v>1985.5</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>653.4</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>123</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>14.6</v>
+        <v>60.3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>15.3</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.1</v>
+        <v>11.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>3.5</v>
+        <v>15.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>3.7</v>
+        <v>49.2</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>17.6</v>
+        <v>95.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>16.2</v>
+        <v>882.6</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>96.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>87</v>
+        <v>438.2</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>146.9</v>
+        <v>146.2</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>215.4</v>
+        <v>2952.6</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>64.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>462.1</v>
+        <v>12.8</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>103.6</v>
+        <v>10.7</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>28.7</v>
+        <v>26.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>411</v>
+        <v>0.4</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>7.1</v>
+        <v>2.1</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2447,76 +2478,74 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1925.5</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>23</v>
+        <v>5851.1</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>24.6</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>60.3</v>
+        <v>3.2</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>85</v>
+        <v>12.6</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>11.6</v>
+        <v>2.3</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>49.2</v>
-      </c>
+        <v>3.1</v>
+      </c>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="n">
-        <v>95.2</v>
+        <v>19</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>88.2</v>
+        <v>12.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>96.5</v>
+        <v>1.3</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>437.2</v>
+        <v>872.4</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q24" s="8" t="n">
-        <v>46.9</v>
+        <v>2.7</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>29.2</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>14.3</v>
+        <v>22.9</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>19</v>
+        <v>23.8</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>215.4</v>
+        <v>59</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>64.59999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>462.1</v>
+        <v>4.4</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>103.6</v>
+        <v>22.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>28.7</v>
+        <v>0.9</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>411</v>
+        <v>0.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>7.1</v>
+        <v>0.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2532,76 +2561,76 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>385.1</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>81.61</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>24.6</v>
+        <v>34</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>45.1</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>12</v>
+        <v>0.1</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>87</v>
+        <v>18.8</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>19.3</v>
+        <v>0.1</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>60.4</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>21.7</v>
+        <v>0.5</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>29.2</v>
+        <v>324.3</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>22.9</v>
+        <v>24.3</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>23.8</v>
+        <v>1.8</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>59</v>
+        <v>56.9</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>17</v>
+        <v>19.7</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>24.4</v>
+        <v>7.1</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>22.1</v>
+        <v>20.9</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>85.3</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2617,49 +2646,49 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>374</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>34.1</v>
+        <v>34</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>26.1</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>13.1</v>
+        <v>13.3</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>45.1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>12.8</v>
+        <v>0.4</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>31.6</v>
+        <v>36.3</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0.4</v>
+        <v>7.5</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>20.4</v>
+        <v>18.1</v>
+      </c>
+      <c r="N26" s="8" t="n">
+        <v>60.4</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>31.3</v>
+        <v>324.3</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>24.3</v>
@@ -2674,19 +2703,19 @@
         <v>19.7</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>0.4</v>
+        <v>24.2</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>22.6</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>74.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2702,7 +2731,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>329.8</v>
+        <v>381.2</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>30.8</v>
@@ -2711,19 +2740,19 @@
         <v>18.6</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>24.7</v>
+        <v>24.2</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>12.2</v>
+        <v>12.8</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>31.6</v>
+        <v>2.6</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>0.3</v>
@@ -2732,18 +2761,18 @@
         <v>19</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>18.4</v>
+        <v>12.6</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>87</v>
+        <v>87.2</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="Q27" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q27" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="R27" s="3" t="n">
@@ -2753,16 +2782,16 @@
         <v>24.5</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="V27" s="3" t="n">
-        <v>24.2</v>
+        <v>6.1</v>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v>42.6</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>21.8</v>
+        <v>41.8</v>
       </c>
       <c r="X27" s="3" t="n">
         <v>24.6</v>
@@ -2770,8 +2799,12 @@
       <c r="Y27" s="3" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="Z27" s="3" t="n">
-        <v>7.6</v>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+54
+</t>
+        </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2787,10 +2820,10 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>354.5</v>
-      </c>
-      <c r="D28" s="11" t="n">
-        <v>0.2</v>
+        <v>354.2</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>28.4</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>19.4</v>
@@ -2799,34 +2832,34 @@
         <v>23.8</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>17.8</v>
+        <v>12.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>5.3</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>20.2</v>
+        <v>10.2</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>17.6</v>
+        <v>18.8</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>20.8</v>
+        <v>61.2</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>187.5</v>
+        <v>82.5</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>26</v>
@@ -2835,7 +2868,7 @@
         <v>21.6</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>23</v>
+        <v>23.8</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>68.40000000000001</v>
@@ -2844,19 +2877,19 @@
         <v>10.6</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>23.2</v>
+        <v>63.5</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>20.8</v>
+        <v>6.2</v>
       </c>
       <c r="X28" s="3" t="n">
         <v>23</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>808.1</v>
+        <v>8.1</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2874,11 +2907,11 @@
       <c r="C29" s="3" t="n">
         <v>389.3</v>
       </c>
-      <c r="D29" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>20.2</v>
+      <c r="D29" s="9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>25</v>
@@ -2887,31 +2920,31 @@
         <v>9.6</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>19.6</v>
+        <v>3.8</v>
+      </c>
+      <c r="K29" s="8" t="n">
+        <v>239.6</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>18.8</v>
+        <v>19.2</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>21.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>28.2</v>
@@ -2926,22 +2959,22 @@
         <v>64.90000000000001</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>13.4</v>
+        <v>1.4</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>26</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="X29" s="3" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="X29" s="8" t="n">
         <v>27.6</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2957,37 +2990,37 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>408.5</v>
-      </c>
-      <c r="D30" s="9" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F30" s="9" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>494.5</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="F30" s="10" t="n">
         <v>24.9</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>9.1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>20.1</v>
+        <v>4.1</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.2</v>
+        <v>20.2</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>21.5</v>
@@ -2996,7 +3029,7 @@
         <v>90</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>12.9</v>
+        <v>2.3</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>28.6</v>
@@ -3011,10 +3044,10 @@
         <v>62.6</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>114.6</v>
+        <v>14.6</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>15.5</v>
+        <v>85.5</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>23</v>
@@ -3023,10 +3056,10 @@
         <v>26.5</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>6.1</v>
+        <v>2.6</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3042,61 +3075,61 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="D31" s="9" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="E31" s="9" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E31" s="10" t="n">
         <v>97.8</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="10" t="n">
         <v>24.1</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>52.5</v>
+        <v>5.5</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>11.7</v>
+        <v>10</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>2.9</v>
+        <v>15.8</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>954.4</v>
+        <v>25.4</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="N31" s="8" t="n">
-        <v>3.2</v>
+        <v>93.2</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>113.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>441.9</v>
+        <v>44.4</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>2.3</v>
+        <v>13.1</v>
       </c>
       <c r="Q31" s="8" t="n">
-        <v>138.5</v>
+        <v>38.5</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>43.8</v>
+        <v>3.7</v>
       </c>
       <c r="S31" s="8" t="n">
-        <v>22.7</v>
+        <v>18.7</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>332.8</v>
+        <v>334.8</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>64.3</v>
+        <v>0.5</v>
       </c>
       <c r="V31" s="8" t="n">
         <v>23.1</v>
@@ -3108,10 +3141,10 @@
         <v>24.3</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>399.8</v>
+        <v>322.8</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>2.6</v>
+        <v>0.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3127,46 +3160,48 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>371.3</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>19.6</v>
+        <v>437.3</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>2.6</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>10.5</v>
+        <v>1.5</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>10.1</v>
+        <v>2</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="K32" s="3" t="n"/>
+        <v>3.2</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>4.7</v>
+      </c>
       <c r="L32" s="3" t="n">
-        <v>19.9</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>92.2</v>
+        <v>18.5</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>206.1</v>
+        <v>26.6</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>88.40000000000001</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="Q32" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q32" s="3" t="n">
         <v>27.7</v>
       </c>
       <c r="R32" s="3" t="n">
@@ -3176,25 +3211,29 @@
         <v>24.5</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>66.59999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>122.1</v>
+        <v>12.9</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>24.6</v>
+        <v>4.6</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>22</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>24.9</v>
+        <v>42.9</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v>6.5</v>
+        <v>22.8</v>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+78
+</t>
+        </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3210,52 +3249,52 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>437.3</v>
+        <v>3272</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>32.8</v>
+        <v>34.8</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="F33" s="11" t="n">
-        <v>26.51</v>
+      <c r="F33" s="3" t="n">
+        <v>26.5</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>6.6</v>
+        <v>12.6</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>20.6</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>18.6</v>
+        <v>19.3</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>21.5</v>
+        <v>61.5</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>28.4</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>31</v>
+        <v>0.1</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>25.4</v>
@@ -3267,19 +3306,19 @@
         <v>19.5</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>28.2</v>
+        <v>25.8</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>23.7</v>
+        <v>2.8</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>26.4</v>
+        <v>5.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3295,28 +3334,28 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>397</v>
-      </c>
-      <c r="D34" s="11" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="D34" s="9" t="n">
         <v>0.3</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>26.7</v>
+        <v>26.2</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>17.9</v>
+        <v>12.2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>13.5</v>
+        <v>4.4</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0</v>
@@ -3325,46 +3364,50 @@
         <v>20.9</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>21.7</v>
+        <v>21.2</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>32.9</v>
+        <v>26.1</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>23.9</v>
+        <v>2.2</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>23.9</v>
+        <v>26.6</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>47.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>26.1</v>
+        <v>2.2</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>25.8</v>
+        <v>45.5</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>61.2</v>
+        <v>23.3</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>25.8</v>
+        <v>27.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="Z34" s="3" t="n">
-        <v>7.4</v>
+        <v>83.2</v>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
+5
+</t>
+        </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3380,76 +3423,74 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>362.4</v>
+        <v>884.5</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>30.4</v>
+        <v>24.6</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>20.2</v>
+        <v>20.7</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>25.3</v>
+        <v>22.7</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>10.2</v>
+        <v>3.4</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="I35" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="J35" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K35" s="3" t="n">
-        <v>0</v>
+      <c r="K35" s="8" t="n">
+        <v>98</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>20.4</v>
+        <v>24.1</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>21</v>
+        <v>61.3</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>87.3</v>
+        <v>25.4</v>
       </c>
       <c r="P35" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="S35" s="3" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="U35" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q35" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="R35" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="S35" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="T35" s="3" t="n">
-        <v>78.59999999999999</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>25.5</v>
+      <c r="V35" s="8" t="n">
+        <v>21.6</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>23.3</v>
+        <v>20.3</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>27.2</v>
+        <v>2.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>83.2</v>
+        <v>3.3</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>5.4</v>
+        <v>0.6</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3465,76 +3506,74 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>398.9</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>24.6</v>
+        <v>28.6</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>20.7</v>
+        <v>21</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>22.7</v>
+        <v>24.3</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>3.9</v>
+        <v>8.6</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>18.7</v>
+        <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J36" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>289</v>
+      </c>
+      <c r="P36" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K36" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="O36" s="3" t="n">
-        <v>85.40000000000001</v>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v>2.9</v>
-      </c>
       <c r="Q36" s="3" t="n">
-        <v>22.6</v>
+        <v>22</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>21.2</v>
+        <v>23.1</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>24.3</v>
+        <v>25.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>88.5</v>
+        <v>72.3</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>3.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="W36" s="3" t="n">
-        <v>20.3</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="W36" s="3" t="n"/>
       <c r="X36" s="3" t="n">
-        <v>22.9</v>
+        <v>24.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>88.5</v>
+        <v>326.6</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3550,76 +3589,76 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>398.9</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>126.4</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>24.3</v>
+        <v>1683.5</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>35.5</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>8.6</v>
+        <v>49.2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>19</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.4</v>
+        <v>15.7</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>9</v>
+        <v>16.2</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>120.6</v>
+        <v>103.5</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>19.3</v>
+        <v>96.5</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>21.7</v>
+        <v>117.2</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>89</v>
+        <v>432.5</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>27</v>
+        <v>691.6</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>23.1</v>
+        <v>6.4</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>25.8</v>
+        <v>62.7</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>72.3</v>
+        <v>13.1</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>651.5</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>25</v>
+        <v>126.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>22.1</v>
+        <v>76.2</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>24.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>0.6</v>
+        <v>62.9</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3635,76 +3674,76 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>1683.5</v>
-      </c>
-      <c r="D38" s="9" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="E38" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F38" s="9" t="n">
-        <v>55.1</v>
+        <v>336.7</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>25.1</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>82.5</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>163.5</v>
+        <v>20.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="N38" s="8" t="n">
-        <v>7.8</v>
+        <v>19.5</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>44.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>437.5</v>
+        <v>87.5</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q38" s="8" t="n">
-        <v>399.6</v>
+        <v>3</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="S38" s="8" t="n">
-        <v>620.1</v>
+        <v>23.1</v>
+      </c>
+      <c r="S38" s="3" t="n">
+        <v>25.2</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>343.7</v>
+        <v>68.7</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>65.7</v>
+        <v>13.1</v>
       </c>
       <c r="V38" s="8" t="n">
-        <v>26.1</v>
+        <v>52.6</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>44.4</v>
+        <v>0.1</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>4.4</v>
+        <v>35.4</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>396.6</v>
+        <v>0.1</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3720,76 +3759,76 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>336.7</v>
+        <v>42.7</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>30</v>
+        <v>31.8</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>20.2</v>
+        <v>19.5</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>25.1</v>
+        <v>25.7</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>18.5</v>
+        <v>18.1</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>12.6</v>
+        <v>15.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>15.7</v>
+        <v>3.4</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="M39" s="8" t="n">
-        <v>25.1</v>
+        <v>41.5</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>19.5</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>22</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>87.5</v>
+        <v>2.4</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>14.9</v>
+        <v>2.1</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>31.4</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>25.2</v>
+        <v>31.6</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>68.7</v>
+        <v>54.5</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>18.1</v>
+        <v>19.8</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>95.2</v>
+        <v>76.8</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>22.4</v>
+        <v>23.8</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>25.4</v>
+        <v>22.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>79.3</v>
+        <v>85.5</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3805,76 +3844,76 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>48.4</v>
+        <v>4.4</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>19.5</v>
+        <v>24.1</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>2.4</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>25.7</v>
+        <v>22.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>13.3</v>
+        <v>3.9</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>2.5</v>
+        <v>19</v>
+      </c>
+      <c r="I40" s="8" t="n">
+        <v>6.4</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0.1</v>
+        <v>4.9</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>0.1</v>
+        <v>22.1</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>88</v>
+        <v>88.8</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q40" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>2.7</v>
+      </c>
+      <c r="Q40" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>23.1</v>
+        <v>19.8</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>23.6</v>
+        <v>22.3</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>54.5</v>
+        <v>89.7</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>19.2</v>
+        <v>2.6</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>26.8</v>
+        <v>21.3</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>77.8</v>
+        <v>1.6</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>25.2</v>
+        <v>21.2</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3890,76 +3929,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>48.8</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>24.1</v>
+        <v>29.4</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>20.2</v>
+        <v>13.5</v>
       </c>
       <c r="F41" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X41" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="G41" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="N41" s="8" t="n">
+      <c r="Y41" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="O41" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q41" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="S41" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v>89.7</v>
-      </c>
-      <c r="U41" s="3" t="n">
+      <c r="Z41" s="3" t="n">
         <v>2.6</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="W41" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y41" s="3" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v>3.6</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3974,77 +4013,81 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
-        <v>448.8</v>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">442
+2 6
+</t>
+        </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>11.4</v>
+        <v>33.1</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>24.5</v>
+        <v>24.9</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>17.4</v>
+        <v>25.8</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>25.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>10.4</v>
+        <v>4.4</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>19.9</v>
+        <v>12.2</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>19.1</v>
+        <v>16.1</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>20.8</v>
+        <v>12.6</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>12.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>28</v>
+        <v>24.7</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>21.6</v>
+        <v>22.3</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>21.7</v>
+        <v>25.4</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>58.4</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>16.1</v>
+        <v>5.2</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>24.6</v>
+        <v>63.2</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>22.2</v>
+        <v>21.4</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>25.2</v>
+        <v>24.4</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>81.3</v>
+        <v>82</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>2.6</v>
+        <v>6.1</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4060,76 +4103,76 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>4.4</v>
+        <v>341.3</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>32.8</v>
+        <v>32.1</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="F43" s="11" t="n">
-        <v>94.90000000000001</v>
+        <v>18.6</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>15.3</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>25.8</v>
+        <v>13.4</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>15.6</v>
+        <v>16.9</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L43" s="8" t="n">
-        <v>78.09999999999999</v>
+        <v>15.2</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>16.1</v>
+        <v>17.7</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>17.6</v>
+        <v>19.4</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>89</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q43" s="8" t="n">
-        <v>30.8</v>
+        <v>2.4</v>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>22.6</v>
+        <v>66.3</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>22.2</v>
+        <v>12.3</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>50</v>
+        <v>21.1</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>23</v>
+        <v>6.3</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>21.4</v>
+        <v>61.1</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>87</v>
+        <v>0.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>0.3</v>
+        <v>4.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4145,76 +4188,76 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>341.3</v>
+        <v>141.6</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="E44" s="8" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H44" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>16.9</v>
-      </c>
       <c r="I44" s="3" t="n">
-        <v>2.2</v>
+        <v>82.8</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>15.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>19</v>
+        <v>0.1</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>17.7</v>
+        <v>19.5</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="P44" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>22.6</v>
+        <v>3.3</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="S44" s="8" t="n">
-        <v>22.3</v>
+        <v>2.2</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>81</v>
+        <v>7</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>92.3</v>
+        <v>3.2</v>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v>33.5</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>20.2</v>
+        <v>21.8</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>4.6</v>
+        <v>73.8</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4229,73 +4272,79 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v>141.6</v>
-      </c>
-      <c r="D45" s="9" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="F45" s="9" t="n">
+      <c r="C45" s="3" t="n"/>
+      <c r="D45" s="10" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>165.6</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>1825.6</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q45" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R45" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="G45" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="I45" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J45" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K45" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="O45" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P45" s="3" t="n"/>
-      <c r="Q45" s="3" t="n"/>
-      <c r="R45" s="3" t="n">
-        <v>2.4</v>
-      </c>
       <c r="S45" s="3" t="n">
-        <v>22</v>
+        <v>22.9</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>7.4</v>
+        <v>69</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>7.2</v>
+        <v>11.9</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>455.1</v>
+        <v>242.4</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>7.1</v>
+        <v>21.8</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Y45" s="3" t="n">
-        <v>81.5</v>
+        <v>124.2</v>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 7
+57
+</t>
+        </is>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4311,43 +4360,46 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>311.7</v>
-      </c>
-      <c r="D46" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E46" s="9" t="n">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="F46" s="9" t="n">
-        <v>240.1</v>
+        <v>5.3</v>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>48</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>10.1</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="I46" s="8" t="n">
-        <v>13.3</v>
+        <v>1.1</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>16.6</v>
+        <v>2.8</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>30</v>
+        <v>1.8</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>3.4</v>
+        <v>19.4</v>
+      </c>
+      <c r="M46" s="8" t="n">
+        <v>825.6</v>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20 8
+</t>
+        </is>
       </c>
       <c r="O46" s="3" t="n">
-        <v>324.1</v>
+        <v>89</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>2.4</v>
@@ -4356,29 +4408,31 @@
         <v>26.2</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>22.9</v>
-      </c>
+        <v>21.5</v>
+      </c>
+      <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="n">
         <v>69</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="8" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="W46" s="3" t="n"/>
+      <c r="X46" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="W46" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="Y46" s="3" t="n"/>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 7
+57
+</t>
+        </is>
+      </c>
       <c r="Z46" s="3" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -41,12 +41,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
@@ -55,6 +49,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC0CB"/>
         <bgColor rgb="00FFC0CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
   </fills>
@@ -763,75 +763,69 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>437.3</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>1.3</v>
+        <v>9437.5</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>24.2</v>
+        <v>0.4</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>22.4</v>
+        <v>142.1</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>14.4</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.1</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K4" s="3" t="n"/>
+        <v>14.2</v>
+      </c>
+      <c r="K4" s="3" t="inlineStr"/>
       <c r="L4" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>17.5</v>
+      <c r="N4" s="8" t="n">
+        <v>82.5</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>87</v>
+        <v>187</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q4" s="8" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="R4" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="R4" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="S4" s="3" t="n">
-        <v>27.8</v>
+      <c r="S4" s="8" t="n">
+        <v>27</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>63.7</v>
+        <v>631.1</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>22.2</v>
+        <v>18.1</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X4" s="3" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -845,29 +839,25 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="D5" s="3" t="n">
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="F5" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F5" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>57.2</v>
+        <v>5.7</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>0.4</v>
+        <v>11.6</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="8" t="n">
+        <v>87.40000000000001</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>25.8</v>
@@ -876,46 +866,42 @@
         <v>19.1</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N5" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="N5" s="8" t="n">
         <v>19.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>24.3</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="S5" s="3" t="n">
+      <c r="S5" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>82.8</v>
+        <v>187.8</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>4.2</v>
+        <v>12.9</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>18.9</v>
-      </c>
+        <v>20.6</v>
+      </c>
+      <c r="W5" s="3" t="inlineStr"/>
       <c r="X5" s="3" t="n">
-        <v>20.7</v>
+        <v>27.5</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>35</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>3.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -931,9 +917,9 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>431.6</v>
-      </c>
-      <c r="D6" s="3" t="n">
+        <v>432.4</v>
+      </c>
+      <c r="D6" s="8" t="n">
         <v>31.4</v>
       </c>
       <c r="E6" s="3" t="n">
@@ -943,64 +929,62 @@
         <v>25.6</v>
       </c>
       <c r="G6" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>3.6</v>
-      </c>
       <c r="K6" s="3" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="L6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L6" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="M6" s="3" t="n">
-        <v>12</v>
+      <c r="M6" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>188.6</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q6" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="Q6" s="8" t="n">
         <v>29.8</v>
       </c>
-      <c r="R6" s="3" t="n">
-        <v>23.9</v>
+      <c r="R6" s="8" t="n">
+        <v>232.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>25.9</v>
+        <v>651.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>61.9</v>
+        <v>1608.9</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="8" t="n">
         <v>23.2</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>26.5</v>
+        <v>20.7</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>11.1</v>
+        <v>185</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>2.5</v>
+        <v>13.6</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1016,76 +1000,74 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>437.3</v>
-      </c>
-      <c r="D7" s="3" t="n">
+        <v>1437.3</v>
+      </c>
+      <c r="D7" s="8" t="n">
         <v>33</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>8</v>
+        <v>0.8</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G7" s="3" t="n">
+        <v>251.1</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M7" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="M7" s="8" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>17.3</v>
+      <c r="N7" s="8" t="n">
+        <v>67.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>187.6</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q7" s="8" t="n">
-        <v>18.9</v>
+      <c r="Q7" s="3" t="n">
+        <v>31.9</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="S7" s="3" t="n">
+      <c r="S7" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>5.1</v>
+        <v>2022.1</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="V7" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W7" s="3" t="n">
+      <c r="V7" s="8" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="W7" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="X7" s="3" t="n">
-        <v>2.8</v>
+      <c r="X7" s="8" t="n">
+        <v>27.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>5.2</v>
+        <v>177.9</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1101,61 +1083,61 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>86.2</v>
+        <v>1297.2</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>26.2</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12.2</v>
+        <v>17.2</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>4.4</v>
+        <v>16.9</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="K8" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="L8" s="3" t="n">
+      <c r="K8" s="8" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="L8" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="M8" s="8" t="n">
-        <v>865.6</v>
-      </c>
-      <c r="N8" s="3" t="n">
+      <c r="M8" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="N8" s="8" t="n">
         <v>20.5</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>82.7</v>
+        <v>187.7</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q8" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="Q8" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="S8" s="3" t="n">
+      <c r="S8" s="8" t="n">
         <v>33.2</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>95.40000000000001</v>
+        <v>2524.1</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>1.6</v>
+        <v>11.6</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>24</v>
@@ -1163,14 +1145,14 @@
       <c r="W8" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X8" s="3" t="n">
-        <v>22</v>
+      <c r="X8" s="8" t="n">
+        <v>27</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>96.2</v>
+        <v>90.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1186,24 +1168,20 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="F9" s="11" t="n"/>
+        <v>1666.5</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>852.6</v>
+      </c>
+      <c r="E9" s="10" t="inlineStr"/>
+      <c r="F9" s="10" t="inlineStr"/>
       <c r="G9" s="3" t="n">
-        <v>611.1</v>
+        <v>681.1</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>4.4</v>
-      </c>
+        <v>80.5</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="n">
         <v>15.5</v>
       </c>
@@ -1211,49 +1189,43 @@
         <v>44.3</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>94.3</v>
+        <v>194.3</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>82.8</v>
+        <v>187.8</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>96.3</v>
+        <v>196.3</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>440.9</v>
+        <v>1440.9</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>12.9</v>
+        <v>162.9</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>138.8</v>
+        <v>1138.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>11.3</v>
+        <v>1617.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>31.9</v>
+        <v>132.9</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>360.9</v>
+        <v>1360.9</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>58.5</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>126.1</v>
-      </c>
-      <c r="W9" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X9" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Y9" s="3" t="n">
-        <v>2.8</v>
-      </c>
+        <v>1126.1</v>
+      </c>
+      <c r="W9" s="3" t="inlineStr"/>
+      <c r="X9" s="3" t="inlineStr"/>
+      <c r="Y9" s="3" t="inlineStr"/>
       <c r="Z9" s="3" t="n">
-        <v>2.8</v>
+        <v>32.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1269,76 +1241,72 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>333.2</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>18.5</v>
+        <v>333.3</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>185.1</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>1.6</v>
+        <v>12</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>16.1</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K10" s="8" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="L10" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="M10" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>1.3</v>
-      </c>
+      <c r="M10" s="8" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="N10" s="3" t="inlineStr"/>
       <c r="O10" s="3" t="n">
-        <v>88.2</v>
+        <v>188.2</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="R10" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="R10" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="S10" s="3" t="n">
-        <v>2.6</v>
+      <c r="S10" s="8" t="n">
+        <v>26.4</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>2.2</v>
+        <v>272.2</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>0.4</v>
+        <v>11.7</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>25.8</v>
+        <v>0.5</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>2.6</v>
+        <v>22.6</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>806.5</v>
+        <v>180.5</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>6.6</v>
+        <v>16.6</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1354,77 +1322,73 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>445.6</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="F11" s="3" t="n">
+        <v>1445</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F11" s="11" t="n">
         <v>24.3</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>18.8</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>3.3</v>
+        <v>13.3</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="3" t="n">
-        <v>20.1</v>
-      </c>
+      <c r="L11" s="3" t="inlineStr"/>
       <c r="M11" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="N11" s="3" t="n">
-        <v>10.7</v>
+      <c r="N11" s="8" t="n">
+        <v>20.7</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>187.9</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>27.9</v>
+        <v>41.9</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="S11" s="3" t="n">
-        <v>31.9</v>
+      <c r="S11" s="8" t="n">
+        <v>981.9</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="U11" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="V11" s="3" t="n">
+      <c r="U11" s="8" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="V11" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>30.9</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>197.5</v>
+      </c>
+      <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1441,32 +1405,32 @@
       <c r="C12" s="3" t="n">
         <v>383.6</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="11" t="n">
         <v>28.1</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="11" t="n">
         <v>19.6</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="11" t="n">
         <v>23.9</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>84.5</v>
+        <v>18.5</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2.9</v>
+        <v>12.9</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>20.6</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>19.3</v>
@@ -1478,10 +1442,10 @@
         <v>88.40000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>22.7</v>
+        <v>20.7</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>72.2</v>
+        <v>27.8</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>25.2</v>
@@ -1490,25 +1454,25 @@
         <v>30.8</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>8544.1</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="V12" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W12" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X12" s="3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="W12" s="8" t="n">
+        <v>284.4</v>
+      </c>
+      <c r="X12" s="8" t="n">
         <v>30.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>97.7</v>
+        <v>197.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>0.8</v>
+        <v>10.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1524,33 +1488,33 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>356.1</v>
-      </c>
-      <c r="D13" s="3" t="n">
+        <v>39356.7</v>
+      </c>
+      <c r="D13" s="11" t="n">
         <v>31.1</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="11" t="n">
         <v>19.8</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F13" s="11" t="n">
         <v>25.5</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="H13" s="3" t="n">
-        <v>12.6</v>
+      <c r="H13" s="8" t="n">
+        <v>17.6</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.6</v>
+        <v>12.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="L13" s="3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="L13" s="8" t="n">
         <v>20</v>
       </c>
       <c r="M13" s="3" t="n">
@@ -1560,40 +1524,38 @@
         <v>20.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>2.5</v>
-      </c>
+        <v>189.1</v>
+      </c>
+      <c r="P13" s="3" t="inlineStr"/>
       <c r="Q13" s="8" t="n">
         <v>28.6</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="S13" s="8" t="n">
-        <v>24.7</v>
+      <c r="S13" s="3" t="n">
+        <v>32.7</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="U13" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="V13" s="3" t="n">
+      <c r="U13" s="8" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="V13" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="W13" s="3" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="X13" s="3" t="n">
+      <c r="W13" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X13" s="8" t="n">
         <v>28.9</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>44.4</v>
+        <v>197.7</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>2.2</v>
+        <v>10.7</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1609,43 +1571,41 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>340.8</v>
-      </c>
-      <c r="D14" s="3" t="n">
+        <v>13974</v>
+      </c>
+      <c r="D14" s="11" t="n">
         <v>32.5</v>
       </c>
-      <c r="E14" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="F14" s="3" t="n">
+      <c r="E14" s="11" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F14" s="11" t="n">
         <v>26.1</v>
       </c>
-      <c r="G14" s="8" t="n">
-        <v>22.9</v>
+      <c r="G14" s="3" t="n">
+        <v>12.9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>12.2</v>
+        <v>17.2</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>3.3</v>
-      </c>
+        <v>12.8</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="3" t="n">
-        <v>57.2</v>
+        <v>5.7</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>189.9</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>2.3</v>
@@ -1654,10 +1614,10 @@
         <v>30.6</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>2.6</v>
+        <v>22.6</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>2.3</v>
+        <v>22.3</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>50.9</v>
@@ -1671,11 +1631,11 @@
       <c r="W14" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="X14" s="3" t="n">
+      <c r="X14" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>93</v>
+        <v>193</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>1.8</v>
@@ -1696,41 +1656,39 @@
       <c r="C15" s="3" t="n">
         <v>433.5</v>
       </c>
-      <c r="D15" s="3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>44.1</v>
+      <c r="D15" s="11" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>24.9</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="H15" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="H15" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>26.4</v>
+        <v>20.4</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="N15" s="3" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="n">
-        <v>88.8</v>
+        <v>188.8</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>2.6</v>
@@ -1741,29 +1699,29 @@
       <c r="R15" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S15" s="3" t="n">
+      <c r="S15" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>63.8</v>
+        <v>163.8</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="V15" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W15" s="3" t="n">
-        <v>21.1</v>
+      <c r="V15" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="W15" s="8" t="n">
+        <v>241.1</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>2.8</v>
+        <v>22.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>11.5</v>
+        <v>174</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>7.2</v>
+        <v>17.9</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1779,76 +1737,70 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>929.1</v>
-      </c>
-      <c r="F16" s="10" t="n">
+        <v>11992.8</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="F16" s="11" t="n">
         <v>124.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>50.8</v>
+        <v>150.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>90.3</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>11.1</v>
-      </c>
+        <v>190.3</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>160.9</v>
+        <v>1100.9</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>21122.2</v>
+        <v>105.2</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>11.1</v>
+        <v>444.1</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>8.9</v>
+        <v>12.9</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>142.8</v>
+        <v>1142.8</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>23.7</v>
+        <v>123</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>42.5</v>
+        <v>142.5</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>368.7</v>
+        <v>1368.7</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>533.4</v>
+        <v>533441.5</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>120.8</v>
       </c>
-      <c r="W16" s="3" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>7.3</v>
-      </c>
+      <c r="W16" s="3" t="inlineStr"/>
+      <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
-        <v>45.1</v>
+        <v>1455.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>3.4</v>
+        <v>13.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1863,79 +1815,75 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-3986
-</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="n">
+      <c r="C17" s="3" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="D17" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E17" s="11" t="n">
         <v>19.8</v>
       </c>
-      <c r="F17" s="10" t="n">
-        <v>14.4</v>
+      <c r="F17" s="9" t="n">
+        <v>224.9</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>2.2</v>
+        <v>18.1</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>81.2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="N17" s="3" t="n">
-        <v>1</v>
+      <c r="N17" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>88.8</v>
+        <v>188.8</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q17" s="3" t="n">
-        <v>28.6</v>
+      <c r="Q17" s="8" t="n">
+        <v>86.09999999999999</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>22.5</v>
+        <v>946.4</v>
+      </c>
+      <c r="S17" s="8" t="n">
+        <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>6.6</v>
+        <v>173.7</v>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v>10.6</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>42.8</v>
+        <v>24.2</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>23</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>2.5</v>
+        <v>27.5</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>1.9</v>
+        <v>191</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>2.7</v>
+        <v>12.7</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1951,31 +1899,29 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="D18" s="3" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="D18" s="11" t="n">
         <v>30.8</v>
       </c>
-      <c r="E18" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>3.5</v>
+      <c r="E18" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="8" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>39.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.6</v>
+        <v>18</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>19.2</v>
@@ -1987,44 +1933,40 @@
         <v>19.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="P18" s="8" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="Q18" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="Q18" s="8" t="n">
         <v>28.6</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S18" s="3" t="n">
+      <c r="S18" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>63.1</v>
+        <v>163.1</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V18" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="V18" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="W18" s="3" t="n">
+      <c r="W18" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>31</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="Z18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-8 179
-</t>
-        </is>
+        <v>92.09999999999999</v>
+      </c>
+      <c r="Z18" s="3" t="n">
+        <v>2.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2040,46 +1982,46 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>423.9</v>
-      </c>
-      <c r="D19" s="3" t="n">
+        <v>1423.9</v>
+      </c>
+      <c r="D19" s="11" t="n">
         <v>32.5</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" s="11" t="n">
         <v>25.5</v>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>14.2</v>
+      <c r="G19" s="8" t="n">
+        <v>124.8</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16.9</v>
+        <v>16.1</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>3.3</v>
+        <v>13.5</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.8</v>
+        <v>28.5</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="M19" s="3" t="n">
-        <v>18.2</v>
+      <c r="M19" s="8" t="n">
+        <v>28.2</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>87.5</v>
+        <v>2.3</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>31.8</v>
@@ -2091,33 +2033,25 @@
         <v>25.3</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>54</v>
+        <v>62.1</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="V19" s="3" t="n">
-        <v>85.8</v>
+      <c r="V19" s="8" t="n">
+        <v>25.8</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="X19" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-44
-</t>
-        </is>
-      </c>
-      <c r="Z19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-818
-</t>
-        </is>
+      <c r="X19" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y19" s="3" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="Z19" s="3" t="n">
+        <v>16.2</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2133,80 +2067,77 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3561.5</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E20" s="3" t="n">
+        <v>256.8</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E20" s="11" t="n">
         <v>19.8</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F20" s="11" t="n">
         <v>23.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-1 8 4
-7
-</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="n">
-        <v>82.8</v>
+        <v>17.4</v>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="K20" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="M20" s="3" t="n">
+      <c r="K20" s="8" t="n">
+        <v>2408</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="M20" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="N20" s="3" t="n">
+      <c r="N20" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>21.1</v>
+        <v>189</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Q20" s="8" t="n">
-        <v>535.2</v>
-      </c>
-      <c r="R20" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R20" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>20.8</v>
+        <v>70.7</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>9.5</v>
+        <v>19.5</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="W20" s="3" t="n">
+      <c r="W20" s="8" t="n">
         <v>20.5</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>2.2</v>
+        <v>21.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="Z20" s="3" t="n"/>
+        <v>167.2</v>
+      </c>
+      <c r="Z20" s="3" t="n">
+        <v>10.2</v>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2221,78 +2152,72 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>433.5</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="E21" s="3" t="n">
+        <v>1433.5</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E21" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F21" s="11" t="n">
         <v>24.6</v>
       </c>
-      <c r="G21" s="3" t="n"/>
+      <c r="G21" s="3" t="n">
+        <v>12.4</v>
+      </c>
       <c r="H21" s="3" t="n">
-        <v>12.4</v>
+        <v>17.7</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K21" s="3" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>18.3</v>
+        <v>1.4</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>86.7</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q21" s="3" t="n">
+        <v>186.7</v>
+      </c>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="8" t="n">
         <v>30.1</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>41.7</v>
+        <v>21.7</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>531</v>
+        <v>151</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="V21" s="3" t="n">
-        <v>44.3</v>
+      <c r="V21" s="8" t="n">
+        <v>24.3</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-8111
-</t>
-        </is>
+        <v>2.2</v>
+      </c>
+      <c r="X21" s="3" t="n">
+        <v>25.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>850.1</v>
+        <v>185</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2308,46 +2233,46 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F22" s="9" t="n">
-        <v>84.5</v>
+        <v>374</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>24.5</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.2</v>
+        <v>15.5</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2.1</v>
+        <v>21.1</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>3.5</v>
+        <v>13.5</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>3.7</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>12.5</v>
+        <v>17.6</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.5</v>
+        <v>17.5</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>872</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>2.6</v>
+        <v>187</v>
+      </c>
+      <c r="P22" s="8" t="n">
+        <v>21.6</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>30.2</v>
@@ -2355,26 +2280,26 @@
       <c r="R22" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="S22" s="3" t="n">
+      <c r="S22" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>568.1</v>
+        <v>156.4</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="V22" s="3" t="n">
-        <v>21.8</v>
+      <c r="V22" s="8" t="n">
+        <v>21.2</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="X22" s="3" t="n">
-        <v>4.6</v>
+      <c r="X22" s="8" t="n">
+        <v>21.6</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>5.5</v>
+        <v>185.5</v>
       </c>
       <c r="Z22" s="3" t="n">
         <v>3.6</v>
@@ -2393,19 +2318,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1985.5</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>653.4</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>123</v>
+        <v>1925.5</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>153.1</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>1123</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>60.3</v>
+        <v>160.3</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>85.59999999999999</v>
@@ -2414,55 +2339,47 @@
         <v>11.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>15.5</v>
+        <v>135.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>49.2</v>
+        <v>49.9</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>95.2</v>
+        <v>195.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>882.6</v>
+        <v>1882.8</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>96.5</v>
+        <v>196.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>438.2</v>
+        <v>1437.2</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q23" s="3" t="n">
-        <v>146.2</v>
-      </c>
-      <c r="R23" s="3" t="n">
-        <v>4.3</v>
-      </c>
+        <v>13.7</v>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr"/>
       <c r="S23" s="3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>2952.6</v>
+        <v>1295.2</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>85.40000000000001</v>
-      </c>
-      <c r="V23" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W23" s="3" t="n">
-        <v>10.7</v>
-      </c>
+        <v>85.2</v>
+      </c>
+      <c r="V23" s="3" t="inlineStr"/>
+      <c r="W23" s="3" t="inlineStr"/>
       <c r="X23" s="3" t="n">
-        <v>26.7</v>
+        <v>1126.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>0.4</v>
+        <v>1411</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>2.1</v>
+        <v>27.1</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2478,22 +2395,22 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>5851.1</v>
-      </c>
-      <c r="D24" s="10" t="n">
+        <v>385.1</v>
+      </c>
+      <c r="D24" s="11" t="n">
         <v>30.6</v>
       </c>
-      <c r="E24" s="10" t="n">
+      <c r="E24" s="11" t="n">
         <v>18.6</v>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="F24" s="11" t="n">
         <v>24.6</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>12.6</v>
+        <v>12</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>87.40000000000001</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
@@ -2501,23 +2418,21 @@
       <c r="J24" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K24" s="3" t="n"/>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M24" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>1.3</v>
+      <c r="M24" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="N24" s="8" t="n">
+        <v>19.5</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>872.4</v>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q24" s="3" t="n">
+        <v>187.4</v>
+      </c>
+      <c r="P24" s="3" t="inlineStr"/>
+      <c r="Q24" s="8" t="n">
         <v>29.2</v>
       </c>
       <c r="R24" s="3" t="n">
@@ -2527,25 +2442,25 @@
         <v>23.8</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>59</v>
+        <v>159</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V24" s="3" t="n">
-        <v>4.4</v>
+        <v>17.6</v>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v>24.4</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="X24" s="3" t="n">
-        <v>0.9</v>
+      <c r="X24" s="8" t="n">
+        <v>25.3</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>0.8</v>
+        <v>182.2</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2561,19 +2476,19 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="D25" s="8" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>45.1</v>
+        <v>1374</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>25.7</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.1</v>
+        <v>9.1</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>18.8</v>
@@ -2582,55 +2497,53 @@
         <v>2.4</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>13.6</v>
+      </c>
+      <c r="K25" s="3" t="inlineStr"/>
       <c r="L25" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>0.1</v>
+        <v>18.4</v>
       </c>
       <c r="N25" s="8" t="n">
-        <v>60.4</v>
+        <v>20.4</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>324.3</v>
+        <v>2.2</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>31.3</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>1.8</v>
+        <v>243.1</v>
+      </c>
+      <c r="S25" s="8" t="n">
+        <v>25.9</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>56.9</v>
+        <v>956.9</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="V25" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W25" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>224.2</v>
+      </c>
+      <c r="W25" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="X25" s="3" t="n">
-        <v>66.09999999999999</v>
+      <c r="X25" s="8" t="n">
+        <v>22.6</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>74.8</v>
+        <v>1747.6</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2646,76 +2559,76 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>45.1</v>
+        <v>329.8</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>24.7</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>2.4</v>
+        <v>12.2</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>72</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>11.9</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>36.3</v>
+        <v>12.6</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>7.5</v>
+        <v>10.3</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>18.1</v>
+        <v>1.6</v>
       </c>
       <c r="N26" s="8" t="n">
-        <v>60.4</v>
+        <v>949.2</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>90</v>
+        <v>187</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>2.2</v>
+        <v>12.8</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>324.3</v>
+        <v>24.4</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>24.3</v>
+        <v>21.8</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>25.9</v>
+        <v>24.5</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>56.9</v>
+        <v>180</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="V26" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="V26" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>6.8</v>
+      </c>
+      <c r="X26" s="8" t="n">
+        <v>24.6</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>74.8</v>
+        <v>181.1</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>2.5</v>
+        <v>17.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2731,80 +2644,74 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>381.2</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>24.2</v>
+        <v>0.8</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>23.8</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>12.8</v>
+        <v>18.8</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>2.6</v>
+        <v>17.8</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
+      <c r="J27" s="8" t="n">
+        <v>21.9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>19</v>
+        <v>5.3</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>20.2</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>19.2</v>
+        <v>18.8</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>20.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>87.2</v>
+        <v>187.5</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q27" s="3" t="n">
-        <v>24.4</v>
+        <v>21.9</v>
+      </c>
+      <c r="Q27" s="8" t="n">
+        <v>6</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>24.5</v>
+        <v>23</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>86</v>
+        <v>168.4</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>6.1</v>
+        <v>10.6</v>
       </c>
       <c r="V27" s="8" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="W27" s="3" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v>24.6</v>
+        <v>23.2</v>
+      </c>
+      <c r="W27" s="8" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>23</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="Z27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-54
-</t>
-        </is>
+        <v>180.8</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v>5.4</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2820,76 +2727,76 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>354.2</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>23.8</v>
+        <v>9389.299999999999</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>25</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>12.8</v>
+        <v>19.6</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
+      </c>
+      <c r="J28" s="8" t="n">
+        <v>39.8</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>5.3</v>
+        <v>19.6</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>10.2</v>
+        <v>20.6</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>61.2</v>
+        <v>19.2</v>
+      </c>
+      <c r="N28" s="8" t="n">
+        <v>21.3</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>82.5</v>
+        <v>187.4</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="Q28" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="R28" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="S28" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="V28" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="R28" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="S28" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="T28" s="3" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="U28" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V28" s="3" t="n">
-        <v>63.5</v>
-      </c>
       <c r="W28" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="X28" s="3" t="n">
-        <v>23</v>
+        <v>23.6</v>
+      </c>
+      <c r="X28" s="8" t="n">
+        <v>27.6</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>8.1</v>
+        <v>82</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2905,76 +2812,76 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>389.3</v>
-      </c>
-      <c r="D29" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E29" s="9" t="n">
+        <v>408.5</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K29" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K29" s="8" t="n">
-        <v>239.6</v>
-      </c>
       <c r="L29" s="3" t="n">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="N29" s="3" t="n">
+      <c r="N29" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q29" s="3" t="n">
-        <v>28.2</v>
+        <v>21.3</v>
+      </c>
+      <c r="Q29" s="8" t="n">
+        <v>28.6</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="S29" s="3" t="n">
-        <v>24.8</v>
+      <c r="S29" s="8" t="n">
+        <v>226.5</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>162.6</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V29" s="3" t="n">
-        <v>26</v>
+        <v>14.6</v>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v>25.5</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="X29" s="8" t="n">
-        <v>27.6</v>
+        <v>23</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>26.5</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>82</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>6.1</v>
+        <v>16.1</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2990,76 +2897,76 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>494.5</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>24.9</v>
+        <v>1856.4</v>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>150.3</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>124.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>9.1</v>
+        <v>152.5</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>4.1</v>
+        <v>191.9</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.1</v>
+        <v>180</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>2.9</v>
+        <v>15.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>20.2</v>
+        <v>125.4</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>20.3</v>
+        <v>199.6</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>19.5</v>
+        <v>93.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>21.5</v>
+        <v>1103.2</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>90</v>
+        <v>1441.9</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>2.3</v>
+        <v>13.1</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>28.6</v>
+        <v>1138.5</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>23</v>
+        <v>1113.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>24.5</v>
+        <v>122.8</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>62.6</v>
+        <v>1332.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>14.6</v>
+        <v>164.5</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>85.5</v>
+        <v>1823.1</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>23</v>
+        <v>110.1</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>26.5</v>
+        <v>1124.3</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>1399.8</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>2.6</v>
+        <v>32.6</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3075,76 +2982,74 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="D31" s="10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="F31" s="10" t="n">
-        <v>24.1</v>
+        <v>383.1</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>24.8</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>2.9</v>
+        <v>184.5</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>25.4</v>
-      </c>
+        <v>3.2</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>19.9</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>93.2</v>
+        <v>18.6</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>113.6</v>
+        <v>6.4</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>44.4</v>
+        <v>188.4</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>13.1</v>
+        <v>12.6</v>
       </c>
       <c r="Q31" s="8" t="n">
-        <v>38.5</v>
+        <v>27.7</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>3.7</v>
+        <v>22.7</v>
       </c>
       <c r="S31" s="8" t="n">
-        <v>18.7</v>
+        <v>24.5</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>334.8</v>
+        <v>166.6</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>0.5</v>
+        <v>12.9</v>
       </c>
       <c r="V31" s="8" t="n">
-        <v>23.1</v>
+        <v>24.6</v>
       </c>
       <c r="W31" s="8" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="X31" s="8" t="n">
-        <v>24.3</v>
+        <v>22</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>94.90000000000001</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>322.8</v>
+        <v>80</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0.2</v>
+        <v>6.5</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3162,78 +3067,70 @@
       <c r="C32" s="3" t="n">
         <v>437.3</v>
       </c>
-      <c r="D32" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E32" s="9" t="n">
-        <v>2.6</v>
+      <c r="D32" s="3" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>20.2</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>1.5</v>
-      </c>
+        <v>865.1</v>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
       <c r="H32" s="3" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2</v>
+        <v>13.5</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>3.2</v>
+        <v>14.4</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>20.6</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>18.5</v>
+        <v>12.3</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>26.6</v>
+        <v>21.5</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>2.6</v>
-      </c>
+        <v>188.4</v>
+      </c>
+      <c r="P32" s="3" t="inlineStr"/>
       <c r="Q32" s="3" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v>22.7</v>
+        <v>31</v>
+      </c>
+      <c r="R32" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>24.5</v>
+        <v>25.4</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>66.5</v>
+        <v>156.6</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>12.9</v>
+        <v>19.5</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="X32" s="3" t="n">
-        <v>42.9</v>
+        <v>23.7</v>
+      </c>
+      <c r="X32" s="8" t="n">
+        <v>26.4</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-78
-</t>
-        </is>
+        <v>69.09999999999999</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>1118.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3249,76 +3146,74 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>3272</v>
+        <v>1397</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>20.2</v>
+        <v>33.7</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>19.8</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>26.5</v>
+        <v>26.7</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>12.6</v>
+        <v>34.1</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>18.2</v>
+        <v>17.9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>4.4</v>
-      </c>
+        <v>4.3</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr"/>
       <c r="K33" s="3" t="n">
-        <v>0.8</v>
+        <v>10</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>20.9</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>19.3</v>
+        <v>49.5</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>61.5</v>
+        <v>26.7</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>28.4</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Q33" s="3" t="n">
-        <v>0.1</v>
+        <v>3.1</v>
+      </c>
+      <c r="Q33" s="8" t="n">
+        <v>32.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>44</v>
+        <v>23.9</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>25.4</v>
+        <v>63.4</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="V33" s="3" t="n">
+        <v>1947.7</v>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="V33" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="W33" s="3" t="n">
-        <v>2.8</v>
+      <c r="W33" s="8" t="n">
+        <v>22.8</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>5.8</v>
+        <v>25.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>2.6</v>
+        <v>127.6</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>0.3</v>
+        <v>17.4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3334,80 +3229,74 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="D34" s="9" t="n">
-        <v>0.3</v>
+        <v>362.4</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>30.4</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>19.8</v>
+        <v>20.2</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>26.2</v>
+        <v>25.3</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>13.9</v>
+        <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="I34" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="I34" s="3" t="n">
-        <v>4.4</v>
-      </c>
       <c r="J34" s="3" t="n">
-        <v>5.5</v>
+        <v>12.6</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>20.9</v>
+        <v>20.4</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="P34" s="3" t="n">
-        <v>2.9</v>
-      </c>
+        <v>187.3</v>
+      </c>
+      <c r="P34" s="3" t="inlineStr"/>
       <c r="Q34" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S34" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="S34" s="8" t="n">
         <v>26.6</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>78.59999999999999</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>2.2</v>
+        <v>17.2</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>45.5</v>
+        <v>55.4</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="X34" s="3" t="n">
+      <c r="X34" s="8" t="n">
         <v>27.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="Z34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54
-5
-</t>
-        </is>
+        <v>183.2</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>15.4</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3423,52 +3312,54 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>884.5</v>
-      </c>
-      <c r="D35" s="3" t="n">
+        <v>187.9</v>
+      </c>
+      <c r="D35" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="F35" s="3" t="n">
+      <c r="F35" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>3.4</v>
+        <v>23.9</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="I35" s="3" t="n"/>
+      <c r="I35" s="3" t="n">
+        <v>10.3</v>
+      </c>
       <c r="J35" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K35" s="8" t="n">
-        <v>98</v>
-      </c>
-      <c r="L35" s="3" t="n">
-        <v>24.1</v>
+        <v>10.4</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="L35" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="N35" s="3" t="n">
-        <v>61.3</v>
+      <c r="N35" s="8" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>25.4</v>
+        <v>854.1</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q35" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Q35" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="S35" s="3" t="n">
+      <c r="S35" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="T35" s="3" t="n">
@@ -3483,14 +3374,14 @@
       <c r="W35" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="X35" s="3" t="n">
+      <c r="X35" s="8" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="Y35" s="3" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="Z35" s="3" t="n">
         <v>2.9</v>
-      </c>
-      <c r="Y35" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v>0.6</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3508,17 +3399,17 @@
       <c r="C36" s="3" t="n">
         <v>398.9</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="E36" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="F36" s="3" t="n">
+      <c r="E36" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F36" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>8.6</v>
+        <v>18.6</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>19</v>
@@ -3530,7 +3421,7 @@
         <v>2.8</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>20.6</v>
@@ -3538,23 +3429,23 @@
       <c r="M36" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="N36" s="3" t="n">
-        <v>21.2</v>
+      <c r="N36" s="8" t="n">
+        <v>21.7</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>289</v>
+        <v>189</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q36" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="R36" s="3" t="n">
+      <c r="Q36" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="R36" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="S36" s="3" t="n">
-        <v>25.8</v>
+      <c r="S36" s="8" t="n">
+        <v>593.8</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>72.3</v>
@@ -3562,18 +3453,20 @@
       <c r="U36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V36" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="W36" s="3" t="n"/>
-      <c r="X36" s="3" t="n">
+      <c r="V36" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W36" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X36" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>326.6</v>
+        <v>178.2</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.4</v>
+        <v>16.9</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3589,22 +3482,16 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1683.5</v>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="F37" s="10" t="n">
-        <v>35.5</v>
-      </c>
+        <v>11683.5</v>
+      </c>
+      <c r="D37" s="10" t="inlineStr"/>
+      <c r="E37" s="10" t="inlineStr"/>
+      <c r="F37" s="10" t="inlineStr"/>
       <c r="G37" s="3" t="n">
         <v>49.2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>192.4</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>12.6</v>
@@ -3613,52 +3500,44 @@
         <v>15.7</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>16.2</v>
+        <v>160.8</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>103.5</v>
       </c>
-      <c r="M37" s="3" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>117.2</v>
-      </c>
+      <c r="M37" s="3" t="inlineStr"/>
+      <c r="N37" s="3" t="inlineStr"/>
       <c r="O37" s="3" t="n">
-        <v>432.5</v>
+        <v>1432.5</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>1.9</v>
+        <v>14.9</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>691.6</v>
+        <v>139.6</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>6.4</v>
+        <v>115.4</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>62.7</v>
+        <v>126.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>13.1</v>
+        <v>3431.1</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>651.5</v>
+        <v>165.7</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>126.1</v>
       </c>
-      <c r="W37" s="3" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="X37" s="3" t="n">
-        <v>72.09999999999999</v>
-      </c>
+      <c r="W37" s="3" t="inlineStr"/>
+      <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
-        <v>79.3</v>
+        <v>396.6</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>62.9</v>
+        <v>342.4</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3676,74 +3555,72 @@
       <c r="C38" s="3" t="n">
         <v>336.7</v>
       </c>
-      <c r="D38" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="F38" s="10" t="n">
-        <v>25.1</v>
+      <c r="D38" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>5.4</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="H38" s="8" t="n">
-        <v>82.5</v>
+      <c r="H38" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>7.4</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="J38" s="8" t="n">
+        <v>211.1</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>44.4</v>
+        <v>21.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>87.5</v>
+        <v>187.5</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>17.9</v>
+        <v>27.9</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S38" s="3" t="n">
+      <c r="S38" s="8" t="n">
         <v>25.2</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>68.7</v>
+        <v>168.7</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v>52.6</v>
+        <v>18.1</v>
+      </c>
+      <c r="V38" s="3" t="n">
+        <v>25.2</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>0.1</v>
+        <v>22.4</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>35.4</v>
+        <v>25.4</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>0.1</v>
+        <v>79.3</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>0.6</v>
+        <v>18.9</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3759,12 +3636,12 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>42.7</v>
+        <v>1400.8</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>31.8</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="8" t="n">
         <v>19.5</v>
       </c>
       <c r="F39" s="3" t="n">
@@ -3777,58 +3654,58 @@
         <v>18.1</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>15.5</v>
+        <v>52.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>41.5</v>
+        <v>10</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>20.5</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N39" s="3" t="n">
+      <c r="N39" s="8" t="n">
         <v>22</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>31.4</v>
+        <v>91</v>
+      </c>
+      <c r="P39" s="8" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>30.4</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>31.6</v>
+        <v>23.6</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>54.5</v>
+        <v>345.1</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="V39" s="3" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="W39" s="3" t="n">
+      <c r="V39" s="8" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="W39" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="X39" s="3" t="n">
-        <v>22.6</v>
+      <c r="X39" s="8" t="n">
+        <v>27.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>85.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>6.6</v>
+        <v>17.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3844,31 +3721,31 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>2.4</v>
+        <v>74.40000000000001</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>20.2</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H40" s="3" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H40" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="I40" s="8" t="n">
-        <v>6.4</v>
+      <c r="I40" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.5</v>
+        <v>10.5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>4.9</v>
+        <v>14.9</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>20.4</v>
@@ -3877,16 +3754,16 @@
         <v>19.1</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>22.1</v>
+        <v>10.1</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>88.8</v>
+        <v>88</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>2.7</v>
+        <v>18.7</v>
       </c>
       <c r="Q40" s="8" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>19.8</v>
@@ -3895,7 +3772,7 @@
         <v>22.3</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>89.7</v>
+        <v>189.7</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>2.6</v>
@@ -3904,16 +3781,16 @@
         <v>21.3</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X40" s="3" t="n">
-        <v>21.2</v>
+        <v>19.6</v>
+      </c>
+      <c r="X40" s="8" t="n">
+        <v>21.7</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>81.3</v>
+        <v>85.5</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3929,40 +3806,40 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>48.8</v>
+        <v>1448.8</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>29.4</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="F41" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F41" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>9.9</v>
+        <v>19.9</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>12.4</v>
+        <v>17.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>3.1</v>
+        <v>13</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="L41" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L41" s="8" t="n">
         <v>19.9</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>10.8</v>
+        <v>20.8</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>89.09999999999999</v>
@@ -3973,32 +3850,32 @@
       <c r="Q41" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>58.4</v>
+        <v>584.5</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>16.1</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>28.5</v>
+        <v>4.6</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
+      </c>
+      <c r="X41" s="8" t="n">
+        <v>25.2</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>0.1</v>
+        <v>174</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>2.6</v>
+        <v>19.6</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4013,81 +3890,77 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">442
-2 6
-</t>
-        </is>
+      <c r="C42" s="3" t="n">
+        <v>464.3</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>33.1</v>
+        <v>32.8</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G42" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>924.9</v>
+      </c>
+      <c r="G42" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>25.6</v>
+        <v>15.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>4.4</v>
+        <v>14.4</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>5.8</v>
+        <v>20.1</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>12.2</v>
+        <v>2.8</v>
+      </c>
+      <c r="L42" s="8" t="n">
+        <v>72.8</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>16.1</v>
+        <v>16.8</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>12.6</v>
+        <v>17.6</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>89</v>
+        <v>289</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>2.1</v>
+        <v>12.1</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>24.7</v>
+        <v>30.8</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="S42" s="3" t="n">
-        <v>25.4</v>
+        <v>22.6</v>
+      </c>
+      <c r="S42" s="8" t="n">
+        <v>22.2</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>5.2</v>
+        <v>130</v>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v>22.2</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>63.2</v>
+        <v>27.5</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>21.4</v>
+        <v>23.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>24.4</v>
+        <v>0.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>6.1</v>
+        <v>3.7</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4103,25 +3976,25 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>341.3</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>18.6</v>
+        <v>2341.3</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>88.59999999999999</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>15.3</v>
+        <v>25.3</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="H43" s="3" t="n">
+      <c r="H43" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>2.2</v>
+        <v>24.9</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>2.8</v>
@@ -4142,37 +4015,37 @@
         <v>88.09999999999999</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="R43" s="3" t="n">
-        <v>66.3</v>
+        <v>12.5</v>
+      </c>
+      <c r="Q43" s="8" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="R43" s="8" t="n">
+        <v>22.3</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>12.3</v>
+        <v>25.4</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>21.1</v>
+        <v>181.4</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>61.1</v>
+        <v>15.7</v>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="W43" s="8" t="n">
+        <v>791.4</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>0.8</v>
+        <v>182.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>4.6</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4190,14 +4063,14 @@
       <c r="C44" s="3" t="n">
         <v>141.6</v>
       </c>
-      <c r="D44" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>19.8</v>
+      <c r="D44" s="8" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>21.5</v>
+        <v>44.5</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>4.9</v>
@@ -4206,59 +4079,53 @@
         <v>18.6</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>82.8</v>
+        <v>10.8</v>
       </c>
       <c r="J44" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>19.7</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.1</v>
+        <v>19.4</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>19.5</v>
+        <v>1.4</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>20.1</v>
+        <v>6.5</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>89</v>
+        <v>390.1</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>3.3</v>
+        <v>12.4</v>
+      </c>
+      <c r="Q44" s="8" t="n">
+        <v>28.6</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>2.2</v>
+        <v>20.3</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>22.9</v>
+        <v>22.3</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>7</v>
+        <v>181</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v>33.5</v>
+        <v>15.1</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>22.3</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y44" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="Z44" s="3" t="n">
-        <v>73.8</v>
-      </c>
+        <v>20.2</v>
+      </c>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4272,79 +4139,59 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="10" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="F45" s="10" t="n">
-        <v>77.7</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>12.6</v>
-      </c>
+      <c r="C45" s="3" t="n">
+        <v>16871.1</v>
+      </c>
+      <c r="D45" s="10" t="inlineStr"/>
+      <c r="E45" s="10" t="inlineStr"/>
+      <c r="F45" s="10" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr"/>
       <c r="I45" s="3" t="n">
-        <v>13.3</v>
+        <v>123.3</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>165.6</v>
+        <v>116.6</v>
       </c>
       <c r="K45" s="3" t="n">
         <v>30</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>1825.6</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>67.7</v>
-      </c>
+        <v>110.4</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>37.2</v>
+        <v>10234.2</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>2.4</v>
+        <v>1167.4</v>
       </c>
       <c r="Q45" s="3" t="n">
+        <v>1691.2</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>129.7</v>
+      </c>
+      <c r="S45" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="R45" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v>22.9</v>
-      </c>
       <c r="T45" s="3" t="n">
-        <v>69</v>
+        <v>4084.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="V45" s="3" t="n">
-        <v>242.4</v>
-      </c>
-      <c r="W45" s="3" t="n">
-        <v>21.8</v>
-      </c>
+        <v>112.2</v>
+      </c>
+      <c r="V45" s="3" t="inlineStr"/>
+      <c r="W45" s="3" t="inlineStr"/>
       <c r="X45" s="3" t="n">
-        <v>124.2</v>
-      </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6 7
-57
-</t>
-        </is>
+        <v>184832438.2</v>
+      </c>
+      <c r="Y45" s="3" t="n">
+        <v>81.5</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>5.8</v>
+        <v>15.8</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4360,43 +4207,38 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="D46" s="10" t="n">
+        <v>311.7</v>
+      </c>
+      <c r="D46" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="E46" s="10" t="n">
+      <c r="E46" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="F46" s="10" t="n">
-        <v>48</v>
+      <c r="F46" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="H46" s="3" t="n">
-        <v>1.1</v>
+      <c r="H46" s="8" t="n">
+        <v>67.59999999999999</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>1.8</v>
-      </c>
+        <v>12.8</v>
+      </c>
+      <c r="K46" s="3" t="inlineStr"/>
       <c r="L46" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="M46" s="8" t="n">
-        <v>825.6</v>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20 8
-</t>
-        </is>
+      <c r="M46" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>89</v>
@@ -4404,36 +4246,34 @@
       <c r="P46" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q46" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="S46" s="3" t="n"/>
+      <c r="Q46" s="8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="R46" s="8" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>22.9</v>
+      </c>
       <c r="T46" s="3" t="n">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="V46" s="8" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="W46" s="3" t="n"/>
-      <c r="X46" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6 7
-57
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="W46" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="Y46" s="3" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -47,14 +47,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -150,6 +156,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -763,62 +772,64 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>9437.5</v>
+        <v>83.7</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>31.2</v>
+        <v>18.2</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0.4</v>
+        <v>17.2</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>24.2</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>14.4</v>
+        <v>14</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>91241.10000000001</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.1</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="K4" s="3" t="inlineStr"/>
+        <v>4.2</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="L4" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="M4" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>82.5</v>
+        <v>178.5</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>187</v>
+        <v>87</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="R4" s="8" t="n">
+      <c r="R4" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="S4" s="8" t="n">
+      <c r="S4" s="3" t="n">
         <v>27</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>631.1</v>
+        <v>63.7</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>18.1</v>
+        <v>27.7</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24</v>
@@ -839,28 +850,28 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="8" t="n">
+      <c r="C5" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>21.5</v>
+        <v>13.5</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="8" t="n">
-        <v>87.40000000000001</v>
-      </c>
+      <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="n">
-        <v>25.8</v>
+        <v>9.6</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>19.1</v>
@@ -868,37 +879,41 @@
       <c r="M5" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="N5" s="8" t="n">
-        <v>19.9</v>
+      <c r="N5" s="3" t="n">
+        <v>89.90000000000001</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>190</v>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Q5" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="S5" s="8" t="n">
+      <c r="S5" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>187.8</v>
+        <v>87.8</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>12.9</v>
+        <v>2.7</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="n">
-        <v>27.5</v>
+      <c r="W5" s="8" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="X5" s="8" t="n">
+        <v>72.5</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>726.1</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>9.699999999999999</v>
@@ -917,9 +932,9 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>432.4</v>
-      </c>
-      <c r="D6" s="8" t="n">
+        <v>831.6</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>31.4</v>
       </c>
       <c r="E6" s="3" t="n">
@@ -931,60 +946,62 @@
       <c r="G6" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="J6" s="3" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="M6" s="8" t="n">
+      <c r="M6" s="3" t="n">
         <v>19</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>188.6</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="Q6" s="8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q6" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="R6" s="8" t="n">
-        <v>232.9</v>
+      <c r="R6" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>651.1</v>
+        <v>25.9</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>1608.9</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="V6" s="8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V6" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="W6" s="8" t="n">
+      <c r="W6" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>185</v>
+        <v>85</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>13.6</v>
+        <v>3.6</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1000,71 +1017,71 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1437.3</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0.8</v>
+        <v>143.7</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>1.5</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>251.1</v>
-      </c>
-      <c r="G7" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="G7" s="3" t="n">
         <v>15</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="I7" s="3" t="inlineStr"/>
+        <v>14.8</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="J7" s="3" t="n">
-        <v>14.9</v>
+        <v>4.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>13.1</v>
+        <v>0</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>12.3</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="N7" s="8" t="n">
-        <v>67.3</v>
+      <c r="N7" s="3" t="n">
+        <v>17.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>187.6</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>31.9</v>
+        <v>21.9</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="S7" s="8" t="n">
+      <c r="S7" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>2022.1</v>
+        <v>52.1</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="V7" s="8" t="n">
+      <c r="V7" s="3" t="n">
         <v>27.6</v>
       </c>
-      <c r="W7" s="8" t="n">
-        <v>24.1</v>
-      </c>
+      <c r="W7" s="3" t="inlineStr"/>
       <c r="X7" s="8" t="n">
-        <v>27.8</v>
+        <v>26.5</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>177.9</v>
+        <v>1772.9</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>17.5</v>
@@ -1083,15 +1100,15 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1297.2</v>
+        <v>98971.60000000001</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>32.6</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F8" s="8" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F8" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="G8" s="3" t="n">
@@ -1101,40 +1118,40 @@
         <v>17.2</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>16.9</v>
+        <v>1.9</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="K8" s="8" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="L8" s="8" t="n">
+      <c r="K8" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="L8" s="3" t="n">
         <v>20</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="N8" s="8" t="n">
+      <c r="N8" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>187.7</v>
+        <v>87.7</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="Q8" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q8" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R8" s="8" t="n">
+      <c r="R8" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="S8" s="8" t="n">
+      <c r="S8" s="3" t="n">
         <v>33.2</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>2524.1</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>11.6</v>
@@ -1145,15 +1162,13 @@
       <c r="W8" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X8" s="8" t="n">
+      <c r="X8" s="3" t="n">
         <v>27</v>
       </c>
       <c r="Y8" s="3" t="n">
         <v>90.2</v>
       </c>
-      <c r="Z8" s="3" t="n">
-        <v>2.9</v>
-      </c>
+      <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1168,64 +1183,74 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1666.5</v>
+        <v>166.6</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>852.6</v>
-      </c>
-      <c r="E9" s="10" t="inlineStr"/>
-      <c r="F9" s="10" t="inlineStr"/>
+        <v>1152.6</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>122.9</v>
+      </c>
       <c r="G9" s="3" t="n">
-        <v>681.1</v>
+        <v>8</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>80.5</v>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="n">
+        <v>211.2</v>
+      </c>
       <c r="J9" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>44.3</v>
+        <v>44</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>194.3</v>
+        <v>94.3</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>187.8</v>
+        <v>87.8</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>196.3</v>
+        <v>96.3</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1440.9</v>
+        <v>1840.9</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>162.9</v>
+        <v>12.9</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1138.8</v>
+        <v>138.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>1617.3</v>
+        <v>1217.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>132.9</v>
+        <v>1831.9</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>1360.9</v>
+        <v>360.9</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>58.5</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>1126.1</v>
-      </c>
-      <c r="W9" s="3" t="inlineStr"/>
+        <v>126.1</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>113</v>
+      </c>
       <c r="X9" s="3" t="inlineStr"/>
-      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Y9" s="3" t="n">
+        <v>11418.4</v>
+      </c>
       <c r="Z9" s="3" t="n">
-        <v>32.8</v>
+        <v>58.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1241,39 +1266,43 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>333.3</v>
+        <v>33.3</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>185.1</v>
-      </c>
-      <c r="F10" s="3" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F10" s="9" t="n">
         <v>24.5</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="H10" s="8" t="n">
-        <v>16.1</v>
+      <c r="H10" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2.2</v>
+        <v>15.2</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="8" t="n">
+      <c r="K10" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>87.59999999999999</v>
       </c>
-      <c r="N10" s="3" t="inlineStr"/>
+      <c r="N10" s="8" t="n">
+        <v>19.3</v>
+      </c>
       <c r="O10" s="3" t="n">
-        <v>188.2</v>
+        <v>88.5</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>2.6</v>
@@ -1281,29 +1310,29 @@
       <c r="Q10" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="R10" s="8" t="n">
+      <c r="R10" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="S10" s="8" t="n">
+      <c r="S10" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>272.2</v>
+        <v>72.2</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>11.7</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>0.5</v>
+        <v>25.2</v>
       </c>
       <c r="W10" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="X10" s="3" t="n">
+      <c r="X10" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>180.5</v>
+        <v>80.5</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>16.6</v>
@@ -1322,12 +1351,12 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1445</v>
-      </c>
-      <c r="D11" s="11" t="n">
+        <v>1445.1</v>
+      </c>
+      <c r="D11" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="F11" s="11" t="n">
@@ -1340,55 +1369,59 @@
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>13.3</v>
+        <v>3.9</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
+        <v>80.59999999999999</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>20.1</v>
+      </c>
       <c r="M11" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>20.7</v>
+        <v>46.7</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>187.9</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>41.9</v>
+        <v>27.9</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S11" s="8" t="n">
-        <v>981.9</v>
+        <v>230.8</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>31.9</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="V11" s="8" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="V11" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="W11" s="8" t="n">
-        <v>24.7</v>
+      <c r="W11" s="3" t="n">
+        <v>4.1</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>30.9</v>
+        <v>31.9</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>197.5</v>
-      </c>
-      <c r="Z11" s="3" t="inlineStr"/>
+        <v>97.5</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>10.8</v>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1403,34 +1436,34 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>383.6</v>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="E12" s="11" t="n">
+        <v>318.3</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="E12" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="F12" s="11" t="n">
         <v>23.9</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>18</v>
+        <v>8.5</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>81.09999999999999</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>12.9</v>
+        <v>2.9</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>20.6</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>19.3</v>
@@ -1442,10 +1475,10 @@
         <v>88.40000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="Q12" s="8" t="n">
-        <v>27.8</v>
+        <v>2.7</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>27.2</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>25.2</v>
@@ -1454,25 +1487,25 @@
         <v>30.8</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>8544.1</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="V12" s="8" t="n">
+      <c r="V12" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="W12" s="8" t="n">
-        <v>284.4</v>
-      </c>
-      <c r="X12" s="8" t="n">
+      <c r="W12" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X12" s="3" t="n">
         <v>30.4</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>197.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>10.8</v>
+        <v>19.7</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1488,12 +1521,12 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>39356.7</v>
-      </c>
-      <c r="D13" s="11" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="D13" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="F13" s="11" t="n">
@@ -1502,19 +1535,19 @@
       <c r="G13" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>12.6</v>
+        <v>0.1</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="L13" s="8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L13" s="3" t="n">
         <v>20</v>
       </c>
       <c r="M13" s="3" t="n">
@@ -1524,10 +1557,12 @@
         <v>20.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>189.1</v>
-      </c>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="8" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q13" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="R13" s="3" t="n">
@@ -1539,23 +1574,23 @@
       <c r="T13" s="3" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="U13" s="8" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="V13" s="8" t="n">
+      <c r="U13" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="V13" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="W13" s="8" t="n">
+      <c r="W13" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="X13" s="8" t="n">
         <v>28.9</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>197.7</v>
+        <v>192.9</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>10.7</v>
+        <v>2.2</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1571,12 +1606,12 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>13974</v>
-      </c>
-      <c r="D14" s="11" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="D14" s="8" t="n">
         <v>32.5</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="F14" s="11" t="n">
@@ -1586,29 +1621,31 @@
         <v>12.9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>1.3</v>
+      </c>
       <c r="K14" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="L14" s="8" t="n">
+      <c r="L14" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>189.9</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>30.6</v>
@@ -1617,7 +1654,7 @@
         <v>22.6</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>50.9</v>
@@ -1654,13 +1691,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>433.5</v>
-      </c>
-      <c r="D15" s="11" t="n">
+        <v>1643.3</v>
+      </c>
+      <c r="D15" s="3" t="n">
         <v>29.5</v>
       </c>
-      <c r="E15" s="11" t="n">
-        <v>20.8</v>
+      <c r="E15" s="10" t="n">
+        <v>2.8</v>
       </c>
       <c r="F15" s="11" t="n">
         <v>24.9</v>
@@ -1668,27 +1705,29 @@
       <c r="G15" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="H15" s="8" t="n">
+      <c r="H15" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1.9</v>
+        <v>11.9</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>10</v>
+        <v>0.8</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>20.4</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N15" s="3" t="inlineStr"/>
+        <v>19.1</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>21.3</v>
+      </c>
       <c r="O15" s="3" t="n">
-        <v>188.8</v>
+        <v>88.8</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>2.6</v>
@@ -1699,26 +1738,26 @@
       <c r="R15" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S15" s="8" t="n">
+      <c r="S15" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>163.8</v>
+        <v>63.8</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="V15" s="8" t="n">
+      <c r="V15" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="W15" s="8" t="n">
-        <v>241.1</v>
+      <c r="W15" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>174</v>
+        <v>1741</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>17.9</v>
@@ -1737,22 +1776,22 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>11992.8</v>
-      </c>
-      <c r="D16" s="11" t="n">
-        <v>149.9</v>
+        <v>199.2</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>1129.9</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>124.7</v>
+        <v>991.8</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>124.2</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>150.8</v>
+        <v>50.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>190.3</v>
+        <v>9</v>
       </c>
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="n">
@@ -1762,42 +1801,46 @@
         <v>16</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1100.9</v>
+        <v>460.9</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>194.6</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>105.2</v>
+        <v>1055.9</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>444.1</v>
+        <v>4464.1</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>12.9</v>
+        <v>102.9</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1142.8</v>
+        <v>142.8</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>123</v>
+        <v>1123</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>142.5</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>1368.7</v>
+        <v>368.7</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>533441.5</v>
+        <v>53.1</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>120.8</v>
       </c>
-      <c r="W16" s="3" t="inlineStr"/>
-      <c r="X16" s="3" t="inlineStr"/>
+      <c r="W16" s="3" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>137.5</v>
+      </c>
       <c r="Y16" s="3" t="n">
-        <v>1455.1</v>
+        <v>455.1</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>13.4</v>
@@ -1816,62 +1859,58 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="D17" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="E17" s="11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="E17" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="F17" s="9" t="n">
-        <v>224.9</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="F17" s="11" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="I17" s="8" t="n">
-        <v>81.2</v>
+      <c r="I17" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="8" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="M17" s="8" t="n">
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="N17" s="8" t="n">
-        <v>20</v>
+      <c r="N17" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>188.8</v>
+        <v>88.8</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q17" s="8" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="R17" s="3" t="n">
-        <v>946.4</v>
+      <c r="Q17" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="R17" s="8" t="n">
+        <v>82</v>
       </c>
       <c r="S17" s="8" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>173.7</v>
+        <v>23.7</v>
       </c>
       <c r="U17" s="8" t="n">
         <v>10.6</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>24.2</v>
+        <v>48.2</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>23</v>
@@ -1899,56 +1938,56 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>437.5</v>
-      </c>
-      <c r="D18" s="11" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E18" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F18" s="11" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="8" t="n">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="I18" s="8" t="n">
-        <v>39.5</v>
+        <v>0.1</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>91</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>84.41</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>18</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>19.2</v>
+        <v>9.6</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>12.7</v>
+        <v>27.7</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>19.3</v>
+        <v>1.9</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>187</v>
-      </c>
-      <c r="P18" s="8" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="Q18" s="8" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="Q18" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S18" s="8" t="n">
+      <c r="S18" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>163.1</v>
+        <v>6.2</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>14.4</v>
@@ -1956,11 +1995,11 @@
       <c r="V18" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="W18" s="8" t="n">
+      <c r="W18" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="X18" s="3" t="n">
-        <v>31</v>
+      <c r="X18" s="8" t="n">
+        <v>11.3</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>92.09999999999999</v>
@@ -1982,77 +2021,75 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1423.9</v>
-      </c>
-      <c r="D19" s="11" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="E19" s="11" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E19" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="G19" s="8" t="n">
-        <v>124.8</v>
+      <c r="G19" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16.1</v>
+        <v>11.6</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>13.5</v>
+        <v>3.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>28.5</v>
+        <v>91.5</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>20</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>2.3</v>
+        <v>87.5</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="Q19" s="3" t="n">
-        <v>31.8</v>
+        <v>2.8</v>
+      </c>
+      <c r="Q19" s="8" t="n">
+        <v>61.8</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="S19" s="3" t="n">
-        <v>25.3</v>
+        <v>94.2</v>
+      </c>
+      <c r="S19" s="8" t="n">
+        <v>295.3</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>62.1</v>
+        <v>54</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="V19" s="8" t="n">
-        <v>25.8</v>
+        <v>655.8</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="X19" s="8" t="n">
+      <c r="X19" s="3" t="n">
         <v>27</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>181.2</v>
-      </c>
-      <c r="Z19" s="3" t="n">
-        <v>16.2</v>
-      </c>
+        <v>81.8</v>
+      </c>
+      <c r="Z19" s="3" t="inlineStr"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -2067,39 +2104,37 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>256.8</v>
-      </c>
-      <c r="D20" s="11" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="E20" s="11" t="n">
+        <v>856.8</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="E20" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F20" s="11" t="n">
-        <v>23.5</v>
+      <c r="F20" s="3" t="n">
+        <v>25.5</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="H20" s="8" t="n">
-        <v>82.2</v>
+      <c r="H20" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K20" s="8" t="n">
-        <v>2408</v>
-      </c>
-      <c r="L20" s="8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M20" s="8" t="n">
+      <c r="M20" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N20" s="8" t="n">
+      <c r="N20" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="O20" s="3" t="n">
@@ -2109,31 +2144,31 @@
         <v>12.5</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R20" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R20" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>70.7</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>19.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="W20" s="8" t="n">
+      <c r="W20" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>167.2</v>
+        <v>67.2</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>10.2</v>
@@ -2152,44 +2187,48 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1433.5</v>
-      </c>
-      <c r="D21" s="11" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="D21" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>17.7</v>
+        <v>1.7</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="L21" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>1.4</v>
+        <v>12.3</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>186.7</v>
-      </c>
-      <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="8" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q21" s="3" t="n">
         <v>30.1</v>
       </c>
       <c r="R21" s="3" t="n">
@@ -2199,16 +2238,16 @@
         <v>21.7</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>151</v>
+        <v>51</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="V21" s="8" t="n">
+      <c r="V21" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>2.2</v>
+        <v>22.4</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>25.9</v>
@@ -2233,28 +2272,26 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>374</v>
-      </c>
-      <c r="D22" s="11" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="D22" s="3" t="n">
         <v>31.8</v>
       </c>
-      <c r="E22" s="11" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F22" s="11" t="n">
+      <c r="E22" s="12" t="inlineStr"/>
+      <c r="F22" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="G22" s="3" t="n">
+      <c r="G22" s="8" t="n">
         <v>14.6</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="I22" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I22" s="8" t="n">
         <v>21.1</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>3.7</v>
@@ -2269,10 +2306,10 @@
         <v>17.5</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>187</v>
-      </c>
-      <c r="P22" s="8" t="n">
-        <v>21.6</v>
+        <v>87</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>2.6</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>30.2</v>
@@ -2280,29 +2317,29 @@
       <c r="R22" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="S22" s="8" t="n">
+      <c r="S22" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>156.4</v>
+        <v>56.4</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="V22" s="8" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="W22" s="3" t="n">
-        <v>19.5</v>
+      <c r="V22" s="3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W22" s="8" t="n">
+        <v>93.5</v>
       </c>
       <c r="X22" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>185.5</v>
+        <v>85.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2320,17 +2357,17 @@
       <c r="C23" s="3" t="n">
         <v>1925.5</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="9" t="n">
         <v>153.1</v>
       </c>
-      <c r="E23" s="11" t="n">
-        <v>92.8</v>
+      <c r="E23" s="9" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1123</v>
+        <v>123</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>160.3</v>
+        <v>16027.4</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>85.59999999999999</v>
@@ -2339,44 +2376,52 @@
         <v>11.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>135.5</v>
+        <v>15.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>49.9</v>
+        <v>49.5</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>195.2</v>
+        <v>95.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1882.8</v>
+        <v>88.2</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>196.5</v>
+        <v>96.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1437.2</v>
+        <v>1137.2</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="Q23" s="3" t="inlineStr"/>
-      <c r="R23" s="3" t="inlineStr"/>
+        <v>1535.7</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>146.2</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>1145.1</v>
+      </c>
       <c r="S23" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>1295.2</v>
+        <v>295.2</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>85.2</v>
       </c>
-      <c r="V23" s="3" t="inlineStr"/>
-      <c r="W23" s="3" t="inlineStr"/>
+      <c r="V23" s="3" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="W23" s="3" t="n">
+        <v>210.7</v>
+      </c>
       <c r="X23" s="3" t="n">
-        <v>1126.7</v>
+        <v>226.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>1411</v>
+        <v>1811</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>27.1</v>
@@ -2395,44 +2440,48 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>385.1</v>
-      </c>
-      <c r="D24" s="11" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E24" s="11" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="E24" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="F24" s="11" t="n">
-        <v>24.6</v>
+      <c r="F24" s="9" t="n">
+        <v>84.59999999999999</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>87.40000000000001</v>
+        <v>12.9</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>11.2</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
+        <v>5.1</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="N24" s="8" t="n">
-        <v>19.5</v>
+      <c r="N24" s="3" t="n">
+        <v>29.3</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>187.4</v>
-      </c>
-      <c r="P24" s="3" t="inlineStr"/>
-      <c r="Q24" s="8" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="Q24" s="3" t="n">
         <v>29.2</v>
       </c>
       <c r="R24" s="3" t="n">
@@ -2442,23 +2491,21 @@
         <v>23.8</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>159</v>
+        <v>59</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="V24" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="V24" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="X24" s="8" t="n">
+      <c r="X24" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="Y24" s="3" t="n">
-        <v>182.2</v>
-      </c>
+      <c r="Y24" s="3" t="inlineStr"/>
       <c r="Z24" s="3" t="n">
         <v>5.4</v>
       </c>
@@ -2476,74 +2523,76 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1374</v>
-      </c>
-      <c r="D25" s="11" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>25.7</v>
+        <v>374</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>9.1</v>
+        <v>12.8</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="K25" s="3" t="inlineStr"/>
+        <v>3.6</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>81414.60000000001</v>
+      </c>
       <c r="L25" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="M25" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="N25" s="8" t="n">
+      <c r="N25" s="3" t="n">
         <v>20.4</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q25" s="8" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="Q25" s="3" t="n">
         <v>31.3</v>
       </c>
-      <c r="R25" s="3" t="n">
-        <v>243.1</v>
-      </c>
-      <c r="S25" s="8" t="n">
+      <c r="R25" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S25" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>956.9</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U25" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="V25" s="8" t="n">
-        <v>224.2</v>
-      </c>
-      <c r="W25" s="8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="W25" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="X25" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>1747.6</v>
+        <v>174.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>7.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2559,46 +2608,46 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>329.8</v>
-      </c>
-      <c r="D26" s="11" t="n">
+        <v>329.2</v>
+      </c>
+      <c r="D26" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E26" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="F26" s="11" t="n">
+      <c r="F26" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="H26" s="8" t="n">
-        <v>72</v>
-      </c>
-      <c r="I26" s="8" t="n">
-        <v>11.9</v>
+      <c r="H26" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>1.9</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>10.3</v>
+        <v>0.3</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>19</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="N26" s="8" t="n">
-        <v>949.2</v>
+        <v>17.6</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>187</v>
+        <v>87</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>24.4</v>
@@ -2610,23 +2659,21 @@
         <v>24.5</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="V26" s="8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="V26" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="X26" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="X26" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="Y26" s="3" t="n">
-        <v>181.1</v>
-      </c>
+      <c r="Y26" s="3" t="inlineStr"/>
       <c r="Z26" s="3" t="n">
         <v>17.6</v>
       </c>
@@ -2644,16 +2691,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D27" s="11" t="n">
+        <v>952.2</v>
+      </c>
+      <c r="D27" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="E27" s="11" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>23.8</v>
+      <c r="E27" s="10" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>18.8</v>
@@ -2661,50 +2708,52 @@
       <c r="H27" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="8" t="n">
-        <v>21.9</v>
+      <c r="I27" s="3" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>2.9</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="L27" s="8" t="n">
+      <c r="L27" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N27" s="8" t="n">
+      <c r="N27" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>187.5</v>
+        <v>82.5</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="Q27" s="8" t="n">
-        <v>6</v>
+        <v>2.9</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>26</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>21.6</v>
+        <v>22.6</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>23</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>168.4</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v>23.2</v>
+        <v>68.40000000000001</v>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="W27" s="8" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X27" s="8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="X27" s="3" t="n">
         <v>23</v>
       </c>
       <c r="Y27" s="3" t="n">
@@ -2727,31 +2776,31 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>9389.299999999999</v>
-      </c>
-      <c r="D28" s="11" t="n">
+        <v>288.9</v>
+      </c>
+      <c r="D28" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="E28" s="11" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F28" s="11" t="n">
+      <c r="E28" s="10" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="F28" s="3" t="n">
         <v>25</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="H28" s="8" t="n">
+      <c r="H28" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K28" s="3" t="n">
         <v>19</v>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J28" s="8" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>19.6</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>20.6</v>
@@ -2760,40 +2809,40 @@
         <v>19.2</v>
       </c>
       <c r="N28" s="8" t="n">
-        <v>21.3</v>
+        <v>281.3</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>187.4</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>2.9</v>
+        <v>11.4</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="R28" s="8" t="n">
+      <c r="R28" s="3" t="n">
         <v>23</v>
       </c>
       <c r="S28" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>164.9</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="V28" s="8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="V28" s="3" t="n">
         <v>26</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>23.6</v>
+        <v>55.6</v>
       </c>
       <c r="X28" s="8" t="n">
         <v>27.6</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>82</v>
+        <v>182</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>16</v>
@@ -2812,16 +2861,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>408.5</v>
-      </c>
-      <c r="D29" s="11" t="n">
+        <v>140.8</v>
+      </c>
+      <c r="D29" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="E29" s="11" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F29" s="11" t="n">
-        <v>24.9</v>
+      <c r="E29" s="10" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>22.9</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>19.1</v>
@@ -2830,7 +2879,7 @@
         <v>20.1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>16.7</v>
+        <v>11.7</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2.9</v>
@@ -2844,23 +2893,23 @@
       <c r="M29" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="N29" s="8" t="n">
+      <c r="N29" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="Q29" s="8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q29" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="S29" s="8" t="n">
-        <v>226.5</v>
+      <c r="S29" s="3" t="n">
+        <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>162.6</v>
@@ -2868,17 +2917,17 @@
       <c r="U29" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="V29" s="8" t="n">
+      <c r="V29" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="X29" s="3" t="n">
+      <c r="X29" s="8" t="n">
         <v>26.5</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>8182.8</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>16.1</v>
@@ -2897,22 +2946,22 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1856.4</v>
-      </c>
-      <c r="D30" s="11" t="n">
-        <v>150.3</v>
-      </c>
-      <c r="E30" s="11" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="F30" s="11" t="n">
-        <v>124.1</v>
+        <v>11836.4</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>150.5</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>1224.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>152.5</v>
+        <v>52.5</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>191.9</v>
+        <v>9.1</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>180</v>
@@ -2921,49 +2970,49 @@
         <v>15.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>125.4</v>
+        <v>25.4</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>199.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>93.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>1103.2</v>
+        <v>9103.4</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>1441.9</v>
+        <v>14241.9</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>13.1</v>
+        <v>10.1</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>1138.5</v>
+        <v>138.5</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>1113.7</v>
+        <v>113.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>122.8</v>
+        <v>122.7</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>1332.8</v>
+        <v>332.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>164.5</v>
+        <v>16.4</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1823.1</v>
+        <v>1123.1</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>110.1</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>1124.3</v>
+        <v>164.3</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>1399.8</v>
+        <v>39.4</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>32.6</v>
@@ -2982,22 +3031,22 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>383.1</v>
-      </c>
-      <c r="D31" s="11" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="E31" s="11" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="E31" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="F31" s="11" t="n">
-        <v>24.8</v>
+      <c r="F31" s="9" t="n">
+        <v>94.8</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>184.5</v>
+        <v>10.5</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>182.4</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2</v>
@@ -3005,52 +3054,52 @@
       <c r="J31" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="n">
+      <c r="K31" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L31" s="8" t="n">
         <v>19.9</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>6.4</v>
+        <v>20.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>188.4</v>
+        <v>22.4</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="Q31" s="8" t="n">
+      <c r="Q31" s="3" t="n">
         <v>27.7</v>
       </c>
       <c r="R31" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="S31" s="8" t="n">
-        <v>24.5</v>
+      <c r="S31" s="3" t="n">
+        <v>845.8</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>166.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="V31" s="8" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V31" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="W31" s="8" t="n">
+      <c r="W31" s="3" t="n">
         <v>22</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="Z31" s="3" t="n">
-        <v>6.5</v>
-      </c>
+        <v>80.90000000000001</v>
+      </c>
+      <c r="Z31" s="3" t="inlineStr"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3065,72 +3114,76 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>437.3</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="E32" s="8" t="n">
+        <v>943.7</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="E32" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>865.1</v>
-      </c>
-      <c r="G32" s="3" t="inlineStr"/>
+        <v>26.9</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>12.6</v>
+      </c>
       <c r="H32" s="3" t="n">
-        <v>18.5</v>
+        <v>18.2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>13.5</v>
+        <v>3.9</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>14.4</v>
+        <v>4.4</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="N32" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="N32" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>188.4</v>
-      </c>
-      <c r="P32" s="3" t="inlineStr"/>
+        <v>88.40000000000001</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="Q32" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="3" t="n">
         <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>156.6</v>
+        <v>560.6</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="V32" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W32" s="3" t="n">
-        <v>23.7</v>
+        <v>1.9</v>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="W32" s="8" t="n">
+        <v>128.8</v>
       </c>
       <c r="X32" s="8" t="n">
         <v>26.4</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>169.1</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>1118.8</v>
+        <v>11.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3146,38 +3199,40 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1397</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E33" s="8" t="n">
+        <v>397.1</v>
+      </c>
+      <c r="D33" s="10" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="E33" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>26.7</v>
+      <c r="F33" s="10" t="n">
+        <v>65.7</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>34.1</v>
+        <v>13.9</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>17.9</v>
+        <v>12.9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr"/>
-      <c r="K33" s="3" t="n">
-        <v>10</v>
+        <v>11.4</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K33" s="8" t="n">
+        <v>1.1</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>49.5</v>
+        <v>19.5</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>26.7</v>
+        <v>21.7</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>87.40000000000001</v>
@@ -3185,32 +3240,32 @@
       <c r="P33" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q33" s="8" t="n">
+      <c r="Q33" s="3" t="n">
         <v>32.9</v>
       </c>
       <c r="R33" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="S33" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="S33" s="3" t="n">
-        <v>63.4</v>
-      </c>
       <c r="T33" s="3" t="n">
-        <v>1947.7</v>
-      </c>
-      <c r="U33" s="8" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="U33" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="V33" s="8" t="n">
+      <c r="V33" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="W33" s="8" t="n">
+      <c r="W33" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>127.6</v>
+        <v>122.6</v>
       </c>
       <c r="Z33" s="3" t="n">
         <v>17.4</v>
@@ -3229,10 +3284,10 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>362.4</v>
+        <v>36.2</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>30.4</v>
+        <v>10.4</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>20.2</v>
@@ -3240,20 +3295,20 @@
       <c r="F34" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="G34" s="8" t="n">
         <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="K34" s="3" t="n">
-        <v>4.2</v>
+      <c r="K34" s="8" t="n">
+        <v>2.4</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>20.4</v>
@@ -3265,26 +3320,28 @@
         <v>21</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>187.3</v>
-      </c>
-      <c r="P34" s="3" t="inlineStr"/>
+        <v>87.3</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>2.9</v>
+      </c>
       <c r="Q34" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="S34" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="S34" s="3" t="n">
         <v>26.6</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>7886.8</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>17.2</v>
+        <v>7.5</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>55.4</v>
+        <v>25.5</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>23.3</v>
@@ -3293,10 +3350,10 @@
         <v>27.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>183.2</v>
+        <v>1832.8</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>15.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3314,74 +3371,74 @@
       <c r="C35" s="3" t="n">
         <v>187.9</v>
       </c>
-      <c r="D35" s="8" t="n">
+      <c r="D35" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="E35" s="8" t="n">
+      <c r="E35" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="F35" s="8" t="n">
+      <c r="F35" s="3" t="n">
         <v>22.7</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>23.9</v>
+        <v>3.9</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>18.7</v>
+        <v>1.8</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>10.3</v>
+        <v>0.3</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="L35" s="8" t="n">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="N35" s="8" t="n">
-        <v>9.300000000000001</v>
+      <c r="N35" s="3" t="n">
+        <v>21.3</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>854.1</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Q35" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q35" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="S35" s="8" t="n">
+      <c r="S35" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>88.5</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V35" s="8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="V35" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="X35" s="8" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="X35" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>188.5</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>2.9</v>
+        <v>12.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3399,11 +3456,11 @@
       <c r="C36" s="3" t="n">
         <v>398.9</v>
       </c>
-      <c r="D36" s="8" t="n">
+      <c r="D36" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="E36" s="8" t="n">
-        <v>20</v>
+      <c r="E36" s="10" t="n">
+        <v>10.01</v>
       </c>
       <c r="F36" s="8" t="n">
         <v>24.3</v>
@@ -3418,10 +3475,10 @@
         <v>2.2</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>20.6</v>
@@ -3429,45 +3486,43 @@
       <c r="M36" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="N36" s="8" t="n">
+      <c r="N36" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>189</v>
+        <v>89</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q36" s="8" t="n">
+      <c r="Q36" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="R36" s="8" t="n">
+      <c r="R36" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S36" s="8" t="n">
-        <v>593.8</v>
+      <c r="S36" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>72.3</v>
+        <v>822.5</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="V36" s="8" t="n">
-        <v>5</v>
+        <v>95.8</v>
       </c>
       <c r="W36" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>24.8</v>
+        <v>46.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>178.2</v>
-      </c>
-      <c r="Z36" s="3" t="n">
-        <v>16.9</v>
-      </c>
+        <v>78.2</v>
+      </c>
+      <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3484,14 +3539,20 @@
       <c r="C37" s="3" t="n">
         <v>11683.5</v>
       </c>
-      <c r="D37" s="10" t="inlineStr"/>
-      <c r="E37" s="10" t="inlineStr"/>
-      <c r="F37" s="10" t="inlineStr"/>
+      <c r="D37" s="9" t="n">
+        <v>1450.1</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>125.5</v>
+      </c>
       <c r="G37" s="3" t="n">
         <v>49.2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>192.4</v>
+        <v>9224.1</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>12.6</v>
@@ -3500,44 +3561,52 @@
         <v>15.7</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>160.8</v>
+        <v>10.2</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>103.5</v>
       </c>
-      <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr"/>
+      <c r="M37" s="3" t="n">
+        <v>1396.5</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>127.2</v>
+      </c>
       <c r="O37" s="3" t="n">
-        <v>1432.5</v>
+        <v>437.5</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>139.6</v>
+        <v>129</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>115.4</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>126.8</v>
+        <v>126</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>3431.1</v>
+        <v>343.7</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>165.7</v>
+        <v>65.7</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>126.1</v>
       </c>
-      <c r="W37" s="3" t="inlineStr"/>
-      <c r="X37" s="3" t="inlineStr"/>
+      <c r="W37" s="3" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="X37" s="3" t="n">
+        <v>127.1</v>
+      </c>
       <c r="Y37" s="3" t="n">
         <v>396.6</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>342.4</v>
+        <v>34.4</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3555,28 +3624,30 @@
       <c r="C38" s="3" t="n">
         <v>336.7</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="D38" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>5.4</v>
+      <c r="F38" s="9" t="n">
+        <v>25.1</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>18.5</v>
+        <v>88.5</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J38" s="8" t="n">
-        <v>211.1</v>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
       </c>
@@ -3584,13 +3655,13 @@
         <v>19.3</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>21.4</v>
+        <v>28.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>187.5</v>
+        <v>87.5</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>27.9</v>
@@ -3598,29 +3669,29 @@
       <c r="R38" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S38" s="8" t="n">
-        <v>25.2</v>
+      <c r="S38" s="3" t="n">
+        <v>23.2</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>168.7</v>
+        <v>68.7</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>18.1</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>22.4</v>
+        <v>224.2</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>79.3</v>
+        <v>179.3</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>18.9</v>
+        <v>16.9</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3636,76 +3707,74 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1400.8</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E39" s="8" t="n">
+        <v>14001.8</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E39" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="F39" s="3" t="n">
+      <c r="F39" s="11" t="n">
         <v>25.7</v>
       </c>
-      <c r="G39" s="3" t="n">
-        <v>12.3</v>
+      <c r="G39" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="I39" s="3" t="n">
-        <v>52.5</v>
-      </c>
+      <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="n">
-        <v>3.9</v>
+        <v>29.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>20.5</v>
+        <v>0</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>10.5</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N39" s="8" t="n">
-        <v>22</v>
+      <c r="N39" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="P39" s="8" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="Q39" s="8" t="n">
+      <c r="P39" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q39" s="3" t="n">
         <v>30.4</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>23.1</v>
+        <v>25.1</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>345.1</v>
+        <v>534.5</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="V39" s="8" t="n">
+      <c r="V39" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="W39" s="8" t="n">
+      <c r="W39" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X39" s="8" t="n">
-        <v>27.6</v>
+      <c r="X39" s="3" t="n">
+        <v>97.59999999999999</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>175.4</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>17.6</v>
+        <v>13.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3723,29 +3792,29 @@
       <c r="C40" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="D40" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F40" s="3" t="n">
+      <c r="D40" s="10" t="n">
+        <v>44.46</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="F40" s="11" t="n">
         <v>22.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H40" s="8" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="H40" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>10.5</v>
+        <v>0.5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>14.9</v>
+        <v>4.9</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>20.4</v>
@@ -3753,16 +3822,16 @@
       <c r="M40" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="N40" s="8" t="n">
-        <v>10.1</v>
+      <c r="N40" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>88</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="Q40" s="8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q40" s="3" t="n">
         <v>21</v>
       </c>
       <c r="R40" s="3" t="n">
@@ -3772,25 +3841,25 @@
         <v>22.3</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>189.7</v>
+        <v>89.7</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="W40" s="3" t="n">
-        <v>19.6</v>
+        <v>28.3</v>
+      </c>
+      <c r="W40" s="8" t="n">
+        <v>90.59999999999999</v>
       </c>
       <c r="X40" s="8" t="n">
-        <v>21.7</v>
+        <v>217.2</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>85.5</v>
+        <v>181.5</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>5.7</v>
+        <v>19.9</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3806,33 +3875,33 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1448.8</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>29.4</v>
+        <v>114.8</v>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>49.43</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="F41" s="8" t="n">
+      <c r="F41" s="11" t="n">
         <v>24.5</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="H41" s="3" t="n">
+      <c r="H41" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L41" s="8" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="K41" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="L41" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="M41" s="3" t="n">
@@ -3850,26 +3919,26 @@
       <c r="Q41" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="R41" s="8" t="n">
+      <c r="R41" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>584.5</v>
+        <v>58.4</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>16.1</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>4.6</v>
+        <v>24.6</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="X41" s="8" t="n">
-        <v>25.2</v>
+        <v>25.8</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>174</v>
@@ -3891,43 +3960,43 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>464.3</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>32.8</v>
+        <v>86.2</v>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>98.8</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F42" s="8" t="n">
-        <v>924.9</v>
-      </c>
-      <c r="G42" s="8" t="n">
+      <c r="F42" s="11" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G42" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>15.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>14.4</v>
+        <v>4.4</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>20.1</v>
+        <v>0.8</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L42" s="8" t="n">
-        <v>72.8</v>
+        <v>0.2</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>16.8</v>
+        <v>16.1</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>289</v>
+        <v>89</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>12.1</v>
@@ -3938,29 +4007,29 @@
       <c r="R42" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="S42" s="8" t="n">
+      <c r="S42" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="U42" s="8" t="n">
-        <v>22.2</v>
+        <v>28.2</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X42" s="3" t="n">
-        <v>0.2</v>
+        <v>25.8</v>
+      </c>
+      <c r="X42" s="8" t="n">
+        <v>10.4</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>87</v>
+        <v>18708</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>3.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3976,28 +4045,28 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>2341.3</v>
-      </c>
-      <c r="D43" s="8" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="D43" s="3" t="n">
         <v>32</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="F43" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F43" s="11" t="n">
         <v>25.3</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="H43" s="8" t="n">
+      <c r="H43" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>24.9</v>
+        <v>2.2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="K43" s="3" t="n">
         <v>15.2</v>
@@ -4015,37 +4084,35 @@
         <v>88.09999999999999</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Q43" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q43" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="8" t="n">
+      <c r="R43" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="S43" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>181.4</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="V43" s="8" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="U43" s="3" t="inlineStr"/>
+      <c r="V43" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="W43" s="8" t="n">
-        <v>791.4</v>
+      <c r="W43" s="3" t="n">
+        <v>22.4</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="Y43" s="3" t="n">
         <v>182.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>14.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4061,16 +4128,16 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>141.6</v>
-      </c>
-      <c r="D44" s="8" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="D44" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="E44" s="8" t="n">
+      <c r="E44" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>44.5</v>
+      <c r="F44" s="11" t="n">
+        <v>21.5</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>4.9</v>
@@ -4078,8 +4145,8 @@
       <c r="H44" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="I44" s="3" t="n">
-        <v>10.8</v>
+      <c r="I44" s="8" t="n">
+        <v>80.8</v>
       </c>
       <c r="J44" s="3" t="n">
         <v>0.6</v>
@@ -4091,34 +4158,34 @@
         <v>19.4</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>6.5</v>
+        <v>19.9</v>
+      </c>
+      <c r="N44" s="8" t="n">
+        <v>0.8</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>390.1</v>
+        <v>189</v>
       </c>
       <c r="P44" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="Q44" s="8" t="n">
-        <v>28.6</v>
+      <c r="Q44" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="S44" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>181</v>
+        <v>181.9</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>22.3</v>
+        <v>15.9</v>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v>822.3</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>20.2</v>
@@ -4140,52 +4207,66 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>16871.1</v>
-      </c>
-      <c r="D45" s="10" t="inlineStr"/>
-      <c r="E45" s="10" t="inlineStr"/>
-      <c r="F45" s="10" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="3" t="inlineStr"/>
+        <v>18841.1</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>841.1</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>174</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>160.2</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>105.6</v>
+      </c>
       <c r="I45" s="3" t="n">
-        <v>123.3</v>
+        <v>169</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>116.6</v>
+        <v>16.6</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>30</v>
+        <v>2816.1</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>110.4</v>
+        <v>12180.4</v>
       </c>
       <c r="M45" s="3" t="inlineStr"/>
-      <c r="N45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="n">
+        <v>110109210619.1</v>
+      </c>
       <c r="O45" s="3" t="n">
-        <v>10234.2</v>
+        <v>204.1</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>1167.4</v>
+        <v>16808.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1691.2</v>
+        <v>1257.2</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>129.7</v>
+        <v>1291.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>26.2</v>
+        <v>18317.9</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>4084.4</v>
+        <v>44841.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>112.2</v>
+        <v>81.5</v>
       </c>
       <c r="V45" s="3" t="inlineStr"/>
-      <c r="W45" s="3" t="inlineStr"/>
+      <c r="W45" s="3" t="n">
+        <v>1122.2</v>
+      </c>
       <c r="X45" s="3" t="n">
-        <v>184832438.2</v>
+        <v>924.7</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>81.5</v>
@@ -4207,30 +4288,32 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>311.7</v>
-      </c>
-      <c r="D46" s="8" t="n">
+        <v>511.7</v>
+      </c>
+      <c r="D46" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="E46" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="F46" s="8" t="n">
+      <c r="F46" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="G46" s="3" t="n">
-        <v>10.1</v>
+      <c r="G46" s="8" t="n">
+        <v>20.1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>2.2</v>
+        <v>17.6</v>
+      </c>
+      <c r="I46" s="8" t="n">
+        <v>122.6</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="K46" s="3" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="L46" s="3" t="n">
         <v>19.4</v>
       </c>
@@ -4238,7 +4321,7 @@
         <v>18.2</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>20.2</v>
+        <v>60.5</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>89</v>
@@ -4246,33 +4329,31 @@
       <c r="P46" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q46" s="8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="R46" s="8" t="n">
+      <c r="Q46" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R46" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>169</v>
+        <v>69</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="V46" s="8" t="n">
+      <c r="V46" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="W46" s="8" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v>81.5</v>
-      </c>
+        <v>18.8</v>
+      </c>
+      <c r="X46" s="8" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="Y46" s="3" t="inlineStr"/>
       <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -41,8 +41,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -53,14 +53,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -156,9 +150,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -774,20 +765,20 @@
       <c r="C4" s="3" t="n">
         <v>83.7</v>
       </c>
-      <c r="D4" s="8" t="n">
-        <v>18.2</v>
+      <c r="D4" s="9" t="n">
+        <v>31.2</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="9" t="n">
         <v>24.2</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>14</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>91241.10000000001</v>
+        <v>91124.10000000001</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.1</v>
@@ -796,16 +787,16 @@
         <v>4.2</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>17.6</v>
+        <v>88.8</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>75.59999999999999</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>178.5</v>
+      <c r="N4" s="3" t="n">
+        <v>17.5</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>87</v>
@@ -829,7 +820,7 @@
         <v>15.4</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>27.7</v>
+        <v>27.2</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24</v>
@@ -853,26 +844,24 @@
       <c r="C5" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="9" t="n">
         <v>24.4</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="F5" s="8" t="n">
-        <v>13.5</v>
+      <c r="F5" s="9" t="n">
+        <v>21.5</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="n">
         <v>19.1</v>
       </c>
@@ -880,14 +869,12 @@
         <v>18</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>19.9</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="P5" s="3" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="n">
         <v>20.5</v>
       </c>
@@ -901,19 +888,19 @@
         <v>87.8</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W5" s="8" t="n">
+      <c r="W5" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="X5" s="8" t="n">
-        <v>72.5</v>
+      <c r="X5" s="3" t="n">
+        <v>27.5</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>726.1</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>9.699999999999999</v>
@@ -932,31 +919,31 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>831.6</v>
-      </c>
-      <c r="D6" s="3" t="n">
+        <v>432.6</v>
+      </c>
+      <c r="D6" s="9" t="n">
         <v>31.4</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="9" t="n">
         <v>25.6</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="H6" s="8" t="n">
+      <c r="H6" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2.6</v>
+        <v>9.6</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>20.3</v>
@@ -983,10 +970,10 @@
         <v>25.9</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>61.9</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>1.6</v>
+        <v>18.6</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>26.2</v>
@@ -1017,25 +1004,25 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>143.7</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>23.8</v>
+        <v>43.7</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>33</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F7" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F7" s="9" t="n">
         <v>25</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>14.8</v>
+        <v>84.8</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>18.2</v>
+        <v>2.2</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>4.9</v>
@@ -1043,17 +1030,17 @@
       <c r="K7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="8" t="n">
+      <c r="L7" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="M7" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>17.3</v>
+      <c r="M7" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>27.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.5</v>
@@ -1081,7 +1068,7 @@
         <v>26.5</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>1772.9</v>
+        <v>727.9</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>17.5</v>
@@ -1100,15 +1087,15 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>98971.60000000001</v>
-      </c>
-      <c r="D8" s="3" t="n">
+        <v>297.6</v>
+      </c>
+      <c r="D8" s="9" t="n">
         <v>32.6</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F8" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F8" s="9" t="n">
         <v>26.2</v>
       </c>
       <c r="G8" s="3" t="n">
@@ -1130,7 +1117,7 @@
         <v>20</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>20.5</v>
@@ -1186,12 +1173,12 @@
         <v>166.6</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1152.6</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F9" s="9" t="n">
+        <v>152.6</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F9" s="11" t="n">
         <v>122.9</v>
       </c>
       <c r="G9" s="3" t="n">
@@ -1201,7 +1188,7 @@
         <v>80.5</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>211.2</v>
+        <v>22.2</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>15.5</v>
@@ -1219,7 +1206,7 @@
         <v>96.3</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1840.9</v>
+        <v>440.9</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>12.9</v>
@@ -1228,10 +1215,10 @@
         <v>138.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>1217.3</v>
+        <v>117.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1831.9</v>
+        <v>1231.9</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>360.9</v>
@@ -1245,12 +1232,14 @@
       <c r="W9" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="X9" s="3" t="inlineStr"/>
+      <c r="X9" s="3" t="n">
+        <v>12.9</v>
+      </c>
       <c r="Y9" s="3" t="n">
-        <v>11418.4</v>
+        <v>114102.4</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>58.8</v>
+        <v>38.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1271,7 +1260,7 @@
       <c r="D10" s="9" t="n">
         <v>30.5</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="11" t="n">
         <v>18.5</v>
       </c>
       <c r="F10" s="9" t="n">
@@ -1281,17 +1270,13 @@
         <v>12</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>15.2</v>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>6.2</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
         <v>18.9</v>
       </c>
@@ -1302,7 +1287,7 @@
         <v>19.3</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>88.5</v>
+        <v>88.2</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>2.6</v>
@@ -1328,14 +1313,14 @@
       <c r="W10" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="X10" s="8" t="n">
+      <c r="X10" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>80.5</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1351,31 +1336,31 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1445.1</v>
-      </c>
-      <c r="D11" s="3" t="n">
+        <v>2445.1</v>
+      </c>
+      <c r="D11" s="9" t="n">
         <v>28.7</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="H11" s="3" t="n">
-        <v>18.2</v>
+      <c r="H11" s="8" t="n">
+        <v>85.2</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>20.1</v>
@@ -1383,35 +1368,35 @@
       <c r="M11" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="N11" s="8" t="n">
-        <v>46.7</v>
+      <c r="N11" s="3" t="n">
+        <v>24.7</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>87.90000000000001</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>230.8</v>
+        <v>25.8</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>31.9</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>85</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>5.7</v>
+        <v>58.7</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>25</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>4.1</v>
+        <v>2471.6</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>31.9</v>
@@ -1420,7 +1405,7 @@
         <v>97.5</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1436,22 +1421,22 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>318.3</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="E12" s="3" t="n">
+        <v>383.3</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="H12" s="8" t="n">
-        <v>81.09999999999999</v>
+      <c r="H12" s="3" t="n">
+        <v>18.1</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>2.9</v>
@@ -1460,7 +1445,7 @@
         <v>3.2</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>20.6</v>
@@ -1502,10 +1487,10 @@
         <v>30.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>197.7</v>
+        <v>97.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>19.7</v>
+        <v>0.7</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1521,16 +1506,16 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="D13" s="3" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="D13" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="F13" s="11" t="n">
-        <v>25.5</v>
+      <c r="F13" s="8" t="n">
+        <v>35.5</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>11.3</v>
@@ -1542,10 +1527,10 @@
         <v>1.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.1</v>
+        <v>2.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>5.3</v>
+        <v>0.3</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>20</v>
@@ -1583,11 +1568,11 @@
       <c r="W13" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X13" s="8" t="n">
+      <c r="X13" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>192.9</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>2.2</v>
@@ -1608,27 +1593,25 @@
       <c r="C14" s="3" t="n">
         <v>32.4</v>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D14" s="9" t="n">
         <v>32.5</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>17</v>
+        <v>17.4</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="J14" s="3" t="n">
-        <v>1.3</v>
-      </c>
+      <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="3" t="n">
         <v>5.7</v>
       </c>
@@ -1636,7 +1619,7 @@
         <v>19.8</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>18.7</v>
+        <v>28.7</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>20.8</v>
@@ -1645,7 +1628,7 @@
         <v>89.90000000000001</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>30.6</v>
@@ -1654,7 +1637,7 @@
         <v>22.6</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>50.9</v>
@@ -1668,11 +1651,11 @@
       <c r="W14" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="X14" s="8" t="n">
+      <c r="X14" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>193</v>
+        <v>93</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>1.8</v>
@@ -1691,31 +1674,31 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1643.3</v>
-      </c>
-      <c r="D15" s="3" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="D15" s="9" t="n">
         <v>29.5</v>
       </c>
-      <c r="E15" s="10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F15" s="11" t="n">
+      <c r="E15" s="9" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F15" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>19.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>19.8</v>
+        <v>89.8</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.8</v>
+        <v>16.8</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>20.4</v>
@@ -1745,7 +1728,7 @@
         <v>63.8</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>14.1</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>24.5</v>
@@ -1757,7 +1740,7 @@
         <v>22.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>1741</v>
+        <v>74</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>17.9</v>
@@ -1778,14 +1761,14 @@
       <c r="C16" s="3" t="n">
         <v>199.2</v>
       </c>
-      <c r="D16" s="9" t="n">
-        <v>1129.9</v>
+      <c r="D16" s="11" t="n">
+        <v>19249.9</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>991.8</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>124.2</v>
+        <v>99.09999999999999</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>124.7</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>50.8</v>
@@ -1793,7 +1776,9 @@
       <c r="H16" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="I16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="n">
+        <v>8.1</v>
+      </c>
       <c r="J16" s="3" t="n">
         <v>15.8</v>
       </c>
@@ -1801,25 +1786,25 @@
         <v>16</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>460.9</v>
+        <v>11.2</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>194.6</v>
+        <v>924.6</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1055.9</v>
+        <v>105.8</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>4464.1</v>
+        <v>444.8</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>102.9</v>
+        <v>12.9</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>142.8</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1123</v>
+        <v>23</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>142.5</v>
@@ -1859,10 +1844,10 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>5.8</v>
+        <v>39.8</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>19.8</v>
@@ -1870,18 +1855,22 @@
       <c r="F17" s="11" t="n">
         <v>24.9</v>
       </c>
-      <c r="G17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="H17" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>18.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>3.2</v>
+        <v>0.3</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="M17" s="3" t="n">
         <v>18.9</v>
       </c>
@@ -1889,7 +1878,7 @@
         <v>21</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>88.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>2.6</v>
@@ -1898,31 +1887,31 @@
         <v>28.6</v>
       </c>
       <c r="R17" s="8" t="n">
-        <v>82</v>
+        <v>8224</v>
       </c>
       <c r="S17" s="8" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="U17" s="8" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="U17" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V17" s="8" t="n">
-        <v>48.2</v>
+      <c r="V17" s="3" t="n">
+        <v>24.2</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="X17" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>191</v>
+        <v>91</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>12.7</v>
+        <v>2.7</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1938,32 +1927,34 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="D18" s="10" t="n">
         <v>40.8</v>
       </c>
-      <c r="E18" s="10" t="n">
-        <v>91</v>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>84.41</v>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="H18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="I18" s="3" t="n">
-        <v>1.5</v>
+        <v>24.9</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4.1</v>
+        <v>14</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>9.6</v>
+        <v>19.6</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>27.7</v>
@@ -1972,10 +1963,10 @@
         <v>1.9</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>87.2</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>28.6</v>
@@ -1987,19 +1978,19 @@
         <v>24.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>6.2</v>
+        <v>1.2</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V18" s="8" t="n">
+      <c r="V18" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="W18" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="X18" s="8" t="n">
-        <v>11.3</v>
+      <c r="W18" s="8" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>41</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>92.09999999999999</v>
@@ -2021,10 +2012,10 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>22.5</v>
+        <v>433.6</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>32.5</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>18.4</v>
@@ -2033,7 +2024,7 @@
         <v>25.5</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>11.6</v>
@@ -2042,7 +2033,7 @@
         <v>2.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>3.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>91.5</v>
@@ -2062,14 +2053,14 @@
       <c r="P19" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q19" s="8" t="n">
-        <v>61.8</v>
+      <c r="Q19" s="3" t="n">
+        <v>21.8</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="S19" s="8" t="n">
-        <v>295.3</v>
+        <v>24.2</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>25.3</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>54</v>
@@ -2077,8 +2068,8 @@
       <c r="U19" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="V19" s="8" t="n">
-        <v>655.8</v>
+      <c r="V19" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>23.3</v>
@@ -2087,7 +2078,7 @@
         <v>27</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>81.8</v>
+        <v>81.2</v>
       </c>
       <c r="Z19" s="3" t="inlineStr"/>
       <c r="AA19" s="3" t="inlineStr">
@@ -2104,30 +2095,30 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>856.8</v>
-      </c>
-      <c r="D20" s="10" t="n">
-        <v>88.40000000000001</v>
+        <v>956.8</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>27.2</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>25.5</v>
+        <v>23.5</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>18.5</v>
+        <v>1.8</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J20" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="n">
+        <v>24.3</v>
+      </c>
       <c r="L20" s="3" t="n">
         <v>20</v>
       </c>
@@ -2138,22 +2129,22 @@
         <v>20.9</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>189</v>
+        <v>289</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>70.7</v>
+        <v>707.2</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>95.09999999999999</v>
@@ -2162,7 +2153,7 @@
         <v>24.9</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>20.5</v>
+        <v>106.1</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>21.2</v>
@@ -2211,7 +2202,7 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>18.8</v>
@@ -2240,8 +2231,8 @@
       <c r="T21" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="U21" s="3" t="n">
-        <v>20.9</v>
+      <c r="U21" s="8" t="n">
+        <v>8.9</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>24.3</v>
@@ -2253,7 +2244,7 @@
         <v>25.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>185</v>
+        <v>850.8</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>14.5</v>
@@ -2272,23 +2263,25 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>34.4</v>
+        <v>374.1</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>31.8</v>
       </c>
-      <c r="E22" s="12" t="inlineStr"/>
+      <c r="E22" s="10" t="n">
+        <v>0.1</v>
+      </c>
       <c r="F22" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>14.6</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I22" s="8" t="n">
-        <v>21.1</v>
+      <c r="I22" s="3" t="n">
+        <v>2.1</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>3.5</v>
@@ -2327,19 +2320,19 @@
         <v>18.7</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W22" s="8" t="n">
-        <v>93.5</v>
-      </c>
-      <c r="X22" s="8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="W22" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="X22" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>85.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2357,17 +2350,17 @@
       <c r="C23" s="3" t="n">
         <v>1925.5</v>
       </c>
-      <c r="D23" s="9" t="n">
-        <v>153.1</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="F23" s="9" t="n">
+      <c r="D23" s="11" t="n">
+        <v>155.1</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="F23" s="11" t="n">
         <v>123</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>16027.4</v>
+        <v>605.9</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>85.59999999999999</v>
@@ -2379,7 +2372,7 @@
         <v>15.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>49.5</v>
+        <v>495.3</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>95.2</v>
@@ -2391,16 +2384,16 @@
         <v>96.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1137.2</v>
+        <v>437.2</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1535.7</v>
+        <v>113.7</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>146.2</v>
+        <v>14.6</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>1145.1</v>
+        <v>1143.1</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>19</v>
@@ -2412,16 +2405,16 @@
         <v>85.2</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>122.2</v>
+        <v>22.2</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>210.7</v>
+        <v>21</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>226.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>1811</v>
+        <v>1411</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>27.1</v>
@@ -2440,28 +2433,28 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="E24" s="9" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E24" s="11" t="n">
         <v>18.6</v>
       </c>
-      <c r="F24" s="9" t="n">
-        <v>84.59999999999999</v>
+      <c r="F24" s="11" t="n">
+        <v>82.59999999999999</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>11.2</v>
+        <v>1.7</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>0.1</v>
@@ -2473,16 +2466,16 @@
         <v>17.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>29.3</v>
+        <v>19.3</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>87.40000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>21.7</v>
+        <v>2.7</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>29.2</v>
+        <v>2.9</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>22.9</v>
@@ -2525,20 +2518,20 @@
       <c r="C25" s="3" t="n">
         <v>374</v>
       </c>
-      <c r="D25" s="10" t="n">
-        <v>42.1</v>
+      <c r="D25" s="3" t="n">
+        <v>12.1</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>20.7</v>
+        <v>19.3</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>25.7</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2.4</v>
@@ -2547,7 +2540,7 @@
         <v>3.6</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>81414.60000000001</v>
+        <v>1.6</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>19.5</v>
@@ -2559,40 +2552,40 @@
         <v>20.4</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>18.2</v>
+        <v>12.2</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="R25" s="8" t="n">
-        <v>4</v>
+        <v>31.5</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>24</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>96.90000000000001</v>
+        <v>56.9</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V25" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V25" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="X25" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>174.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2616,7 +2609,7 @@
       <c r="E26" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="F26" s="3" t="n">
+      <c r="F26" s="9" t="n">
         <v>24.7</v>
       </c>
       <c r="G26" s="3" t="n">
@@ -2628,8 +2621,8 @@
       <c r="I26" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J26" s="3" t="n">
-        <v>12.6</v>
+      <c r="J26" s="8" t="n">
+        <v>25.6</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>0.3</v>
@@ -2641,7 +2634,7 @@
         <v>17.6</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>19.2</v>
+        <v>89.2</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>87</v>
@@ -2656,13 +2649,13 @@
         <v>21.8</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>80</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>24.2</v>
@@ -2691,25 +2684,25 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>952.2</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>25.8</v>
+        <v>354.8</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>23.8</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="H27" s="3" t="n">
+      <c r="H27" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>11.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>2.9</v>
@@ -2727,7 +2720,7 @@
         <v>20.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>82.5</v>
+        <v>87.5</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>2.9</v>
@@ -2736,7 +2729,7 @@
         <v>26</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>22.6</v>
+        <v>21.6</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>23</v>
@@ -2744,20 +2737,20 @@
       <c r="T27" s="3" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="U27" s="8" t="n">
-        <v>0.6</v>
+      <c r="U27" s="3" t="n">
+        <v>10.4</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W27" s="8" t="n">
-        <v>9.800000000000001</v>
+        <v>63.4</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="X27" s="3" t="n">
         <v>23</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>180.8</v>
+        <v>84.8</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>5.4</v>
@@ -2776,25 +2769,25 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>288.9</v>
+        <v>0.8</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="E28" s="10" t="n">
-        <v>90.09999999999999</v>
-      </c>
-      <c r="F28" s="3" t="n">
+      <c r="E28" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F28" s="9" t="n">
         <v>25</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>19.6</v>
+        <v>9.6</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>12.3</v>
+        <v>2.3</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.8</v>
@@ -2808,14 +2801,14 @@
       <c r="M28" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="N28" s="8" t="n">
-        <v>281.3</v>
+      <c r="N28" s="3" t="n">
+        <v>21.3</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>87.40000000000001</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>11.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>28.2</v>
@@ -2830,19 +2823,19 @@
         <v>64.90000000000001</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>26</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="X28" s="8" t="n">
+        <v>956.1</v>
+      </c>
+      <c r="X28" s="3" t="n">
         <v>27.6</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>16</v>
@@ -2861,19 +2854,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>140.8</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>29.4</v>
+        <v>20.8</v>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>49.4</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>50.31</v>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>22.9</v>
+        <v>61.31</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>24.9</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>20.1</v>
@@ -2894,13 +2887,13 @@
         <v>19.2</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>28.6</v>
@@ -2908,11 +2901,11 @@
       <c r="R29" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="S29" s="3" t="n">
+      <c r="S29" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>162.6</v>
+        <v>62.4</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>14.6</v>
@@ -2923,14 +2916,14 @@
       <c r="W29" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="X29" s="8" t="n">
+      <c r="X29" s="3" t="n">
         <v>26.5</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>8182.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>16.1</v>
+        <v>6.1</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2946,16 +2939,16 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>11836.4</v>
-      </c>
-      <c r="D30" s="9" t="n">
+        <v>11856.4</v>
+      </c>
+      <c r="D30" s="11" t="n">
         <v>150.5</v>
       </c>
-      <c r="E30" s="9" t="n">
-        <v>0.8</v>
+      <c r="E30" s="11" t="n">
+        <v>97.8</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>1224.1</v>
+        <v>124.1</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>52.5</v>
@@ -2964,7 +2957,7 @@
         <v>9.1</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>15.8</v>
@@ -2973,22 +2966,22 @@
         <v>25.4</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>929.6</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>93.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>9103.4</v>
+        <v>103.4</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>14241.9</v>
+        <v>441.9</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>10.1</v>
+        <v>13.1</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>138.5</v>
+        <v>238.5</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>113.7</v>
@@ -3000,19 +2993,19 @@
         <v>332.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>16.4</v>
+        <v>6.4</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1123.1</v>
+        <v>123.1</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>110.1</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>164.3</v>
+        <v>61.3</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>39.4</v>
+        <v>43.9</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>32.6</v>
@@ -3031,22 +3024,22 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="D31" s="9" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="F31" s="9" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F31" s="11" t="n">
         <v>94.8</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>182.4</v>
+        <v>18.4</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2</v>
@@ -3054,10 +3047,8 @@
       <c r="J31" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L31" s="8" t="n">
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="M31" s="3" t="n">
@@ -3067,10 +3058,10 @@
         <v>20.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>22.4</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>27.7</v>
@@ -3079,25 +3070,25 @@
         <v>22.7</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>845.8</v>
+        <v>24.5</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>66.59999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V31" s="3" t="n">
-        <v>24.6</v>
+        <v>1.2</v>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v>824.6</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>22</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="Z31" s="3" t="inlineStr"/>
       <c r="AA31" s="3" t="inlineStr">
@@ -3114,16 +3105,16 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>943.7</v>
-      </c>
-      <c r="D32" s="10" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="E32" s="3" t="n">
+        <v>143.7</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E32" s="9" t="n">
         <v>20.2</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>26.9</v>
+        <v>28.9</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>12.6</v>
@@ -3132,13 +3123,13 @@
         <v>18.2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>20.6</v>
@@ -3147,13 +3138,13 @@
         <v>19.3</v>
       </c>
       <c r="N32" s="8" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>88.40000000000001</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>31</v>
@@ -3165,25 +3156,25 @@
         <v>25.4</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>560.6</v>
+        <v>56.6</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="V32" s="8" t="n">
-        <v>68.2</v>
+      <c r="V32" s="3" t="n">
+        <v>28.2</v>
       </c>
       <c r="W32" s="8" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="X32" s="8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X32" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="Y32" s="3" t="n">
         <v>169.1</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>11.8</v>
+        <v>111.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3199,31 +3190,31 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>397.1</v>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="E33" s="3" t="n">
+        <v>310.1</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="F33" s="10" t="n">
-        <v>65.7</v>
+      <c r="F33" s="3" t="n">
+        <v>26.7</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>12.9</v>
+        <v>17.9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>11.4</v>
+        <v>4.4</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K33" s="8" t="n">
-        <v>1.1</v>
+      <c r="K33" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>20.9</v>
@@ -3243,8 +3234,8 @@
       <c r="Q33" s="3" t="n">
         <v>32.9</v>
       </c>
-      <c r="R33" s="3" t="n">
-        <v>29.9</v>
+      <c r="R33" s="8" t="n">
+        <v>38.9</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>23.9</v>
@@ -3265,10 +3256,10 @@
         <v>25.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>122.6</v>
+        <v>1727.6</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>17.4</v>
+        <v>7.4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3287,15 +3278,15 @@
         <v>36.2</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E34" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E34" s="9" t="n">
         <v>20.2</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="G34" s="8" t="n">
+      <c r="G34" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
@@ -3307,8 +3298,8 @@
       <c r="J34" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="K34" s="8" t="n">
-        <v>2.4</v>
+      <c r="K34" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>20.4</v>
@@ -3329,28 +3320,28 @@
         <v>26.1</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>28.2</v>
+        <v>23.2</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>26.6</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>7886.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="V34" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="V34" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="X34" s="8" t="n">
+      <c r="X34" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>1832.8</v>
+        <v>182.8</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>5.4</v>
@@ -3369,12 +3360,12 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>187.9</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="9" t="n">
         <v>20.7</v>
       </c>
       <c r="F35" s="3" t="n">
@@ -3402,10 +3393,10 @@
         <v>19.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>21.3</v>
+        <v>29.3</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>3.6</v>
@@ -3423,22 +3414,22 @@
         <v>88.5</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>7.1</v>
+        <v>28.4</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>21.6</v>
+        <v>28.6</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>26.3</v>
+        <v>20.3</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>188.5</v>
+        <v>88.5</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>12.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3459,17 +3450,17 @@
       <c r="D36" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="E36" s="10" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="F36" s="8" t="n">
+      <c r="E36" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F36" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>18.6</v>
+        <v>8.6</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>19</v>
+        <v>190.1</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>2.2</v>
@@ -3478,7 +3469,7 @@
         <v>12.8</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>20.6</v>
@@ -3487,7 +3478,7 @@
         <v>19.4</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>89</v>
@@ -3505,19 +3496,19 @@
         <v>25.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>822.5</v>
+        <v>72.3</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="V36" s="8" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="W36" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="W36" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="X36" s="8" t="n">
-        <v>46.8</v>
+      <c r="X36" s="3" t="n">
+        <v>84.8</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>78.2</v>
@@ -3539,20 +3530,20 @@
       <c r="C37" s="3" t="n">
         <v>11683.5</v>
       </c>
-      <c r="D37" s="9" t="n">
-        <v>1450.1</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>120.2</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>125.5</v>
+      <c r="D37" s="11" t="n">
+        <v>150.1</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>92.5</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>49.2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>9224.1</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>12.6</v>
@@ -3567,10 +3558,10 @@
         <v>103.5</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>1396.5</v>
+        <v>96.5</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>127.2</v>
+        <v>18.7</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>437.5</v>
@@ -3579,13 +3570,13 @@
         <v>14.9</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>129</v>
+        <v>139.6</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>115.4</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>126</v>
+        <v>1256</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>343.7</v>
@@ -3624,29 +3615,29 @@
       <c r="C38" s="3" t="n">
         <v>336.7</v>
       </c>
-      <c r="D38" s="9" t="n">
+      <c r="D38" s="11" t="n">
         <v>30</v>
       </c>
       <c r="E38" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="11" t="n">
         <v>25.1</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>88.5</v>
+        <v>18.5</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>18.4</v>
+        <v>0.3</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
@@ -3670,25 +3661,25 @@
         <v>23.1</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>23.2</v>
+        <v>22.2</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>68.7</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>28.1</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>224.2</v>
+        <v>224.1</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>179.3</v>
+        <v>79.3</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>16.9</v>
@@ -3707,56 +3698,56 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>14001.8</v>
-      </c>
-      <c r="D39" s="8" t="n">
-        <v>11.8</v>
+        <v>400.8</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>31.8</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="F39" s="11" t="n">
+      <c r="F39" s="9" t="n">
         <v>25.7</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>18.1</v>
+        <v>58.5</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>82.09999999999999</v>
       </c>
       <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="n">
-        <v>29.9</v>
+        <v>13.9</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>10.5</v>
+        <v>20.5</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N39" s="3" t="n">
-        <v>12.8</v>
+      <c r="N39" s="8" t="n">
+        <v>88.40000000000001</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>91</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>2.1</v>
+        <v>5.1</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>30.4</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>25.1</v>
+        <v>23.1</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>23.6</v>
+        <v>22.6</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>534.5</v>
+        <v>54.5</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>19.8</v>
@@ -3768,13 +3759,13 @@
         <v>23.8</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>97.59999999999999</v>
+        <v>27.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>175.4</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>13.6</v>
+        <v>3.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3792,20 +3783,20 @@
       <c r="C40" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="D40" s="10" t="n">
-        <v>44.46</v>
+      <c r="D40" s="3" t="n">
+        <v>9.1</v>
       </c>
       <c r="E40" s="10" t="n">
         <v>90.2</v>
       </c>
-      <c r="F40" s="11" t="n">
+      <c r="F40" s="9" t="n">
         <v>22.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>19</v>
+        <v>3.9</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>89</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0.4</v>
@@ -3846,20 +3837,20 @@
       <c r="U40" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="V40" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="W40" s="8" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="X40" s="8" t="n">
-        <v>217.2</v>
+      <c r="V40" s="8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W40" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>21.7</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>181.5</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>19.9</v>
+        <v>15.9</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3875,31 +3866,31 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>114.8</v>
+        <v>64.8</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>49.43</v>
+        <v>94.3</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="F41" s="11" t="n">
+      <c r="F41" s="9" t="n">
         <v>24.5</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="H41" s="8" t="n">
+      <c r="H41" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="K41" s="8" t="n">
-        <v>11.6</v>
+        <v>3.8</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>19.9</v>
@@ -3938,10 +3929,10 @@
         <v>22.2</v>
       </c>
       <c r="X41" s="8" t="n">
-        <v>25.8</v>
+        <v>25.2</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>174</v>
+        <v>74</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>19.6</v>
@@ -3960,15 +3951,15 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="D42" s="10" t="n">
-        <v>98.8</v>
+        <v>1464.5</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>32.8</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F42" s="11" t="n">
+      <c r="F42" s="9" t="n">
         <v>24.9</v>
       </c>
       <c r="G42" s="3" t="n">
@@ -3981,7 +3972,7 @@
         <v>4.4</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>0.2</v>
@@ -4007,14 +3998,14 @@
       <c r="R42" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="S42" s="3" t="n">
-        <v>22.2</v>
+      <c r="S42" s="8" t="n">
+        <v>28.2</v>
       </c>
       <c r="T42" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="U42" s="8" t="n">
-        <v>28.2</v>
+      <c r="U42" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>27.5</v>
@@ -4022,11 +4013,11 @@
       <c r="W42" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="X42" s="8" t="n">
-        <v>10.4</v>
+      <c r="X42" s="3" t="n">
+        <v>94.40000000000001</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>18708</v>
+        <v>182</v>
       </c>
       <c r="Z42" s="3" t="n">
         <v>8.699999999999999</v>
@@ -4045,7 +4036,7 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>44.1</v>
+        <v>34.1</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>32</v>
@@ -4053,7 +4044,7 @@
       <c r="E43" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="F43" s="11" t="n">
+      <c r="F43" s="9" t="n">
         <v>25.3</v>
       </c>
       <c r="G43" s="3" t="n">
@@ -4066,7 +4057,7 @@
         <v>2.2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="K43" s="3" t="n">
         <v>15.2</v>
@@ -4084,7 +4075,7 @@
         <v>88.09999999999999</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>24.7</v>
@@ -4098,7 +4089,9 @@
       <c r="T43" s="3" t="n">
         <v>81.40000000000001</v>
       </c>
-      <c r="U43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="V43" s="3" t="n">
         <v>23</v>
       </c>
@@ -4106,7 +4099,7 @@
         <v>22.4</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>0.3</v>
+        <v>53.1</v>
       </c>
       <c r="Y43" s="3" t="n">
         <v>182.8</v>
@@ -4128,7 +4121,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>121.6</v>
+        <v>141.6</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>23.9</v>
@@ -4136,7 +4129,7 @@
       <c r="E44" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F44" s="11" t="n">
+      <c r="F44" s="9" t="n">
         <v>21.5</v>
       </c>
       <c r="G44" s="3" t="n">
@@ -4145,11 +4138,11 @@
       <c r="H44" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="I44" s="8" t="n">
-        <v>80.8</v>
+      <c r="I44" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>19.7</v>
@@ -4157,39 +4150,37 @@
       <c r="L44" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="M44" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="N44" s="8" t="n">
-        <v>0.8</v>
+      <c r="M44" s="8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>189</v>
+        <v>890.1</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="S44" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>181.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v>822.3</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>20.2</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="W44" s="3" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4207,72 +4198,74 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>18841.1</v>
-      </c>
-      <c r="D45" s="9" t="n">
-        <v>841.1</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>122.2</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <v>174</v>
+        <v>168211.1</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>825.1</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>51.7</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>160.2</v>
+        <v>10.6</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>105.6</v>
+        <v>2637</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>169</v>
+        <v>183.3</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>2816.1</v>
+        <v>28</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>12180.4</v>
+        <v>1910.4</v>
       </c>
       <c r="M45" s="3" t="inlineStr"/>
       <c r="N45" s="3" t="n">
-        <v>110109210619.1</v>
+        <v>10092105.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>204.1</v>
+        <v>34.2</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>16808.4</v>
+        <v>140.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1257.2</v>
+        <v>257.5</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>1291.7</v>
+        <v>129.2</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>18317.9</v>
+        <v>1382</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>44841.4</v>
+        <v>484</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="V45" s="3" t="inlineStr"/>
+        <v>11.2</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="W45" s="3" t="n">
-        <v>1122.2</v>
+        <v>182.2</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>924.7</v>
+        <v>24.7</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>81.5</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>15.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4288,31 +4281,31 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>511.7</v>
-      </c>
-      <c r="D46" s="9" t="n">
+        <v>311.7</v>
+      </c>
+      <c r="D46" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="F46" s="11" t="n">
+      <c r="F46" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="G46" s="8" t="n">
-        <v>20.1</v>
+      <c r="G46" s="3" t="n">
+        <v>10.1</v>
       </c>
       <c r="H46" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="I46" s="8" t="n">
-        <v>122.6</v>
+      <c r="I46" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>19.4</v>
@@ -4321,7 +4314,7 @@
         <v>18.2</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>60.5</v>
+        <v>20.2</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>89</v>
@@ -4330,7 +4323,7 @@
         <v>2.4</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>26.2</v>
+        <v>25.2</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>21.6</v>
@@ -4347,10 +4340,10 @@
       <c r="V46" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="W46" s="8" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="X46" s="8" t="n">
+      <c r="W46" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="X46" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="Y46" s="3" t="inlineStr"/>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -140,7 +152,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -150,6 +162,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -789,7 +810,7 @@
       <c r="K4" s="3" t="n">
         <v>88.8</v>
       </c>
-      <c r="L4" s="8" t="n">
+      <c r="L4" s="10" t="n">
         <v>75.59999999999999</v>
       </c>
       <c r="M4" s="3" t="n">
@@ -807,7 +828,7 @@
       <c r="Q4" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="9" t="n">
         <v>24.4</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -819,7 +840,7 @@
       <c r="U4" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" s="9" t="n">
         <v>27.2</v>
       </c>
       <c r="W4" s="3" t="n">
@@ -861,7 +882,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
+      <c r="K5" s="12" t="inlineStr"/>
       <c r="L5" s="3" t="n">
         <v>19.1</v>
       </c>
@@ -878,7 +899,7 @@
       <c r="Q5" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="9" t="n">
         <v>19.1</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -890,7 +911,7 @@
       <c r="U5" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" s="9" t="n">
         <v>20.6</v>
       </c>
       <c r="W5" s="3" t="n">
@@ -963,7 +984,7 @@
       <c r="Q6" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="9" t="n">
         <v>23.9</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -975,7 +996,7 @@
       <c r="U6" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="9" t="n">
         <v>26.2</v>
       </c>
       <c r="W6" s="3" t="n">
@@ -1018,7 +1039,7 @@
       <c r="G7" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="13" t="n">
         <v>84.8</v>
       </c>
       <c r="I7" s="3" t="n">
@@ -1033,10 +1054,10 @@
       <c r="L7" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="M7" s="8" t="n">
+      <c r="M7" s="10" t="n">
         <v>62</v>
       </c>
-      <c r="N7" s="8" t="n">
+      <c r="N7" s="13" t="n">
         <v>27.3</v>
       </c>
       <c r="O7" s="3" t="n">
@@ -1048,7 +1069,7 @@
       <c r="Q7" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="9" t="n">
         <v>23.9</v>
       </c>
       <c r="S7" s="3" t="n">
@@ -1060,11 +1081,11 @@
       <c r="U7" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="9" t="n">
         <v>27.6</v>
       </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="8" t="n">
+      <c r="W7" s="12" t="inlineStr"/>
+      <c r="X7" s="13" t="n">
         <v>26.5</v>
       </c>
       <c r="Y7" s="3" t="n">
@@ -1131,7 +1152,7 @@
       <c r="Q8" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="9" t="n">
         <v>26</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1143,7 +1164,7 @@
       <c r="U8" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="9" t="n">
         <v>24</v>
       </c>
       <c r="W8" s="3" t="n">
@@ -1193,13 +1214,13 @@
       <c r="J9" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="11" t="n">
         <v>44</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="11" t="n">
         <v>94.3</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="11" t="n">
         <v>87.8</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1211,10 +1232,10 @@
       <c r="P9" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="11" t="n">
         <v>138.8</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="9" t="n">
         <v>117.3</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1226,10 +1247,10 @@
       <c r="U9" s="3" t="n">
         <v>58.5</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="11" t="n">
         <v>126.1</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="11" t="n">
         <v>113</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1277,13 +1298,13 @@
         <v>6.2</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="M10" s="8" t="n">
+      <c r="M10" s="11" t="n">
         <v>87.59999999999999</v>
       </c>
-      <c r="N10" s="8" t="n">
+      <c r="N10" s="13" t="n">
         <v>19.3</v>
       </c>
       <c r="O10" s="3" t="n">
@@ -1292,10 +1313,10 @@
       <c r="P10" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="11" t="n">
         <v>27.8</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="9" t="n">
         <v>23.5</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1307,10 +1328,10 @@
       <c r="U10" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="11" t="n">
         <v>22.6</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1350,7 +1371,7 @@
       <c r="G11" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="H11" s="8" t="n">
+      <c r="H11" s="13" t="n">
         <v>85.2</v>
       </c>
       <c r="I11" s="3" t="n">
@@ -1377,7 +1398,7 @@
       <c r="P11" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="Q11" s="3" t="n">
+      <c r="Q11" s="9" t="n">
         <v>27.9</v>
       </c>
       <c r="R11" s="3" t="n">
@@ -1392,11 +1413,11 @@
       <c r="U11" s="3" t="n">
         <v>58.7</v>
       </c>
-      <c r="V11" s="3" t="n">
+      <c r="V11" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="W11" s="3" t="n">
-        <v>2471.6</v>
+      <c r="W11" s="10" t="n">
+        <v>247.16</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>31.9</v>
@@ -1462,7 +1483,7 @@
       <c r="P12" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" s="9" t="n">
         <v>27.2</v>
       </c>
       <c r="R12" s="3" t="n">
@@ -1477,7 +1498,7 @@
       <c r="U12" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="V12" s="9" t="n">
         <v>24.7</v>
       </c>
       <c r="W12" s="3" t="n">
@@ -1514,7 +1535,7 @@
       <c r="E13" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="13" t="n">
         <v>35.5</v>
       </c>
       <c r="G13" s="3" t="n">
@@ -1547,7 +1568,7 @@
       <c r="P13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" s="9" t="n">
         <v>28.6</v>
       </c>
       <c r="R13" s="3" t="n">
@@ -1562,7 +1583,7 @@
       <c r="U13" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="V13" s="9" t="n">
         <v>24.7</v>
       </c>
       <c r="W13" s="3" t="n">
@@ -1630,7 +1651,7 @@
       <c r="P14" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="Q14" s="9" t="n">
         <v>30.6</v>
       </c>
       <c r="R14" s="3" t="n">
@@ -1645,7 +1666,7 @@
       <c r="U14" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="V14" s="9" t="n">
         <v>21.9</v>
       </c>
       <c r="W14" s="3" t="n">
@@ -1715,7 +1736,7 @@
       <c r="P15" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="9" t="n">
         <v>28.5</v>
       </c>
       <c r="R15" s="3" t="n">
@@ -1730,7 +1751,7 @@
       <c r="U15" s="3" t="n">
         <v>84.09999999999999</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="9" t="n">
         <v>24.5</v>
       </c>
       <c r="W15" s="3" t="n">
@@ -1782,13 +1803,13 @@
       <c r="J16" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="11" t="n">
         <v>11.2</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="11" t="n">
         <v>924.6</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1800,10 +1821,10 @@
       <c r="P16" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="9" t="n">
         <v>142.8</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="11" t="n">
         <v>23</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1815,10 +1836,10 @@
       <c r="U16" s="3" t="n">
         <v>53.1</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" s="9" t="n">
         <v>120.8</v>
       </c>
-      <c r="W16" s="3" t="n">
+      <c r="W16" s="11" t="n">
         <v>115.1</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1868,10 +1889,10 @@
         <v>0.3</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="11" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="11" t="n">
         <v>18.9</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1883,13 +1904,13 @@
       <c r="P17" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="Q17" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="R17" s="8" t="n">
+      <c r="R17" s="11" t="n">
         <v>8224</v>
       </c>
-      <c r="S17" s="8" t="n">
+      <c r="S17" s="13" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
@@ -1898,10 +1919,10 @@
       <c r="U17" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="W17" s="3" t="n">
+      <c r="W17" s="11" t="n">
         <v>28</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1953,7 +1974,7 @@
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L18" s="9" t="n">
         <v>19.6</v>
       </c>
       <c r="M18" s="3" t="n">
@@ -1971,7 +1992,7 @@
       <c r="Q18" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="9" t="n">
         <v>23.1</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -1983,10 +2004,10 @@
       <c r="U18" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="W18" s="8" t="n">
+      <c r="W18" s="10" t="n">
         <v>50.6</v>
       </c>
       <c r="X18" s="3" t="n">
@@ -2038,7 +2059,7 @@
       <c r="K19" s="3" t="n">
         <v>91.5</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="9" t="n">
         <v>19.6</v>
       </c>
       <c r="M19" s="3" t="n">
@@ -2056,7 +2077,7 @@
       <c r="Q19" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" s="9" t="n">
         <v>24.2</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2068,7 +2089,7 @@
       <c r="U19" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="V19" s="9" t="n">
         <v>25.8</v>
       </c>
       <c r="W19" s="3" t="n">
@@ -2119,7 +2140,7 @@
       <c r="K20" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="9" t="n">
         <v>20</v>
       </c>
       <c r="M20" s="3" t="n">
@@ -2134,10 +2155,10 @@
       <c r="P20" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q20" s="3" t="n">
+      <c r="Q20" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="R20" s="3" t="n">
+      <c r="R20" s="9" t="n">
         <v>21.5</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2149,11 +2170,11 @@
       <c r="U20" s="3" t="n">
         <v>95.09999999999999</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="W20" s="3" t="n">
-        <v>106.1</v>
+      <c r="W20" s="10" t="n">
+        <v>10.61</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>21.2</v>
@@ -2204,7 +2225,7 @@
       <c r="K21" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="9" t="n">
         <v>18.8</v>
       </c>
       <c r="M21" s="3" t="n">
@@ -2222,7 +2243,7 @@
       <c r="Q21" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" s="9" t="n">
         <v>22.2</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2231,10 +2252,10 @@
       <c r="T21" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="U21" s="8" t="n">
+      <c r="U21" s="13" t="n">
         <v>8.9</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="9" t="n">
         <v>24.3</v>
       </c>
       <c r="W21" s="3" t="n">
@@ -2274,7 +2295,7 @@
       <c r="F22" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="G22" s="8" t="n">
+      <c r="G22" s="13" t="n">
         <v>84.59999999999999</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2289,7 +2310,7 @@
       <c r="K22" s="3" t="n">
         <v>3.7</v>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="L22" s="9" t="n">
         <v>17.6</v>
       </c>
       <c r="M22" s="3" t="n">
@@ -2307,7 +2328,7 @@
       <c r="Q22" s="3" t="n">
         <v>30.2</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="9" t="n">
         <v>23.3</v>
       </c>
       <c r="S22" s="3" t="n">
@@ -2319,7 +2340,7 @@
       <c r="U22" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="V22" s="9" t="n">
         <v>21.5</v>
       </c>
       <c r="W22" s="3" t="n">
@@ -2371,13 +2392,13 @@
       <c r="J23" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="11" t="n">
         <v>495.3</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="11" t="n">
         <v>95.2</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="11" t="n">
         <v>88.2</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2389,10 +2410,10 @@
       <c r="P23" s="3" t="n">
         <v>113.7</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="11" t="n">
         <v>14.6</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="11" t="n">
         <v>1143.1</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2404,10 +2425,10 @@
       <c r="U23" s="3" t="n">
         <v>85.2</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="11" t="n">
         <v>22.2</v>
       </c>
-      <c r="W23" s="3" t="n">
+      <c r="W23" s="11" t="n">
         <v>21</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2459,10 +2480,10 @@
       <c r="K24" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="M24" s="11" t="n">
         <v>17.6</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2474,10 +2495,10 @@
       <c r="P24" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="11" t="n">
         <v>2.9</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="9" t="n">
         <v>22.9</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2489,10 +2510,10 @@
       <c r="U24" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="11" t="n">
         <v>22.1</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2542,10 +2563,10 @@
       <c r="K25" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="L25" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="M25" s="3" t="n">
+      <c r="M25" s="9" t="n">
         <v>18.4</v>
       </c>
       <c r="N25" s="3" t="n">
@@ -2557,10 +2578,10 @@
       <c r="P25" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="Q25" s="3" t="n">
+      <c r="Q25" s="9" t="n">
         <v>31.5</v>
       </c>
-      <c r="R25" s="3" t="n">
+      <c r="R25" s="9" t="n">
         <v>24</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2621,16 +2642,16 @@
       <c r="I26" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J26" s="8" t="n">
+      <c r="J26" s="13" t="n">
         <v>25.6</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="L26" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="M26" s="9" t="n">
         <v>17.6</v>
       </c>
       <c r="N26" s="3" t="n">
@@ -2642,10 +2663,10 @@
       <c r="P26" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="9" t="n">
         <v>21.8</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2698,7 +2719,7 @@
       <c r="G27" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="H27" s="8" t="n">
+      <c r="H27" s="13" t="n">
         <v>17.8</v>
       </c>
       <c r="I27" s="3" t="n">
@@ -2710,10 +2731,10 @@
       <c r="K27" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="L27" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="9" t="n">
         <v>18.8</v>
       </c>
       <c r="N27" s="3" t="n">
@@ -2725,10 +2746,10 @@
       <c r="P27" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q27" s="3" t="n">
+      <c r="Q27" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="R27" s="9" t="n">
         <v>21.6</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2740,7 +2761,7 @@
       <c r="U27" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="V27" s="3" t="n">
+      <c r="V27" s="10" t="n">
         <v>63.4</v>
       </c>
       <c r="W27" s="3" t="n">
@@ -2795,10 +2816,10 @@
       <c r="K28" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="L28" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M28" s="3" t="n">
+      <c r="M28" s="9" t="n">
         <v>19.2</v>
       </c>
       <c r="N28" s="3" t="n">
@@ -2810,10 +2831,10 @@
       <c r="P28" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q28" s="3" t="n">
+      <c r="Q28" s="9" t="n">
         <v>28.2</v>
       </c>
-      <c r="R28" s="3" t="n">
+      <c r="R28" s="9" t="n">
         <v>23</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2828,8 +2849,8 @@
       <c r="V28" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="W28" s="3" t="n">
-        <v>956.1</v>
+      <c r="W28" s="10" t="n">
+        <v>95.61</v>
       </c>
       <c r="X28" s="3" t="n">
         <v>27.6</v>
@@ -2880,10 +2901,10 @@
       <c r="K29" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L29" s="3" t="n">
+      <c r="L29" s="9" t="n">
         <v>20.3</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="9" t="n">
         <v>19.2</v>
       </c>
       <c r="N29" s="3" t="n">
@@ -2895,13 +2916,13 @@
       <c r="P29" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q29" s="3" t="n">
+      <c r="Q29" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="3" t="n">
+      <c r="R29" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="S29" s="8" t="n">
+      <c r="S29" s="13" t="n">
         <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
@@ -2962,13 +2983,13 @@
       <c r="J30" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="11" t="n">
         <v>25.4</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="11" t="n">
         <v>929.6</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="9" t="n">
         <v>93.2</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -2980,10 +3001,10 @@
       <c r="P30" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" s="11" t="n">
         <v>238.5</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R30" s="11" t="n">
         <v>113.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -2995,10 +3016,10 @@
       <c r="U30" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="11" t="n">
         <v>123.1</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W30" s="11" t="n">
         <v>110.1</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3038,7 +3059,7 @@
       <c r="G31" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H31" s="8" t="n">
+      <c r="H31" s="13" t="n">
         <v>18.4</v>
       </c>
       <c r="I31" s="3" t="n">
@@ -3048,10 +3069,10 @@
         <v>3.2</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="n">
+      <c r="L31" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="M31" s="3" t="n">
+      <c r="M31" s="9" t="n">
         <v>18.6</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3063,10 +3084,10 @@
       <c r="P31" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="9" t="n">
         <v>27.7</v>
       </c>
-      <c r="R31" s="3" t="n">
+      <c r="R31" s="9" t="n">
         <v>22.7</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3078,10 +3099,10 @@
       <c r="U31" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="V31" s="8" t="n">
+      <c r="V31" s="11" t="n">
         <v>824.6</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="11" t="n">
         <v>22</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3107,7 +3128,7 @@
       <c r="C32" s="3" t="n">
         <v>143.7</v>
       </c>
-      <c r="D32" s="8" t="n">
+      <c r="D32" s="13" t="n">
         <v>12.8</v>
       </c>
       <c r="E32" s="9" t="n">
@@ -3131,13 +3152,13 @@
       <c r="K32" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L32" s="3" t="n">
+      <c r="L32" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M32" s="3" t="n">
+      <c r="M32" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="N32" s="8" t="n">
+      <c r="N32" s="13" t="n">
         <v>28.5</v>
       </c>
       <c r="O32" s="3" t="n">
@@ -3146,7 +3167,7 @@
       <c r="P32" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q32" s="3" t="n">
+      <c r="Q32" s="9" t="n">
         <v>31</v>
       </c>
       <c r="R32" s="3" t="n">
@@ -3164,7 +3185,7 @@
       <c r="V32" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="W32" s="8" t="n">
+      <c r="W32" s="13" t="n">
         <v>23.4</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3192,7 +3213,7 @@
       <c r="C33" s="3" t="n">
         <v>310.1</v>
       </c>
-      <c r="D33" s="8" t="n">
+      <c r="D33" s="13" t="n">
         <v>14.1</v>
       </c>
       <c r="E33" s="9" t="n">
@@ -3216,10 +3237,10 @@
       <c r="K33" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="9" t="n">
         <v>20.9</v>
       </c>
-      <c r="M33" s="3" t="n">
+      <c r="M33" s="9" t="n">
         <v>19.5</v>
       </c>
       <c r="N33" s="3" t="n">
@@ -3231,10 +3252,10 @@
       <c r="P33" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" s="9" t="n">
         <v>32.9</v>
       </c>
-      <c r="R33" s="8" t="n">
+      <c r="R33" s="13" t="n">
         <v>38.9</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3301,10 +3322,10 @@
       <c r="K34" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="9" t="n">
         <v>20.4</v>
       </c>
-      <c r="M34" s="3" t="n">
+      <c r="M34" s="9" t="n">
         <v>19</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -3316,7 +3337,7 @@
       <c r="P34" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" s="9" t="n">
         <v>26.1</v>
       </c>
       <c r="R34" s="3" t="n">
@@ -3331,7 +3352,7 @@
       <c r="U34" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="V34" s="8" t="n">
+      <c r="V34" s="13" t="n">
         <v>25.5</v>
       </c>
       <c r="W34" s="3" t="n">
@@ -3386,10 +3407,10 @@
       <c r="K35" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M35" s="3" t="n">
+      <c r="M35" s="9" t="n">
         <v>19.3</v>
       </c>
       <c r="N35" s="3" t="n">
@@ -3401,7 +3422,7 @@
       <c r="P35" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q35" s="3" t="n">
+      <c r="Q35" s="9" t="n">
         <v>22.6</v>
       </c>
       <c r="R35" s="3" t="n">
@@ -3471,10 +3492,10 @@
       <c r="K36" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M36" s="3" t="n">
+      <c r="M36" s="9" t="n">
         <v>19.4</v>
       </c>
       <c r="N36" s="3" t="n">
@@ -3486,7 +3507,7 @@
       <c r="P36" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q36" s="3" t="n">
+      <c r="Q36" s="9" t="n">
         <v>27</v>
       </c>
       <c r="R36" s="3" t="n">
@@ -3501,7 +3522,7 @@
       <c r="U36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V36" s="8" t="n">
+      <c r="V36" s="10" t="n">
         <v>58</v>
       </c>
       <c r="W36" s="3" t="n">
@@ -3551,13 +3572,13 @@
       <c r="J37" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="11" t="n">
         <v>10.2</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="L37" s="9" t="n">
         <v>103.5</v>
       </c>
-      <c r="M37" s="3" t="n">
+      <c r="M37" s="9" t="n">
         <v>96.5</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3569,10 +3590,10 @@
       <c r="P37" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="9" t="n">
         <v>139.6</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" s="11" t="n">
         <v>115.4</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3584,10 +3605,10 @@
       <c r="U37" s="3" t="n">
         <v>65.7</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="11" t="n">
         <v>126.1</v>
       </c>
-      <c r="W37" s="3" t="n">
+      <c r="W37" s="11" t="n">
         <v>112.2</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3639,10 +3660,10 @@
       <c r="K38" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L38" s="3" t="n">
+      <c r="L38" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M38" s="9" t="n">
         <v>19.3</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3654,10 +3675,10 @@
       <c r="P38" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="Q38" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="11" t="n">
         <v>23.1</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3669,10 +3690,10 @@
       <c r="U38" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="11" t="n">
         <v>25.2</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W38" s="11" t="n">
         <v>224.1</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3709,10 +3730,10 @@
       <c r="F39" s="9" t="n">
         <v>25.7</v>
       </c>
-      <c r="G39" s="8" t="n">
+      <c r="G39" s="13" t="n">
         <v>58.5</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="H39" s="13" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="I39" s="3" t="inlineStr"/>
@@ -3722,13 +3743,13 @@
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="3" t="n">
+      <c r="L39" s="9" t="n">
         <v>20.5</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N39" s="8" t="n">
+      <c r="N39" s="13" t="n">
         <v>88.40000000000001</v>
       </c>
       <c r="O39" s="3" t="n">
@@ -3737,10 +3758,10 @@
       <c r="P39" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" s="10" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="9" t="n">
         <v>23.1</v>
       </c>
       <c r="S39" s="3" t="n">
@@ -3795,7 +3816,7 @@
       <c r="G40" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="H40" s="8" t="n">
+      <c r="H40" s="13" t="n">
         <v>89</v>
       </c>
       <c r="I40" s="3" t="n">
@@ -3807,7 +3828,7 @@
       <c r="K40" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="L40" s="9" t="n">
         <v>20.4</v>
       </c>
       <c r="M40" s="3" t="n">
@@ -3825,7 +3846,7 @@
       <c r="Q40" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="R40" s="3" t="n">
+      <c r="R40" s="9" t="n">
         <v>19.8</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3837,7 +3858,7 @@
       <c r="U40" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="V40" s="8" t="n">
+      <c r="V40" s="13" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="W40" s="3" t="n">
@@ -3892,7 +3913,7 @@
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L41" s="9" t="n">
         <v>19.9</v>
       </c>
       <c r="M41" s="3" t="n">
@@ -3910,7 +3931,7 @@
       <c r="Q41" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" s="9" t="n">
         <v>21.6</v>
       </c>
       <c r="S41" s="3" t="n">
@@ -3928,7 +3949,7 @@
       <c r="W41" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="X41" s="8" t="n">
+      <c r="X41" s="13" t="n">
         <v>25.2</v>
       </c>
       <c r="Y41" s="3" t="n">
@@ -3977,7 +3998,7 @@
       <c r="K42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L42" s="3" t="n">
+      <c r="L42" s="9" t="n">
         <v>17.2</v>
       </c>
       <c r="M42" s="3" t="n">
@@ -3995,10 +4016,10 @@
       <c r="Q42" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="S42" s="8" t="n">
+      <c r="S42" s="13" t="n">
         <v>28.2</v>
       </c>
       <c r="T42" s="3" t="n">
@@ -4041,7 +4062,7 @@
       <c r="D43" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="E43" s="8" t="n">
+      <c r="E43" s="13" t="n">
         <v>18.6</v>
       </c>
       <c r="F43" s="9" t="n">
@@ -4062,7 +4083,7 @@
       <c r="K43" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="L43" s="3" t="n">
+      <c r="L43" s="9" t="n">
         <v>19</v>
       </c>
       <c r="M43" s="3" t="n">
@@ -4080,7 +4101,7 @@
       <c r="Q43" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="3" t="n">
+      <c r="R43" s="9" t="n">
         <v>22.3</v>
       </c>
       <c r="S43" s="3" t="n">
@@ -4147,10 +4168,10 @@
       <c r="K44" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="L44" s="3" t="n">
+      <c r="L44" s="9" t="n">
         <v>19.4</v>
       </c>
-      <c r="M44" s="8" t="n">
+      <c r="M44" s="13" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="N44" s="3" t="n">
@@ -4165,7 +4186,7 @@
       <c r="Q44" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="R44" s="3" t="n">
+      <c r="R44" s="9" t="n">
         <v>20.3</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4180,7 +4201,7 @@
       <c r="V44" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="W44" s="3" t="inlineStr"/>
+      <c r="W44" s="12" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4221,13 +4242,13 @@
       <c r="J45" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="11" t="n">
         <v>1910.4</v>
       </c>
-      <c r="M45" s="3" t="inlineStr"/>
+      <c r="M45" s="14" t="inlineStr"/>
       <c r="N45" s="3" t="n">
         <v>10092105.9</v>
       </c>
@@ -4237,10 +4258,10 @@
       <c r="P45" s="3" t="n">
         <v>140.4</v>
       </c>
-      <c r="Q45" s="3" t="n">
+      <c r="Q45" s="11" t="n">
         <v>257.5</v>
       </c>
-      <c r="R45" s="3" t="n">
+      <c r="R45" s="11" t="n">
         <v>129.2</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4252,10 +4273,10 @@
       <c r="U45" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="11" t="n">
         <v>12.2</v>
       </c>
-      <c r="W45" s="3" t="n">
+      <c r="W45" s="11" t="n">
         <v>182.2</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4295,7 +4316,7 @@
       <c r="G46" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="H46" s="8" t="n">
+      <c r="H46" s="13" t="n">
         <v>17.6</v>
       </c>
       <c r="I46" s="3" t="n">
@@ -4307,7 +4328,7 @@
       <c r="K46" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="L46" s="3" t="n">
+      <c r="L46" s="9" t="n">
         <v>19.4</v>
       </c>
       <c r="M46" s="3" t="n">
@@ -4322,10 +4343,10 @@
       <c r="P46" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q46" s="3" t="n">
+      <c r="Q46" s="11" t="n">
         <v>25.2</v>
       </c>
-      <c r="R46" s="3" t="n">
+      <c r="R46" s="9" t="n">
         <v>21.6</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4337,10 +4358,10 @@
       <c r="U46" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="11" t="n">
         <v>24.2</v>
       </c>
-      <c r="W46" s="3" t="n">
+      <c r="W46" s="11" t="n">
         <v>21.8</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -41,6 +41,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
       </patternFill>
@@ -49,12 +55,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,7 +152,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -165,6 +165,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -784,22 +790,22 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>83.7</v>
-      </c>
-      <c r="D4" s="9" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="D4" s="10" t="n">
         <v>31.2</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="F4" s="9" t="n">
-        <v>24.2</v>
+      <c r="F4" s="11" t="n">
+        <v>12.42</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>14</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>91124.10000000001</v>
+        <v>27.4</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.1</v>
@@ -808,12 +814,12 @@
         <v>4.2</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>88.8</v>
+        <v>0.6</v>
       </c>
       <c r="L4" s="10" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="M4" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M4" s="10" t="n">
         <v>16.2</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -825,10 +831,10 @@
       <c r="P4" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="R4" s="9" t="n">
+      <c r="R4" s="10" t="n">
         <v>24.4</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -840,10 +846,10 @@
       <c r="U4" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="V4" s="9" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="W4" s="3" t="n">
+      <c r="V4" s="10" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="W4" s="10" t="n">
         <v>24</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
@@ -863,30 +869,34 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="D5" s="9" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="D5" s="10" t="n">
         <v>24.4</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
+        <v>8.6</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="12" t="inlineStr"/>
-      <c r="L5" s="3" t="n">
+      <c r="K5" s="3" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="L5" s="10" t="n">
         <v>19.1</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="10" t="n">
         <v>18</v>
       </c>
       <c r="N5" s="3" t="n">
@@ -895,26 +905,28 @@
       <c r="O5" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="n">
+      <c r="P5" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q5" s="10" t="n">
         <v>20.5</v>
       </c>
-      <c r="R5" s="9" t="n">
+      <c r="R5" s="10" t="n">
         <v>19.1</v>
       </c>
-      <c r="S5" s="3" t="n">
+      <c r="S5" s="15" t="n">
         <v>21.2</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>87.8</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V5" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V5" s="10" t="n">
         <v>20.6</v>
       </c>
-      <c r="W5" s="3" t="n">
+      <c r="W5" s="10" t="n">
         <v>18.9</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -940,15 +952,15 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>432.6</v>
-      </c>
-      <c r="D6" s="9" t="n">
+        <v>421.6</v>
+      </c>
+      <c r="D6" s="10" t="n">
         <v>31.4</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="15" t="n">
         <v>25.6</v>
       </c>
       <c r="G6" s="3" t="n">
@@ -958,18 +970,18 @@
         <v>17.8</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>18.5</v>
+        <v>2.5</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="K6" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K6" s="15" t="n">
         <v>0.6</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="10" t="n">
         <v>20.3</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="10" t="n">
         <v>19</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -981,10 +993,10 @@
       <c r="P6" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="10" t="n">
         <v>29.8</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="R6" s="10" t="n">
         <v>23.9</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -994,12 +1006,12 @@
         <v>61.9</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="V6" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="V6" s="10" t="n">
         <v>26.2</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="10" t="n">
         <v>23.2</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1027,72 +1039,72 @@
       <c r="C7" s="3" t="n">
         <v>43.7</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="E7" s="10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F7" s="9" t="n">
+      <c r="E7" s="12" t="inlineStr"/>
+      <c r="F7" s="3" t="n">
         <v>25</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="13" t="n">
-        <v>84.8</v>
+      <c r="H7" s="15" t="n">
+        <v>14.8</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>4.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>12.3</v>
+        <v>10</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>17.3</v>
       </c>
       <c r="M7" s="10" t="n">
-        <v>62</v>
-      </c>
-      <c r="N7" s="13" t="n">
-        <v>27.3</v>
+        <v>16</v>
+      </c>
+      <c r="N7" s="15" t="n">
+        <v>17.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>87.59999999999999</v>
+        <v>872.6</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q7" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="R7" s="9" t="n">
+      <c r="Q7" s="10" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="R7" s="10" t="n">
         <v>23.9</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>52.1</v>
+        <v>152.1</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="V7" s="9" t="n">
+      <c r="V7" s="10" t="n">
         <v>27.6</v>
       </c>
-      <c r="W7" s="12" t="inlineStr"/>
-      <c r="X7" s="13" t="n">
+      <c r="W7" s="10" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X7" s="3" t="n">
         <v>26.5</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>727.9</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>17.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1108,18 +1120,18 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>297.6</v>
-      </c>
-      <c r="D8" s="9" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="D8" s="10" t="n">
         <v>32.6</v>
       </c>
-      <c r="E8" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F8" s="9" t="n">
+      <c r="E8" s="11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F8" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="15" t="n">
         <v>12.8</v>
       </c>
       <c r="H8" s="3" t="n">
@@ -1134,11 +1146,11 @@
       <c r="K8" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="M8" s="3" t="n">
-        <v>18.5</v>
+      <c r="M8" s="10" t="n">
+        <v>18.6</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>20.5</v>
@@ -1149,10 +1161,10 @@
       <c r="P8" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="R8" s="9" t="n">
+      <c r="R8" s="10" t="n">
         <v>26</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1162,21 +1174,23 @@
         <v>95.40000000000001</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="V8" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V8" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W8" s="10" t="n">
         <v>22.8</v>
       </c>
       <c r="X8" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>175.2</v>
+      </c>
+      <c r="Z8" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="Y8" s="3" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1194,33 +1208,33 @@
         <v>166.6</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>152.6</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>122.9</v>
+        <v>852.6</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>822.5</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>80.5</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>22.2</v>
+        <v>11.2</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="K9" s="11" t="n">
-        <v>44</v>
-      </c>
-      <c r="L9" s="11" t="n">
+      <c r="K9" s="9" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="L9" s="10" t="n">
         <v>94.3</v>
       </c>
-      <c r="M9" s="11" t="n">
+      <c r="M9" s="10" t="n">
         <v>87.8</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1232,14 +1246,14 @@
       <c r="P9" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="Q9" s="11" t="n">
+      <c r="Q9" s="10" t="n">
         <v>138.8</v>
       </c>
       <c r="R9" s="9" t="n">
-        <v>117.3</v>
+        <v>1617.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1231.9</v>
+        <v>131.9</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>360.9</v>
@@ -1247,20 +1261,20 @@
       <c r="U9" s="3" t="n">
         <v>58.5</v>
       </c>
-      <c r="V9" s="11" t="n">
+      <c r="V9" s="10" t="n">
         <v>126.1</v>
       </c>
-      <c r="W9" s="11" t="n">
+      <c r="W9" s="10" t="n">
         <v>113</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>12.9</v>
+        <v>129.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>114102.4</v>
+        <v>402.4</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>38.8</v>
+        <v>32.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1278,10 +1292,10 @@
       <c r="C10" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="10" t="n">
         <v>30.5</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="9" t="n">
         <v>18.5</v>
       </c>
       <c r="F10" s="9" t="n">
@@ -1291,20 +1305,24 @@
         <v>12</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I10" s="3" t="inlineStr"/>
+        <v>16.1</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="J10" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="10" t="n">
         <v>18.9</v>
       </c>
-      <c r="M10" s="11" t="n">
+      <c r="M10" s="9" t="n">
         <v>87.59999999999999</v>
       </c>
-      <c r="N10" s="13" t="n">
+      <c r="N10" s="15" t="n">
         <v>19.3</v>
       </c>
       <c r="O10" s="3" t="n">
@@ -1313,10 +1331,10 @@
       <c r="P10" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q10" s="11" t="n">
+      <c r="Q10" s="10" t="n">
         <v>27.8</v>
       </c>
-      <c r="R10" s="9" t="n">
+      <c r="R10" s="10" t="n">
         <v>23.5</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1328,10 +1346,10 @@
       <c r="U10" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="V10" s="9" t="n">
+      <c r="V10" s="10" t="n">
         <v>25.2</v>
       </c>
-      <c r="W10" s="11" t="n">
+      <c r="W10" s="10" t="n">
         <v>22.6</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1357,70 +1375,70 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2445.1</v>
-      </c>
-      <c r="D11" s="9" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="D11" s="10" t="n">
         <v>28.7</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" s="10" t="n">
         <v>24.3</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>85.2</v>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="10" t="n">
         <v>20.1</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>24.7</v>
+        <v>20.7</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>87.90000000000001</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="Q11" s="9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q11" s="10" t="n">
         <v>27.9</v>
       </c>
-      <c r="R11" s="3" t="n">
+      <c r="R11" s="10" t="n">
         <v>25.8</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>31.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>85</v>
+        <v>850.1</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="V11" s="9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="V11" s="10" t="n">
         <v>25</v>
       </c>
       <c r="W11" s="10" t="n">
-        <v>247.16</v>
+        <v>24.7</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>31.9</v>
+        <v>502.1</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>97.5</v>
@@ -1442,22 +1460,22 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>383.3</v>
-      </c>
-      <c r="D12" s="9" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="D12" s="10" t="n">
         <v>28.1</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="10" t="n">
         <v>23.9</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>8.5</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>18.1</v>
+        <v>18.5</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>2.9</v>
@@ -1466,9 +1484,9 @@
         <v>3.2</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="10" t="n">
         <v>20.6</v>
       </c>
       <c r="M12" s="3" t="n">
@@ -1481,12 +1499,12 @@
         <v>88.40000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q12" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="Q12" s="10" t="n">
         <v>27.2</v>
       </c>
-      <c r="R12" s="3" t="n">
+      <c r="R12" s="10" t="n">
         <v>25.2</v>
       </c>
       <c r="S12" s="3" t="n">
@@ -1498,17 +1516,17 @@
       <c r="U12" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="V12" s="9" t="n">
+      <c r="V12" s="10" t="n">
         <v>24.7</v>
       </c>
-      <c r="W12" s="3" t="n">
+      <c r="W12" s="10" t="n">
         <v>24.4</v>
       </c>
-      <c r="X12" s="3" t="n">
+      <c r="X12" s="15" t="n">
         <v>30.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>97.7</v>
+        <v>1197.7</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>0.7</v>
@@ -1527,16 +1545,16 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="D13" s="9" t="n">
+        <v>235.6</v>
+      </c>
+      <c r="D13" s="10" t="n">
         <v>31.1</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F13" s="13" t="n">
-        <v>35.5</v>
+      <c r="F13" s="10" t="n">
+        <v>25.5</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>11.3</v>
@@ -1553,7 +1571,7 @@
       <c r="K13" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="10" t="n">
         <v>20</v>
       </c>
       <c r="M13" s="3" t="n">
@@ -1568,10 +1586,10 @@
       <c r="P13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="Q13" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="R13" s="3" t="n">
+      <c r="R13" s="10" t="n">
         <v>26.3</v>
       </c>
       <c r="S13" s="3" t="n">
@@ -1583,10 +1601,10 @@
       <c r="U13" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="V13" s="9" t="n">
+      <c r="V13" s="10" t="n">
         <v>24.7</v>
       </c>
-      <c r="W13" s="3" t="n">
+      <c r="W13" s="10" t="n">
         <v>23.8</v>
       </c>
       <c r="X13" s="3" t="n">
@@ -1596,7 +1614,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1612,35 +1630,37 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="D14" s="9" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="D14" s="10" t="n">
         <v>32.5</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" s="10" t="n">
         <v>26.1</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="J14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="n">
+        <v>3.3</v>
+      </c>
       <c r="K14" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="M14" s="3" t="n">
-        <v>28.7</v>
+      <c r="M14" s="15" t="n">
+        <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>20.8</v>
@@ -1649,12 +1669,12 @@
         <v>89.90000000000001</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q14" s="9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q14" s="10" t="n">
         <v>30.6</v>
       </c>
-      <c r="R14" s="3" t="n">
+      <c r="R14" s="10" t="n">
         <v>22.6</v>
       </c>
       <c r="S14" s="3" t="n">
@@ -1663,16 +1683,16 @@
       <c r="T14" s="3" t="n">
         <v>50.9</v>
       </c>
-      <c r="U14" s="3" t="n">
+      <c r="U14" s="15" t="n">
         <v>21.6</v>
       </c>
-      <c r="V14" s="9" t="n">
+      <c r="V14" s="10" t="n">
         <v>21.9</v>
       </c>
-      <c r="W14" s="3" t="n">
+      <c r="W14" s="10" t="n">
         <v>21.1</v>
       </c>
-      <c r="X14" s="3" t="n">
+      <c r="X14" s="15" t="n">
         <v>24.5</v>
       </c>
       <c r="Y14" s="3" t="n">
@@ -1695,22 +1715,22 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="D15" s="9" t="n">
+        <v>143.3</v>
+      </c>
+      <c r="D15" s="10" t="n">
         <v>29.5</v>
       </c>
-      <c r="E15" s="9" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F15" s="3" t="n">
+      <c r="E15" s="11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F15" s="10" t="n">
         <v>24.9</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>89.8</v>
+        <v>19.8</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>1.9</v>
@@ -1719,13 +1739,13 @@
         <v>3.4</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="L15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="10" t="n">
         <v>20.4</v>
       </c>
-      <c r="M15" s="3" t="n">
-        <v>19.1</v>
+      <c r="M15" s="15" t="n">
+        <v>29.1</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>21.3</v>
@@ -1736,10 +1756,10 @@
       <c r="P15" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" s="10" t="n">
         <v>28.5</v>
       </c>
-      <c r="R15" s="3" t="n">
+      <c r="R15" s="10" t="n">
         <v>23.1</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1749,22 +1769,22 @@
         <v>63.8</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="V15" s="9" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="V15" s="10" t="n">
         <v>24.5</v>
       </c>
-      <c r="W15" s="3" t="n">
+      <c r="W15" s="10" t="n">
         <v>21.1</v>
       </c>
-      <c r="X15" s="3" t="n">
+      <c r="X15" s="15" t="n">
         <v>22.8</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>74</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>17.9</v>
+        <v>7.9</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1780,55 +1800,53 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>199.2</v>
-      </c>
-      <c r="D16" s="11" t="n">
-        <v>19249.9</v>
+        <v>1992.8</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>149.9</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="F16" s="10" t="n">
         <v>124.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>50.8</v>
+        <v>508.1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>8.1</v>
+        <v>11.1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="K16" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="L16" s="11" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="M16" s="11" t="n">
-        <v>924.6</v>
+        <v>115.8</v>
+      </c>
+      <c r="K16" s="16" t="inlineStr"/>
+      <c r="L16" s="9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <v>194.6</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>105.8</v>
+        <v>105.2</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>444.8</v>
+        <v>444.1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="Q16" s="9" t="n">
+      <c r="Q16" s="10" t="n">
         <v>142.8</v>
       </c>
-      <c r="R16" s="11" t="n">
-        <v>23</v>
+      <c r="R16" s="10" t="n">
+        <v>123</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>142.5</v>
+        <v>1042.5</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>368.7</v>
@@ -1836,14 +1854,14 @@
       <c r="U16" s="3" t="n">
         <v>53.1</v>
       </c>
-      <c r="V16" s="9" t="n">
+      <c r="V16" s="10" t="n">
         <v>120.8</v>
       </c>
-      <c r="W16" s="11" t="n">
+      <c r="W16" s="10" t="n">
         <v>115.1</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>137.5</v>
+        <v>2.5</v>
       </c>
       <c r="Y16" s="3" t="n">
         <v>455.1</v>
@@ -1865,65 +1883,67 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="D17" s="9" t="n">
+        <v>399.8</v>
+      </c>
+      <c r="D17" s="10" t="n">
         <v>30</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="10" t="n">
         <v>24.9</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>18.1</v>
+        <v>28.1</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="M17" s="11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K17" s="15" t="n">
+        <v>11551.5</v>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="M17" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>21</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q17" s="9" t="n">
+      <c r="Q17" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="R17" s="11" t="n">
-        <v>8224</v>
-      </c>
-      <c r="S17" s="13" t="n">
+      <c r="R17" s="10" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="S17" s="3" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>73.7</v>
+        <v>173.7</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V17" s="9" t="n">
+      <c r="V17" s="10" t="n">
         <v>24.2</v>
       </c>
-      <c r="W17" s="11" t="n">
-        <v>28</v>
+      <c r="W17" s="10" t="n">
+        <v>23</v>
       </c>
       <c r="X17" s="3" t="n">
         <v>27.5</v>
@@ -1948,70 +1968,70 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.5</v>
+        <v>431.1</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="E18" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E18" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>14.9</v>
+      <c r="F18" s="10" t="n">
+        <v>24.9</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.1</v>
+        <v>14.2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>24.9</v>
+        <v>13.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="9" t="n">
-        <v>19.6</v>
+      <c r="L18" s="10" t="n">
+        <v>19.2</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>27.7</v>
+        <v>20.8</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>1.9</v>
+        <v>13.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q18" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q18" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="R18" s="9" t="n">
+      <c r="R18" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>1.2</v>
+        <v>63.1</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V18" s="9" t="n">
+      <c r="V18" s="10" t="n">
         <v>26</v>
       </c>
       <c r="W18" s="10" t="n">
-        <v>50.6</v>
+        <v>25.6</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>92.09999999999999</v>
@@ -2033,15 +2053,15 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>433.6</v>
-      </c>
-      <c r="D19" s="3" t="n">
+        <v>2223.4</v>
+      </c>
+      <c r="D19" s="10" t="n">
         <v>32.5</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" s="10" t="n">
         <v>25.5</v>
       </c>
       <c r="G19" s="3" t="n">
@@ -2054,16 +2074,16 @@
         <v>2.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="L19" s="9" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="L19" s="10" t="n">
         <v>19.6</v>
       </c>
-      <c r="M19" s="3" t="n">
-        <v>28.2</v>
+      <c r="M19" s="15" t="n">
+        <v>18.2</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>20</v>
@@ -2074,10 +2094,10 @@
       <c r="P19" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q19" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="R19" s="9" t="n">
+      <c r="Q19" s="10" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="R19" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2089,10 +2109,10 @@
       <c r="U19" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="V19" s="9" t="n">
+      <c r="V19" s="10" t="n">
         <v>25.8</v>
       </c>
-      <c r="W19" s="3" t="n">
+      <c r="W19" s="10" t="n">
         <v>23.3</v>
       </c>
       <c r="X19" s="3" t="n">
@@ -2101,7 +2121,9 @@
       <c r="Y19" s="3" t="n">
         <v>81.2</v>
       </c>
-      <c r="Z19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -2116,19 +2138,19 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>956.8</v>
-      </c>
-      <c r="D20" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="D20" s="10" t="n">
         <v>27.2</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F20" s="10" t="n">
         <v>23.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>17.4</v>
+        <v>7.4</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>1.8</v>
@@ -2136,11 +2158,13 @@
       <c r="I20" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="K20" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="L20" s="9" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="L20" s="10" t="n">
         <v>20</v>
       </c>
       <c r="M20" s="3" t="n">
@@ -2150,31 +2174,31 @@
         <v>20.9</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>289</v>
+        <v>89</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="Q20" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R20" s="9" t="n">
-        <v>21.5</v>
+        <v>25.5</v>
+      </c>
+      <c r="R20" s="11" t="n">
+        <v>24.15</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>707.2</v>
+        <v>70.7</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>95.09999999999999</v>
-      </c>
-      <c r="V20" s="9" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="V20" s="10" t="n">
         <v>24.9</v>
       </c>
       <c r="W20" s="10" t="n">
-        <v>10.61</v>
+        <v>20.5</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>21.2</v>
@@ -2201,13 +2225,13 @@
       <c r="C21" s="3" t="n">
         <v>43.3</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="10" t="n">
         <v>30.8</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F21" s="10" t="n">
         <v>24.6</v>
       </c>
       <c r="G21" s="3" t="n">
@@ -2225,11 +2249,11 @@
       <c r="K21" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L21" s="9" t="n">
+      <c r="L21" s="10" t="n">
         <v>18.8</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>12.3</v>
+        <v>17.3</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>18.8</v>
@@ -2238,34 +2262,34 @@
         <v>86.7</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q21" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q21" s="10" t="n">
         <v>30.1</v>
       </c>
-      <c r="R21" s="9" t="n">
+      <c r="R21" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="U21" s="13" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="V21" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="V21" s="10" t="n">
         <v>24.3</v>
       </c>
-      <c r="W21" s="3" t="n">
+      <c r="W21" s="10" t="n">
         <v>22.4</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>850.8</v>
+        <v>85</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>14.5</v>
@@ -2284,19 +2308,19 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>374.1</v>
-      </c>
-      <c r="D22" s="3" t="n">
+        <v>2374.6</v>
+      </c>
+      <c r="D22" s="10" t="n">
         <v>31.8</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="G22" s="13" t="n">
-        <v>84.59999999999999</v>
+        <v>17.2</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>14.6</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>1.5</v>
@@ -2310,11 +2334,11 @@
       <c r="K22" s="3" t="n">
         <v>3.7</v>
       </c>
-      <c r="L22" s="9" t="n">
+      <c r="L22" s="10" t="n">
         <v>17.6</v>
       </c>
-      <c r="M22" s="3" t="n">
-        <v>16.2</v>
+      <c r="M22" s="15" t="n">
+        <v>26.2</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>17.5</v>
@@ -2325,25 +2349,25 @@
       <c r="P22" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q22" s="3" t="n">
+      <c r="Q22" s="10" t="n">
         <v>30.2</v>
       </c>
-      <c r="R22" s="9" t="n">
+      <c r="R22" s="3" t="n">
         <v>23.3</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>56.4</v>
+        <v>256.4</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="V22" s="9" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="W22" s="3" t="n">
+      <c r="V22" s="10" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="W22" s="10" t="n">
         <v>19.5</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2369,19 +2393,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1925.5</v>
-      </c>
-      <c r="D23" s="11" t="n">
-        <v>155.1</v>
-      </c>
-      <c r="E23" s="11" t="n">
+        <v>192.5</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>153.1</v>
+      </c>
+      <c r="E23" s="10" t="n">
         <v>92.8</v>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="F23" s="9" t="n">
         <v>123</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>605.9</v>
+        <v>60.5</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>85.59999999999999</v>
@@ -2390,15 +2414,15 @@
         <v>11.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="K23" s="11" t="n">
-        <v>495.3</v>
-      </c>
-      <c r="L23" s="11" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="L23" s="10" t="n">
         <v>95.2</v>
       </c>
-      <c r="M23" s="11" t="n">
+      <c r="M23" s="9" t="n">
         <v>88.2</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2410,35 +2434,35 @@
       <c r="P23" s="3" t="n">
         <v>113.7</v>
       </c>
-      <c r="Q23" s="11" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="R23" s="11" t="n">
-        <v>1143.1</v>
+      <c r="Q23" s="10" t="n">
+        <v>146.2</v>
+      </c>
+      <c r="R23" s="9" t="n">
+        <v>114.3</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>295.2</v>
+        <v>2895.2</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="V23" s="11" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W23" s="11" t="n">
-        <v>21</v>
+        <v>85.40000000000001</v>
+      </c>
+      <c r="V23" s="10" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="W23" s="9" t="n">
+        <v>110.7</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>226.7</v>
+        <v>126.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>1411</v>
+        <v>411</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>27.1</v>
+        <v>0.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2454,22 +2478,22 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="D24" s="11" t="n">
+        <v>1398.5</v>
+      </c>
+      <c r="D24" s="10" t="n">
         <v>30.6</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="F24" s="11" t="n">
-        <v>82.59999999999999</v>
+      <c r="F24" s="10" t="n">
+        <v>24.6</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>1.7</v>
+        <v>12</v>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>67.59999999999999</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
@@ -2480,14 +2504,14 @@
       <c r="K24" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L24" s="9" t="n">
+      <c r="L24" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="M24" s="11" t="n">
+      <c r="M24" s="9" t="n">
         <v>17.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>19.3</v>
+        <v>12.3</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>87.40000000000001</v>
@@ -2495,8 +2519,8 @@
       <c r="P24" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q24" s="11" t="n">
-        <v>2.9</v>
+      <c r="Q24" s="10" t="n">
+        <v>29.2</v>
       </c>
       <c r="R24" s="9" t="n">
         <v>22.9</v>
@@ -2508,18 +2532,20 @@
         <v>59</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="V24" s="9" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="V24" s="10" t="n">
         <v>24.4</v>
       </c>
-      <c r="W24" s="11" t="n">
+      <c r="W24" s="10" t="n">
         <v>22.1</v>
       </c>
       <c r="X24" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="Y24" s="3" t="inlineStr"/>
+      <c r="Y24" s="3" t="n">
+        <v>82.2</v>
+      </c>
       <c r="Z24" s="3" t="n">
         <v>5.4</v>
       </c>
@@ -2537,15 +2563,15 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>374</v>
+        <v>2374</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F25" s="9" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F25" s="10" t="n">
         <v>25.7</v>
       </c>
       <c r="G25" s="3" t="n">
@@ -2555,7 +2581,7 @@
         <v>18</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>3.6</v>
@@ -2563,50 +2589,50 @@
       <c r="K25" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L25" s="9" t="n">
+      <c r="L25" s="10" t="n">
         <v>19.5</v>
       </c>
-      <c r="M25" s="9" t="n">
+      <c r="M25" s="10" t="n">
         <v>18.4</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>20.4</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="Q25" s="9" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="R25" s="9" t="n">
-        <v>24</v>
+        <v>18.2</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="R25" s="10" t="n">
+        <v>24.3</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>25.9</v>
+        <v>22.9</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>56.9</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V25" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="V25" s="10" t="n">
         <v>24.2</v>
       </c>
-      <c r="W25" s="3" t="n">
+      <c r="W25" s="10" t="n">
         <v>20.9</v>
       </c>
-      <c r="X25" s="3" t="n">
+      <c r="X25" s="15" t="n">
         <v>22.6</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>174.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>7.5</v>
+        <v>17.2</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2622,7 +2648,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>329.2</v>
+        <v>329.8</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>30.8</v>
@@ -2630,32 +2656,32 @@
       <c r="E26" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="10" t="n">
         <v>24.7</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J26" s="13" t="n">
-        <v>25.6</v>
+      <c r="J26" s="3" t="n">
+        <v>2.6</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L26" s="9" t="n">
+      <c r="L26" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="M26" s="9" t="n">
+      <c r="M26" s="10" t="n">
         <v>17.6</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>89.2</v>
+        <v>19.2</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>87</v>
@@ -2663,31 +2689,33 @@
       <c r="P26" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q26" s="9" t="n">
+      <c r="Q26" s="10" t="n">
         <v>24.4</v>
       </c>
-      <c r="R26" s="9" t="n">
+      <c r="R26" s="10" t="n">
         <v>21.8</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>24.2</v>
+        <v>24.5</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>80</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="V26" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="V26" s="10" t="n">
         <v>24.2</v>
       </c>
-      <c r="W26" s="3" t="n">
+      <c r="W26" s="10" t="n">
         <v>21.8</v>
       </c>
-      <c r="X26" s="3" t="n">
+      <c r="X26" s="15" t="n">
         <v>24.6</v>
       </c>
-      <c r="Y26" s="3" t="inlineStr"/>
+      <c r="Y26" s="3" t="n">
+        <v>81.09999999999999</v>
+      </c>
       <c r="Z26" s="3" t="n">
         <v>17.6</v>
       </c>
@@ -2705,25 +2733,25 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>354.8</v>
-      </c>
-      <c r="D27" s="10" t="n">
-        <v>2.4</v>
+        <v>1354.4</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>2.2</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="10" t="n">
         <v>23.8</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="H27" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>2.9</v>
@@ -2731,25 +2759,25 @@
       <c r="K27" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="L27" s="9" t="n">
+      <c r="L27" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="M27" s="9" t="n">
+      <c r="M27" s="10" t="n">
         <v>18.8</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>87.5</v>
+        <v>88.5</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q27" s="9" t="n">
+      <c r="Q27" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="R27" s="9" t="n">
+      <c r="R27" s="10" t="n">
         <v>21.6</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2758,20 +2786,20 @@
       <c r="T27" s="3" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="U27" s="3" t="n">
-        <v>10.4</v>
+      <c r="U27" s="15" t="n">
+        <v>10.6</v>
       </c>
       <c r="V27" s="10" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="W27" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="W27" s="10" t="n">
         <v>20.8</v>
       </c>
       <c r="X27" s="3" t="n">
         <v>23</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>84.8</v>
+        <v>802.1</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>5.4</v>
@@ -2790,7 +2818,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.8</v>
+        <v>389.3</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>29.8</v>
@@ -2798,7 +2826,7 @@
       <c r="E28" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="10" t="n">
         <v>25</v>
       </c>
       <c r="G28" s="3" t="n">
@@ -2814,12 +2842,12 @@
         <v>3.8</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="L28" s="9" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="L28" s="10" t="n">
         <v>20.6</v>
       </c>
-      <c r="M28" s="9" t="n">
+      <c r="M28" s="10" t="n">
         <v>19.2</v>
       </c>
       <c r="N28" s="3" t="n">
@@ -2831,10 +2859,10 @@
       <c r="P28" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q28" s="9" t="n">
+      <c r="Q28" s="10" t="n">
         <v>28.2</v>
       </c>
-      <c r="R28" s="9" t="n">
+      <c r="R28" s="10" t="n">
         <v>23</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2844,13 +2872,13 @@
         <v>64.90000000000001</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V28" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="V28" s="10" t="n">
         <v>26</v>
       </c>
       <c r="W28" s="10" t="n">
-        <v>95.61</v>
+        <v>23.6</v>
       </c>
       <c r="X28" s="3" t="n">
         <v>27.6</v>
@@ -2859,7 +2887,7 @@
         <v>82</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2877,64 +2905,64 @@
       <c r="C29" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="D29" s="10" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>61.31</v>
-      </c>
-      <c r="F29" s="9" t="n">
+      <c r="D29" s="3" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F29" s="10" t="n">
         <v>24.9</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>9.1</v>
+        <v>19.1</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L29" s="9" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L29" s="10" t="n">
         <v>20.3</v>
       </c>
-      <c r="M29" s="9" t="n">
+      <c r="M29" s="10" t="n">
         <v>19.2</v>
       </c>
-      <c r="N29" s="3" t="n">
+      <c r="N29" s="15" t="n">
         <v>21.5</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q29" s="9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q29" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="9" t="n">
+      <c r="R29" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="S29" s="13" t="n">
+      <c r="S29" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>62.4</v>
+        <v>62.6</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="V29" s="3" t="n">
+      <c r="V29" s="10" t="n">
         <v>25.5</v>
       </c>
-      <c r="W29" s="3" t="n">
+      <c r="W29" s="10" t="n">
         <v>23</v>
       </c>
       <c r="X29" s="3" t="n">
@@ -2960,22 +2988,22 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>11856.4</v>
-      </c>
-      <c r="D30" s="11" t="n">
-        <v>150.5</v>
-      </c>
-      <c r="E30" s="11" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="F30" s="9" t="n">
+        <v>1856.4</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>150.3</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="F30" s="10" t="n">
         <v>124.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>52.5</v>
+        <v>152.5</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>9.1</v>
+        <v>191.7</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>10</v>
@@ -2983,17 +3011,17 @@
       <c r="J30" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="K30" s="11" t="n">
+      <c r="K30" s="9" t="n">
         <v>25.4</v>
       </c>
-      <c r="L30" s="11" t="n">
-        <v>929.6</v>
-      </c>
-      <c r="M30" s="9" t="n">
+      <c r="L30" s="10" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="M30" s="10" t="n">
         <v>93.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>103.4</v>
+        <v>103.2</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>441.9</v>
@@ -3001,10 +3029,10 @@
       <c r="P30" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q30" s="11" t="n">
-        <v>238.5</v>
-      </c>
-      <c r="R30" s="11" t="n">
+      <c r="Q30" s="10" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="R30" s="10" t="n">
         <v>113.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3014,19 +3042,19 @@
         <v>332.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="V30" s="11" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="V30" s="10" t="n">
         <v>123.1</v>
       </c>
-      <c r="W30" s="11" t="n">
+      <c r="W30" s="10" t="n">
         <v>110.1</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>61.3</v>
+        <v>124.3</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>43.9</v>
+        <v>399.8</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>32.6</v>
@@ -3045,34 +3073,36 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="D31" s="11" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E31" s="11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>94.8</v>
+        <v>37.1</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>24.8</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="H31" s="15" t="n">
         <v>18.4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L31" s="10" t="n">
         <v>19.9</v>
       </c>
-      <c r="M31" s="9" t="n">
+      <c r="M31" s="10" t="n">
         <v>18.6</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3084,34 +3114,36 @@
       <c r="P31" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q31" s="10" t="n">
         <v>27.7</v>
       </c>
-      <c r="R31" s="9" t="n">
+      <c r="R31" s="10" t="n">
         <v>22.7</v>
       </c>
-      <c r="S31" s="3" t="n">
+      <c r="S31" s="15" t="n">
         <v>24.5</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>66.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="V31" s="11" t="n">
-        <v>824.6</v>
-      </c>
-      <c r="W31" s="11" t="n">
+      <c r="V31" s="10" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="W31" s="10" t="n">
         <v>22</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>24.9</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="Z31" s="3" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>6.5</v>
+      </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3126,51 +3158,51 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>143.7</v>
-      </c>
-      <c r="D32" s="13" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E32" s="9" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="E32" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="G32" s="3" t="n">
+      <c r="F32" s="11" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="G32" s="15" t="n">
         <v>12.6</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="10" t="n">
         <v>20.6</v>
       </c>
-      <c r="M32" s="9" t="n">
+      <c r="M32" s="10" t="n">
         <v>19.3</v>
       </c>
-      <c r="N32" s="13" t="n">
-        <v>28.5</v>
+      <c r="N32" s="15" t="n">
+        <v>21.5</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>88.40000000000001</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q32" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q32" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="R32" s="3" t="n">
+      <c r="R32" s="10" t="n">
         <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3180,22 +3212,22 @@
         <v>56.6</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V32" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="V32" s="10" t="n">
         <v>28.2</v>
       </c>
-      <c r="W32" s="13" t="n">
-        <v>23.4</v>
+      <c r="W32" s="10" t="n">
+        <v>23.7</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>169.1</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>111.8</v>
+        <v>11.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3211,12 +3243,12 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>310.1</v>
-      </c>
-      <c r="D33" s="13" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="E33" s="9" t="n">
+        <v>397.9</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="E33" s="10" t="n">
         <v>19.8</v>
       </c>
       <c r="F33" s="3" t="n">
@@ -3235,12 +3267,12 @@
         <v>5.5</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="10" t="n">
         <v>20.9</v>
       </c>
-      <c r="M33" s="9" t="n">
+      <c r="M33" s="10" t="n">
         <v>19.5</v>
       </c>
       <c r="N33" s="3" t="n">
@@ -3252,35 +3284,35 @@
       <c r="P33" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q33" s="9" t="n">
+      <c r="Q33" s="10" t="n">
         <v>32.9</v>
       </c>
-      <c r="R33" s="13" t="n">
-        <v>38.9</v>
+      <c r="R33" s="10" t="n">
+        <v>23.9</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>47.7</v>
+        <v>147.7</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="V33" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V33" s="10" t="n">
         <v>25.8</v>
       </c>
-      <c r="W33" s="3" t="n">
+      <c r="W33" s="10" t="n">
         <v>22.8</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>1727.6</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>7.4</v>
+        <v>17.4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3296,12 +3328,12 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>36.2</v>
+        <v>1362.4</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>30.4</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E34" s="10" t="n">
         <v>20.2</v>
       </c>
       <c r="F34" s="3" t="n">
@@ -3311,21 +3343,21 @@
         <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>18.2</v>
+        <v>1.8</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="L34" s="9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L34" s="10" t="n">
         <v>20.4</v>
       </c>
-      <c r="M34" s="9" t="n">
+      <c r="M34" s="10" t="n">
         <v>19</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -3337,10 +3369,10 @@
       <c r="P34" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="10" t="n">
         <v>26.1</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="10" t="n">
         <v>23.2</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3352,17 +3384,17 @@
       <c r="U34" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="V34" s="13" t="n">
+      <c r="V34" s="10" t="n">
         <v>25.5</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="10" t="n">
         <v>23.3</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>182.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>5.4</v>
@@ -3386,7 +3418,7 @@
       <c r="D35" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" s="10" t="n">
         <v>20.7</v>
       </c>
       <c r="F35" s="3" t="n">
@@ -3396,7 +3428,7 @@
         <v>3.9</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>1.8</v>
+        <v>18.7</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>0.3</v>
@@ -3407,14 +3439,14 @@
       <c r="K35" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="L35" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="M35" s="9" t="n">
+      <c r="L35" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="M35" s="10" t="n">
         <v>19.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>29.3</v>
+        <v>20</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>85.40000000000001</v>
@@ -3422,10 +3454,10 @@
       <c r="P35" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q35" s="9" t="n">
+      <c r="Q35" s="10" t="n">
         <v>22.6</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="10" t="n">
         <v>21.2</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3435,12 +3467,12 @@
         <v>88.5</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="W35" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V35" s="10" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="W35" s="10" t="n">
         <v>20.3</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3468,10 +3500,10 @@
       <c r="C36" s="3" t="n">
         <v>398.9</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="15" t="n">
         <v>28.6</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="E36" s="10" t="n">
         <v>20</v>
       </c>
       <c r="F36" s="3" t="n">
@@ -3480,26 +3512,26 @@
       <c r="G36" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="H36" s="3" t="n">
-        <v>190.1</v>
+      <c r="H36" s="15" t="n">
+        <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="10" t="n">
         <v>20.6</v>
       </c>
-      <c r="M36" s="9" t="n">
+      <c r="M36" s="10" t="n">
         <v>19.4</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>89</v>
@@ -3507,10 +3539,10 @@
       <c r="P36" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q36" s="9" t="n">
+      <c r="Q36" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" s="10" t="n">
         <v>23.1</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3523,18 +3555,20 @@
         <v>9.800000000000001</v>
       </c>
       <c r="V36" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="W36" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="W36" s="10" t="n">
         <v>22.1</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>84.8</v>
+        <v>24.8</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>78.2</v>
       </c>
-      <c r="Z36" s="3" t="inlineStr"/>
+      <c r="Z36" s="3" t="n">
+        <v>6.9</v>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3549,19 +3583,19 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>11683.5</v>
-      </c>
-      <c r="D37" s="11" t="n">
+        <v>168.3</v>
+      </c>
+      <c r="D37" s="9" t="n">
         <v>150.1</v>
       </c>
-      <c r="E37" s="11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F37" s="11" t="n">
-        <v>92.5</v>
+      <c r="E37" s="10" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>125.5</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>49.2</v>
+        <v>149.2</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>92.40000000000001</v>
@@ -3572,17 +3606,17 @@
       <c r="J37" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="K37" s="11" t="n">
-        <v>10.2</v>
+      <c r="K37" s="9" t="n">
+        <v>102.8</v>
       </c>
       <c r="L37" s="9" t="n">
         <v>103.5</v>
       </c>
-      <c r="M37" s="9" t="n">
+      <c r="M37" s="10" t="n">
         <v>96.5</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>18.7</v>
+        <v>107.2</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>437.5</v>
@@ -3590,14 +3624,14 @@
       <c r="P37" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="Q37" s="9" t="n">
+      <c r="Q37" s="10" t="n">
         <v>139.6</v>
       </c>
-      <c r="R37" s="11" t="n">
+      <c r="R37" s="10" t="n">
         <v>115.4</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>1256</v>
+        <v>126</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>343.7</v>
@@ -3605,10 +3639,10 @@
       <c r="U37" s="3" t="n">
         <v>65.7</v>
       </c>
-      <c r="V37" s="11" t="n">
+      <c r="V37" s="10" t="n">
         <v>126.1</v>
       </c>
-      <c r="W37" s="11" t="n">
+      <c r="W37" s="10" t="n">
         <v>112.2</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3634,15 +3668,15 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>336.7</v>
-      </c>
-      <c r="D38" s="11" t="n">
+        <v>2326.7</v>
+      </c>
+      <c r="D38" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="F38" s="11" t="n">
+      <c r="F38" s="9" t="n">
         <v>25.1</v>
       </c>
       <c r="G38" s="3" t="n">
@@ -3655,19 +3689,19 @@
         <v>2.5</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L38" s="9" t="n">
+      <c r="L38" s="10" t="n">
         <v>20.7</v>
       </c>
       <c r="M38" s="9" t="n">
-        <v>19.3</v>
+        <v>1.9</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>28.4</v>
+        <v>21.4</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>87.5</v>
@@ -3675,26 +3709,26 @@
       <c r="P38" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q38" s="9" t="n">
+      <c r="Q38" s="10" t="n">
         <v>27.9</v>
       </c>
-      <c r="R38" s="11" t="n">
+      <c r="R38" s="10" t="n">
         <v>23.1</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>22.2</v>
+        <v>25.2</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>68.7</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="V38" s="11" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="V38" s="10" t="n">
         <v>25.2</v>
       </c>
-      <c r="W38" s="11" t="n">
-        <v>224.1</v>
+      <c r="W38" s="10" t="n">
+        <v>22.4</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>25.4</v>
@@ -3703,7 +3737,7 @@
         <v>79.3</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3719,7 +3753,7 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>400.8</v>
+        <v>1400.8</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>31.8</v>
@@ -3727,45 +3761,47 @@
       <c r="E39" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F39" s="10" t="n">
         <v>25.7</v>
       </c>
-      <c r="G39" s="13" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="H39" s="13" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="I39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>2.5</v>
+      </c>
       <c r="J39" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="9" t="n">
+      <c r="L39" s="10" t="n">
         <v>20.5</v>
       </c>
-      <c r="M39" s="3" t="n">
+      <c r="M39" s="10" t="n">
         <v>19.5</v>
       </c>
-      <c r="N39" s="13" t="n">
-        <v>88.40000000000001</v>
+      <c r="N39" s="15" t="n">
+        <v>22</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>91</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="Q39" s="10" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="R39" s="9" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="R39" s="10" t="n">
         <v>23.1</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>22.6</v>
+        <v>23.6</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>54.5</v>
@@ -3773,10 +3809,10 @@
       <c r="U39" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="V39" s="10" t="n">
         <v>26.8</v>
       </c>
-      <c r="W39" s="3" t="n">
+      <c r="W39" s="10" t="n">
         <v>23.8</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3804,20 +3840,20 @@
       <c r="C40" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="D40" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="F40" s="9" t="n">
+      <c r="D40" s="11" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F40" s="10" t="n">
         <v>22.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H40" s="13" t="n">
-        <v>89</v>
+        <v>13.9</v>
+      </c>
+      <c r="H40" s="15" t="n">
+        <v>129</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0.4</v>
@@ -3828,14 +3864,14 @@
       <c r="K40" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="L40" s="9" t="n">
+      <c r="L40" s="10" t="n">
         <v>20.4</v>
       </c>
-      <c r="M40" s="3" t="n">
+      <c r="M40" s="10" t="n">
         <v>19.1</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>22.2</v>
+        <v>24.2</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>88</v>
@@ -3843,10 +3879,10 @@
       <c r="P40" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q40" s="3" t="n">
+      <c r="Q40" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="R40" s="9" t="n">
+      <c r="R40" s="10" t="n">
         <v>19.8</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3858,20 +3894,20 @@
       <c r="U40" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="V40" s="13" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W40" s="3" t="n">
-        <v>19</v>
+      <c r="V40" s="10" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="W40" s="10" t="n">
+        <v>19.6</v>
       </c>
       <c r="X40" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>181.5</v>
+        <v>85.5</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>15.9</v>
+        <v>81.3</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3887,15 +3923,15 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="D41" s="10" t="n">
-        <v>94.3</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="F41" s="9" t="n">
+        <v>244.8</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F41" s="10" t="n">
         <v>24.5</v>
       </c>
       <c r="G41" s="3" t="n">
@@ -3905,7 +3941,7 @@
         <v>17.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>3.8</v>
@@ -3913,10 +3949,10 @@
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="9" t="n">
+      <c r="L41" s="10" t="n">
         <v>19.9</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" s="10" t="n">
         <v>18.7</v>
       </c>
       <c r="N41" s="3" t="n">
@@ -3928,10 +3964,10 @@
       <c r="P41" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q41" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="R41" s="9" t="n">
+      <c r="R41" s="10" t="n">
         <v>21.6</v>
       </c>
       <c r="S41" s="3" t="n">
@@ -3943,20 +3979,20 @@
       <c r="U41" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="10" t="n">
         <v>24.6</v>
       </c>
-      <c r="W41" s="3" t="n">
+      <c r="W41" s="10" t="n">
         <v>22.2</v>
       </c>
-      <c r="X41" s="13" t="n">
+      <c r="X41" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>74</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>19.6</v>
+        <v>9.6</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3972,7 +4008,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1464.5</v>
+        <v>116.4</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>32.8</v>
@@ -3980,10 +4016,10 @@
       <c r="E42" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="10" t="n">
         <v>24.9</v>
       </c>
-      <c r="G42" s="3" t="n">
+      <c r="G42" s="15" t="n">
         <v>25.8</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -3998,10 +4034,10 @@
       <c r="K42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L42" s="9" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="M42" s="3" t="n">
+      <c r="L42" s="10" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="M42" s="10" t="n">
         <v>16.1</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -4011,37 +4047,37 @@
         <v>89</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Q42" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q42" s="10" t="n">
         <v>30.8</v>
       </c>
-      <c r="R42" s="9" t="n">
+      <c r="R42" s="10" t="n">
         <v>22.6</v>
       </c>
-      <c r="S42" s="13" t="n">
-        <v>28.2</v>
+      <c r="S42" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="V42" s="3" t="n">
+      <c r="V42" s="10" t="n">
         <v>27.5</v>
       </c>
-      <c r="W42" s="3" t="n">
-        <v>25.8</v>
+      <c r="W42" s="10" t="n">
+        <v>23.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>94.40000000000001</v>
+        <v>27.1</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>182</v>
+        <v>24.4</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>87</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4057,18 +4093,18 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>34.1</v>
+        <v>2341.3</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="E43" s="13" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F43" s="9" t="n">
+      <c r="E43" s="11" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="F43" s="10" t="n">
         <v>25.3</v>
       </c>
-      <c r="G43" s="3" t="n">
+      <c r="G43" s="15" t="n">
         <v>13.4</v>
       </c>
       <c r="H43" s="3" t="n">
@@ -4083,47 +4119,47 @@
       <c r="K43" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="L43" s="9" t="n">
+      <c r="L43" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="M43" s="3" t="n">
+      <c r="M43" s="10" t="n">
         <v>17.7</v>
       </c>
-      <c r="N43" s="3" t="n">
+      <c r="N43" s="15" t="n">
         <v>19.4</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>188.1</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q43" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Q43" s="10" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="9" t="n">
+      <c r="R43" s="10" t="n">
         <v>22.3</v>
       </c>
-      <c r="S43" s="3" t="n">
+      <c r="S43" s="15" t="n">
         <v>25.4</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V43" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="V43" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="W43" s="3" t="n">
+      <c r="W43" s="10" t="n">
         <v>22.4</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>53.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>182.8</v>
+        <v>82.8</v>
       </c>
       <c r="Z43" s="3" t="n">
         <v>14.6</v>
@@ -4150,7 +4186,7 @@
       <c r="E44" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F44" s="9" t="n">
+      <c r="F44" s="10" t="n">
         <v>21.5</v>
       </c>
       <c r="G44" s="3" t="n">
@@ -4163,45 +4199,47 @@
         <v>0.8</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="L44" s="9" t="n">
+      <c r="L44" s="10" t="n">
         <v>19.4</v>
       </c>
-      <c r="M44" s="13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>20.1</v>
+      <c r="M44" s="10" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="N44" s="15" t="n">
+        <v>4.1</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>890.1</v>
+        <v>240.1</v>
       </c>
       <c r="P44" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q44" s="3" t="n">
+      <c r="Q44" s="10" t="n">
         <v>22.6</v>
       </c>
-      <c r="R44" s="9" t="n">
+      <c r="R44" s="10" t="n">
         <v>20.3</v>
       </c>
       <c r="S44" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="V44" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="V44" s="10" t="n">
         <v>22.3</v>
       </c>
-      <c r="W44" s="12" t="inlineStr"/>
+      <c r="W44" s="10" t="n">
+        <v>20.2</v>
+      </c>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4219,71 +4257,71 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>168211.1</v>
-      </c>
-      <c r="D45" s="11" t="n">
-        <v>825.1</v>
-      </c>
-      <c r="E45" s="11" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F45" s="11" t="n">
-        <v>51.7</v>
+        <v>1.8</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>174</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>144</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>10.6</v>
+        <v>60.2</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>2637</v>
+        <v>105.6</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>183.3</v>
+        <v>13.3</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="K45" s="11" t="n">
-        <v>28</v>
-      </c>
-      <c r="L45" s="11" t="n">
-        <v>1910.4</v>
-      </c>
-      <c r="M45" s="14" t="inlineStr"/>
+      <c r="K45" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="L45" s="9" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="M45" s="10" t="n">
+        <v>109.2</v>
+      </c>
       <c r="N45" s="3" t="n">
-        <v>10092105.9</v>
+        <v>1218.1</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>34.2</v>
+        <v>534.4</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>140.4</v>
       </c>
-      <c r="Q45" s="11" t="n">
-        <v>257.5</v>
-      </c>
-      <c r="R45" s="11" t="n">
-        <v>129.2</v>
+      <c r="Q45" s="10" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="R45" s="10" t="n">
+        <v>129.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>1382</v>
+        <v>138.5</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V45" s="11" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="W45" s="11" t="n">
-        <v>182.2</v>
-      </c>
-      <c r="X45" s="3" t="n">
-        <v>24.7</v>
-      </c>
+        <v>1121.5</v>
+      </c>
+      <c r="V45" s="10" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="W45" s="9" t="n">
+        <v>231.2</v>
+      </c>
+      <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>81.5</v>
+        <v>48390.4</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>5.8</v>
@@ -4304,20 +4342,20 @@
       <c r="C46" s="3" t="n">
         <v>311.7</v>
       </c>
-      <c r="D46" s="11" t="n">
+      <c r="D46" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="E46" s="11" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F46" s="9" t="n">
+      <c r="E46" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F46" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="G46" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H46" s="13" t="n">
-        <v>17.6</v>
+      <c r="G46" s="15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>167.6</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>2.2</v>
@@ -4325,28 +4363,26 @@
       <c r="J46" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L46" s="9" t="n">
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="10" t="n">
         <v>19.4</v>
       </c>
-      <c r="M46" s="3" t="n">
+      <c r="M46" s="10" t="n">
         <v>18.2</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>89</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q46" s="11" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="R46" s="9" t="n">
+      <c r="Q46" s="10" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R46" s="10" t="n">
         <v>21.6</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4358,13 +4394,13 @@
       <c r="U46" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="V46" s="11" t="n">
+      <c r="V46" s="10" t="n">
         <v>24.2</v>
       </c>
-      <c r="W46" s="11" t="n">
+      <c r="W46" s="10" t="n">
         <v>21.8</v>
       </c>
-      <c r="X46" s="3" t="n">
+      <c r="X46" s="15" t="n">
         <v>24.7</v>
       </c>
       <c r="Y46" s="3" t="inlineStr"/>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,7 +146,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -165,18 +159,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -792,14 +774,14 @@
       <c r="C4" s="3" t="n">
         <v>43.7</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="9" t="n">
         <v>31.2</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="F4" s="11" t="n">
-        <v>12.42</v>
+      <c r="F4" s="9" t="n">
+        <v>24.2</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>14</v>
@@ -816,10 +798,10 @@
       <c r="K4" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="L4" s="10" t="n">
+      <c r="L4" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="M4" s="10" t="n">
+      <c r="M4" s="9" t="n">
         <v>16.2</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -831,10 +813,10 @@
       <c r="P4" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q4" s="10" t="n">
+      <c r="Q4" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="R4" s="10" t="n">
+      <c r="R4" s="9" t="n">
         <v>24.4</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -846,10 +828,10 @@
       <c r="U4" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="V4" s="10" t="n">
+      <c r="V4" s="9" t="n">
         <v>27.7</v>
       </c>
-      <c r="W4" s="10" t="n">
+      <c r="W4" s="9" t="n">
         <v>24</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
@@ -871,32 +853,32 @@
       <c r="C5" s="3" t="n">
         <v>62.1</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="9" t="n">
         <v>24.4</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="9" t="n">
         <v>21.5</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>8.6</v>
+        <v>1.6</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="L5" s="10" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="L5" s="9" t="n">
         <v>19.1</v>
       </c>
-      <c r="M5" s="10" t="n">
+      <c r="M5" s="9" t="n">
         <v>18</v>
       </c>
       <c r="N5" s="3" t="n">
@@ -908,13 +890,13 @@
       <c r="P5" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q5" s="10" t="n">
+      <c r="Q5" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="R5" s="10" t="n">
+      <c r="R5" s="9" t="n">
         <v>19.1</v>
       </c>
-      <c r="S5" s="15" t="n">
+      <c r="S5" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="T5" s="3" t="n">
@@ -923,10 +905,10 @@
       <c r="U5" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="V5" s="10" t="n">
+      <c r="V5" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="W5" s="10" t="n">
+      <c r="W5" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -954,13 +936,13 @@
       <c r="C6" s="3" t="n">
         <v>421.6</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <v>31.4</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F6" s="15" t="n">
+      <c r="F6" s="9" t="n">
         <v>25.6</v>
       </c>
       <c r="G6" s="3" t="n">
@@ -975,13 +957,13 @@
       <c r="J6" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K6" s="15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L6" s="10" t="n">
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="9" t="n">
         <v>20.3</v>
       </c>
-      <c r="M6" s="10" t="n">
+      <c r="M6" s="9" t="n">
         <v>19</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -993,10 +975,10 @@
       <c r="P6" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q6" s="10" t="n">
+      <c r="Q6" s="9" t="n">
         <v>29.8</v>
       </c>
-      <c r="R6" s="10" t="n">
+      <c r="R6" s="9" t="n">
         <v>23.9</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -1008,10 +990,10 @@
       <c r="U6" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="V6" s="10" t="n">
+      <c r="V6" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="W6" s="10" t="n">
+      <c r="W6" s="9" t="n">
         <v>23.2</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1039,17 +1021,17 @@
       <c r="C7" s="3" t="n">
         <v>43.7</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="E7" s="12" t="inlineStr"/>
-      <c r="F7" s="3" t="n">
+      <c r="E7" s="11" t="inlineStr"/>
+      <c r="F7" s="9" t="n">
         <v>25</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="15" t="n">
+      <c r="H7" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="I7" s="3" t="n">
@@ -1059,42 +1041,42 @@
         <v>4.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" s="10" t="n">
+      <c r="M7" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="N7" s="15" t="n">
+      <c r="N7" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>872.6</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q7" s="10" t="n">
+      <c r="Q7" s="9" t="n">
         <v>31.9</v>
       </c>
-      <c r="R7" s="10" t="n">
+      <c r="R7" s="9" t="n">
         <v>23.9</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>152.1</v>
+        <v>52.1</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="V7" s="10" t="n">
+      <c r="V7" s="9" t="n">
         <v>27.6</v>
       </c>
-      <c r="W7" s="10" t="n">
+      <c r="W7" s="9" t="n">
         <v>24.1</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1120,18 +1102,18 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="D8" s="10" t="n">
+        <v>297.2</v>
+      </c>
+      <c r="D8" s="9" t="n">
         <v>32.6</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="10" t="n">
         <v>4.1</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="G8" s="15" t="n">
+      <c r="G8" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="H8" s="3" t="n">
@@ -1146,10 +1128,10 @@
       <c r="K8" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="L8" s="10" t="n">
+      <c r="L8" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="M8" s="10" t="n">
+      <c r="M8" s="9" t="n">
         <v>18.6</v>
       </c>
       <c r="N8" s="3" t="n">
@@ -1161,10 +1143,10 @@
       <c r="P8" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q8" s="10" t="n">
+      <c r="Q8" s="9" t="n">
         <v>26.6</v>
       </c>
-      <c r="R8" s="10" t="n">
+      <c r="R8" s="9" t="n">
         <v>26</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1176,17 +1158,17 @@
       <c r="U8" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="V8" s="10" t="n">
+      <c r="V8" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="W8" s="10" t="n">
+      <c r="W8" s="9" t="n">
         <v>22.8</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>175.2</v>
+        <v>75.2</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>27</v>
@@ -1207,14 +1189,14 @@
       <c r="C9" s="3" t="n">
         <v>166.6</v>
       </c>
-      <c r="D9" s="9" t="n">
-        <v>852.6</v>
-      </c>
-      <c r="E9" s="9" t="n">
+      <c r="D9" s="8" t="n">
+        <v>252.6</v>
+      </c>
+      <c r="E9" s="8" t="n">
         <v>92.5</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>822.5</v>
+        <v>122.5</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>6</v>
@@ -1228,13 +1210,13 @@
       <c r="J9" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="K9" s="9" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="L9" s="10" t="n">
+      <c r="K9" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="L9" s="9" t="n">
         <v>94.3</v>
       </c>
-      <c r="M9" s="10" t="n">
+      <c r="M9" s="9" t="n">
         <v>87.8</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1246,11 +1228,11 @@
       <c r="P9" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="Q9" s="10" t="n">
+      <c r="Q9" s="9" t="n">
         <v>138.8</v>
       </c>
       <c r="R9" s="9" t="n">
-        <v>1617.3</v>
+        <v>117.3</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>131.9</v>
@@ -1261,10 +1243,10 @@
       <c r="U9" s="3" t="n">
         <v>58.5</v>
       </c>
-      <c r="V9" s="10" t="n">
+      <c r="V9" s="9" t="n">
         <v>126.1</v>
       </c>
-      <c r="W9" s="10" t="n">
+      <c r="W9" s="9" t="n">
         <v>113</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1274,7 +1256,7 @@
         <v>402.4</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>32.8</v>
+        <v>2.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1292,10 +1274,10 @@
       <c r="C10" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="9" t="n">
         <v>30.5</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="8" t="n">
         <v>18.5</v>
       </c>
       <c r="F10" s="9" t="n">
@@ -1316,13 +1298,13 @@
       <c r="K10" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L10" s="10" t="n">
+      <c r="L10" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="N10" s="15" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="N10" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="O10" s="3" t="n">
@@ -1331,10 +1313,10 @@
       <c r="P10" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q10" s="10" t="n">
+      <c r="Q10" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="R10" s="10" t="n">
+      <c r="R10" s="9" t="n">
         <v>23.5</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1346,10 +1328,10 @@
       <c r="U10" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="V10" s="10" t="n">
+      <c r="V10" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="W10" s="10" t="n">
+      <c r="W10" s="9" t="n">
         <v>22.6</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1377,13 +1359,13 @@
       <c r="C11" s="3" t="n">
         <v>44.5</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="9" t="n">
         <v>28.7</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F11" s="9" t="n">
         <v>24.3</v>
       </c>
       <c r="G11" s="3" t="n">
@@ -1401,10 +1383,10 @@
       <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="10" t="n">
+      <c r="L11" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="9" t="n">
         <v>18.7</v>
       </c>
       <c r="N11" s="3" t="n">
@@ -1416,14 +1398,14 @@
       <c r="P11" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q11" s="10" t="n">
+      <c r="Q11" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="R11" s="10" t="n">
+      <c r="R11" s="9" t="n">
         <v>25.8</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>31.9</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>850.1</v>
@@ -1431,10 +1413,10 @@
       <c r="U11" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="V11" s="10" t="n">
+      <c r="V11" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="W11" s="10" t="n">
+      <c r="W11" s="9" t="n">
         <v>24.7</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1462,20 +1444,20 @@
       <c r="C12" s="3" t="n">
         <v>38.3</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="9" t="n">
         <v>28.1</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F12" s="9" t="n">
         <v>23.9</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>8.5</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>2.9</v>
@@ -1486,10 +1468,10 @@
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="10" t="n">
+      <c r="L12" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="9" t="n">
         <v>19.3</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1499,12 +1481,12 @@
         <v>88.40000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="Q12" s="10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q12" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="R12" s="10" t="n">
+      <c r="R12" s="9" t="n">
         <v>25.2</v>
       </c>
       <c r="S12" s="3" t="n">
@@ -1516,17 +1498,17 @@
       <c r="U12" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="V12" s="10" t="n">
+      <c r="V12" s="9" t="n">
         <v>24.7</v>
       </c>
-      <c r="W12" s="10" t="n">
+      <c r="W12" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="X12" s="15" t="n">
+      <c r="X12" s="3" t="n">
         <v>30.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>1197.7</v>
+        <v>97.7</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>0.7</v>
@@ -1545,15 +1527,15 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>235.6</v>
-      </c>
-      <c r="D13" s="10" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="D13" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="F13" s="9" t="n">
         <v>25.5</v>
       </c>
       <c r="G13" s="3" t="n">
@@ -1571,10 +1553,10 @@
       <c r="K13" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L13" s="10" t="n">
+      <c r="L13" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="9" t="n">
         <v>18.8</v>
       </c>
       <c r="N13" s="3" t="n">
@@ -1586,10 +1568,10 @@
       <c r="P13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q13" s="10" t="n">
+      <c r="Q13" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="R13" s="10" t="n">
+      <c r="R13" s="9" t="n">
         <v>26.3</v>
       </c>
       <c r="S13" s="3" t="n">
@@ -1601,10 +1583,10 @@
       <c r="U13" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="V13" s="10" t="n">
+      <c r="V13" s="9" t="n">
         <v>24.7</v>
       </c>
-      <c r="W13" s="10" t="n">
+      <c r="W13" s="9" t="n">
         <v>23.8</v>
       </c>
       <c r="X13" s="3" t="n">
@@ -1632,13 +1614,13 @@
       <c r="C14" s="3" t="n">
         <v>37.4</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="9" t="n">
         <v>32.5</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="F14" s="9" t="n">
         <v>26.1</v>
       </c>
       <c r="G14" s="3" t="n">
@@ -1656,10 +1638,10 @@
       <c r="K14" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="L14" s="10" t="n">
+      <c r="L14" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="M14" s="15" t="n">
+      <c r="M14" s="9" t="n">
         <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1671,10 +1653,10 @@
       <c r="P14" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q14" s="10" t="n">
+      <c r="Q14" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="R14" s="10" t="n">
+      <c r="R14" s="9" t="n">
         <v>22.6</v>
       </c>
       <c r="S14" s="3" t="n">
@@ -1683,16 +1665,16 @@
       <c r="T14" s="3" t="n">
         <v>50.9</v>
       </c>
-      <c r="U14" s="15" t="n">
+      <c r="U14" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="V14" s="10" t="n">
+      <c r="V14" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="W14" s="10" t="n">
+      <c r="W14" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="X14" s="15" t="n">
+      <c r="X14" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="Y14" s="3" t="n">
@@ -1715,15 +1697,15 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>143.3</v>
-      </c>
-      <c r="D15" s="10" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="D15" s="9" t="n">
         <v>29.5</v>
       </c>
-      <c r="E15" s="11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F15" s="10" t="n">
+      <c r="E15" s="9" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F15" s="9" t="n">
         <v>24.9</v>
       </c>
       <c r="G15" s="3" t="n">
@@ -1741,11 +1723,11 @@
       <c r="K15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="10" t="n">
+      <c r="L15" s="9" t="n">
         <v>20.4</v>
       </c>
-      <c r="M15" s="15" t="n">
-        <v>29.1</v>
+      <c r="M15" s="9" t="n">
+        <v>19.1</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>21.3</v>
@@ -1756,10 +1738,10 @@
       <c r="P15" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q15" s="10" t="n">
+      <c r="Q15" s="9" t="n">
         <v>28.5</v>
       </c>
-      <c r="R15" s="10" t="n">
+      <c r="R15" s="9" t="n">
         <v>23.1</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1771,13 +1753,13 @@
       <c r="U15" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="V15" s="10" t="n">
+      <c r="V15" s="9" t="n">
         <v>24.5</v>
       </c>
-      <c r="W15" s="10" t="n">
+      <c r="W15" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="X15" s="15" t="n">
+      <c r="X15" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="Y15" s="3" t="n">
@@ -1800,35 +1782,35 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1992.8</v>
-      </c>
-      <c r="D16" s="10" t="n">
+        <v>992.7</v>
+      </c>
+      <c r="D16" s="9" t="n">
         <v>149.9</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="F16" s="10" t="n">
+      <c r="F16" s="9" t="n">
         <v>124.7</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>508.1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>115.8</v>
-      </c>
-      <c r="K16" s="16" t="inlineStr"/>
-      <c r="L16" s="9" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="K16" s="12" t="inlineStr"/>
+      <c r="L16" s="8" t="n">
         <v>1.9</v>
       </c>
       <c r="M16" s="9" t="n">
-        <v>194.6</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>105.2</v>
@@ -1839,14 +1821,14 @@
       <c r="P16" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="Q16" s="10" t="n">
+      <c r="Q16" s="9" t="n">
         <v>142.8</v>
       </c>
-      <c r="R16" s="10" t="n">
+      <c r="R16" s="9" t="n">
         <v>123</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>1042.5</v>
+        <v>142.5</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>368.7</v>
@@ -1854,10 +1836,10 @@
       <c r="U16" s="3" t="n">
         <v>53.1</v>
       </c>
-      <c r="V16" s="10" t="n">
+      <c r="V16" s="9" t="n">
         <v>120.8</v>
       </c>
-      <c r="W16" s="10" t="n">
+      <c r="W16" s="9" t="n">
         <v>115.1</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1883,22 +1865,22 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>399.8</v>
-      </c>
-      <c r="D17" s="10" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="D17" s="9" t="n">
         <v>30</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="9" t="n">
         <v>24.9</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>28.1</v>
+        <v>18.1</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>2.2</v>
@@ -1906,10 +1888,10 @@
       <c r="J17" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K17" s="15" t="n">
-        <v>11551.5</v>
-      </c>
-      <c r="L17" s="10" t="n">
+      <c r="K17" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L17" s="9" t="n">
         <v>20.2</v>
       </c>
       <c r="M17" s="9" t="n">
@@ -1924,25 +1906,25 @@
       <c r="P17" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q17" s="10" t="n">
+      <c r="Q17" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="R17" s="10" t="n">
+      <c r="R17" s="9" t="n">
         <v>24.6</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>173.7</v>
+        <v>73.7</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V17" s="10" t="n">
+      <c r="V17" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="W17" s="10" t="n">
+      <c r="W17" s="9" t="n">
         <v>23</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1970,23 +1952,23 @@
       <c r="C18" s="3" t="n">
         <v>431.1</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="9" t="n">
         <v>30.8</v>
       </c>
-      <c r="E18" s="10" t="n">
+      <c r="E18" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="F18" s="9" t="n">
         <v>24.9</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>11.3</v>
+        <v>11.8</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>14.2</v>
+        <v>17.2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>4</v>
@@ -1994,25 +1976,25 @@
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="10" t="n">
+      <c r="L18" s="9" t="n">
         <v>19.2</v>
       </c>
-      <c r="M18" s="3" t="n">
-        <v>20.8</v>
+      <c r="M18" s="9" t="n">
+        <v>17.7</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>13.3</v>
+        <v>19.3</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>87</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q18" s="10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q18" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="9" t="n">
         <v>23.1</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -2024,11 +2006,11 @@
       <c r="U18" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V18" s="10" t="n">
+      <c r="V18" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="W18" s="10" t="n">
-        <v>25.6</v>
+      <c r="W18" s="9" t="n">
+        <v>25</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>31</v>
@@ -2053,22 +2035,22 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2223.4</v>
-      </c>
-      <c r="D19" s="10" t="n">
+        <v>223.4</v>
+      </c>
+      <c r="D19" s="9" t="n">
         <v>32.5</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="F19" s="9" t="n">
         <v>25.5</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>18.4</v>
+        <v>1.4</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>2.6</v>
@@ -2079,10 +2061,10 @@
       <c r="K19" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="L19" s="10" t="n">
+      <c r="L19" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="M19" s="15" t="n">
+      <c r="M19" s="9" t="n">
         <v>18.2</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2094,10 +2076,10 @@
       <c r="P19" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q19" s="10" t="n">
+      <c r="Q19" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" s="9" t="n">
         <v>24.2</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2109,10 +2091,10 @@
       <c r="U19" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="V19" s="10" t="n">
+      <c r="V19" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="W19" s="10" t="n">
+      <c r="W19" s="9" t="n">
         <v>23.3</v>
       </c>
       <c r="X19" s="3" t="n">
@@ -2140,34 +2122,34 @@
       <c r="C20" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="E20" s="10" t="n">
+      <c r="E20" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="F20" s="10" t="n">
+      <c r="F20" s="9" t="n">
         <v>23.5</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>7.4</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="L20" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="L20" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="9" t="n">
         <v>18.8</v>
       </c>
       <c r="N20" s="3" t="n">
@@ -2179,11 +2161,11 @@
       <c r="P20" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q20" s="10" t="n">
+      <c r="Q20" s="9" t="n">
         <v>25.5</v>
       </c>
-      <c r="R20" s="11" t="n">
-        <v>24.15</v>
+      <c r="R20" s="9" t="n">
+        <v>21.5</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>23.1</v>
@@ -2194,10 +2176,10 @@
       <c r="U20" s="3" t="n">
         <v>9.5</v>
       </c>
-      <c r="V20" s="10" t="n">
+      <c r="V20" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="W20" s="10" t="n">
+      <c r="W20" s="9" t="n">
         <v>20.5</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2225,13 +2207,13 @@
       <c r="C21" s="3" t="n">
         <v>43.3</v>
       </c>
-      <c r="D21" s="10" t="n">
+      <c r="D21" s="9" t="n">
         <v>30.8</v>
       </c>
-      <c r="E21" s="10" t="n">
+      <c r="E21" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="F21" s="10" t="n">
+      <c r="F21" s="9" t="n">
         <v>24.6</v>
       </c>
       <c r="G21" s="3" t="n">
@@ -2249,10 +2231,10 @@
       <c r="K21" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L21" s="10" t="n">
+      <c r="L21" s="9" t="n">
         <v>18.8</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="9" t="n">
         <v>17.3</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2264,25 +2246,25 @@
       <c r="P21" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q21" s="10" t="n">
+      <c r="Q21" s="9" t="n">
         <v>30.1</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" s="9" t="n">
         <v>22.2</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="V21" s="10" t="n">
+      <c r="V21" s="9" t="n">
         <v>24.3</v>
       </c>
-      <c r="W21" s="10" t="n">
+      <c r="W21" s="9" t="n">
         <v>22.4</v>
       </c>
       <c r="X21" s="3" t="n">
@@ -2292,7 +2274,7 @@
         <v>85</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2308,18 +2290,18 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2374.6</v>
-      </c>
-      <c r="D22" s="10" t="n">
+        <v>374</v>
+      </c>
+      <c r="D22" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="E22" s="10" t="n">
+      <c r="E22" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="F22" s="10" t="n">
-        <v>24.75</v>
-      </c>
-      <c r="G22" s="15" t="n">
+      <c r="F22" s="9" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2334,11 +2316,11 @@
       <c r="K22" s="3" t="n">
         <v>3.7</v>
       </c>
-      <c r="L22" s="10" t="n">
+      <c r="L22" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="M22" s="15" t="n">
-        <v>26.2</v>
+      <c r="M22" s="9" t="n">
+        <v>16.2</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>17.5</v>
@@ -2349,25 +2331,25 @@
       <c r="P22" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q22" s="10" t="n">
+      <c r="Q22" s="9" t="n">
         <v>30.2</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="9" t="n">
         <v>23.3</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>256.4</v>
+        <v>56.4</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="V22" s="10" t="n">
+      <c r="V22" s="9" t="n">
         <v>21.2</v>
       </c>
-      <c r="W22" s="10" t="n">
+      <c r="W22" s="9" t="n">
         <v>19.5</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2393,33 +2375,33 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>192.5</v>
-      </c>
-      <c r="D23" s="10" t="n">
+        <v>1925.5</v>
+      </c>
+      <c r="D23" s="9" t="n">
         <v>153.1</v>
       </c>
-      <c r="E23" s="10" t="n">
+      <c r="E23" s="9" t="n">
         <v>92.8</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>123</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>60.5</v>
+        <v>60.3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>85</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="K23" s="9" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="L23" s="10" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="K23" s="8" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="L23" s="9" t="n">
         <v>95.2</v>
       </c>
       <c r="M23" s="9" t="n">
@@ -2432,9 +2414,9 @@
         <v>437.2</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>113.7</v>
-      </c>
-      <c r="Q23" s="10" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="Q23" s="9" t="n">
         <v>146.2</v>
       </c>
       <c r="R23" s="9" t="n">
@@ -2444,12 +2426,12 @@
         <v>119</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>2895.2</v>
+        <v>295.2</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="V23" s="10" t="n">
+      <c r="V23" s="9" t="n">
         <v>122.2</v>
       </c>
       <c r="W23" s="9" t="n">
@@ -2459,10 +2441,10 @@
         <v>126.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>411</v>
+        <v>11</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>0.8</v>
+        <v>8.1</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2478,22 +2460,22 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1398.5</v>
-      </c>
-      <c r="D24" s="10" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="D24" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="E24" s="10" t="n">
+      <c r="E24" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="F24" s="9" t="n">
         <v>24.6</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="H24" s="15" t="n">
-        <v>67.59999999999999</v>
+      <c r="H24" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
@@ -2504,14 +2486,14 @@
       <c r="K24" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L24" s="10" t="n">
+      <c r="L24" s="9" t="n">
         <v>19</v>
       </c>
       <c r="M24" s="9" t="n">
         <v>17.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>12.3</v>
+        <v>19.3</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>87.40000000000001</v>
@@ -2519,7 +2501,7 @@
       <c r="P24" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q24" s="10" t="n">
+      <c r="Q24" s="9" t="n">
         <v>29.2</v>
       </c>
       <c r="R24" s="9" t="n">
@@ -2532,12 +2514,12 @@
         <v>59</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="V24" s="10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V24" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="W24" s="10" t="n">
+      <c r="W24" s="9" t="n">
         <v>22.1</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2563,15 +2545,15 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>2374</v>
+        <v>374</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>32.1</v>
       </c>
-      <c r="E25" s="11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F25" s="10" t="n">
+      <c r="E25" s="9" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F25" s="9" t="n">
         <v>25.7</v>
       </c>
       <c r="G25" s="3" t="n">
@@ -2589,10 +2571,10 @@
       <c r="K25" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L25" s="10" t="n">
+      <c r="L25" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="M25" s="10" t="n">
+      <c r="M25" s="9" t="n">
         <v>18.4</v>
       </c>
       <c r="N25" s="3" t="n">
@@ -2602,16 +2584,16 @@
         <v>90</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="Q25" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q25" s="9" t="n">
         <v>31.3</v>
       </c>
-      <c r="R25" s="10" t="n">
+      <c r="R25" s="9" t="n">
         <v>24.3</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>22.9</v>
+        <v>25.9</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>56.9</v>
@@ -2619,20 +2601,20 @@
       <c r="U25" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="V25" s="10" t="n">
+      <c r="V25" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="W25" s="10" t="n">
+      <c r="W25" s="9" t="n">
         <v>20.9</v>
       </c>
-      <c r="X25" s="15" t="n">
+      <c r="X25" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>174.8</v>
+        <v>74.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>17.2</v>
+        <v>7.2</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2653,10 +2635,10 @@
       <c r="D26" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="F26" s="10" t="n">
+      <c r="F26" s="9" t="n">
         <v>24.7</v>
       </c>
       <c r="G26" s="3" t="n">
@@ -2674,10 +2656,10 @@
       <c r="K26" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L26" s="10" t="n">
+      <c r="L26" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="M26" s="10" t="n">
+      <c r="M26" s="9" t="n">
         <v>17.6</v>
       </c>
       <c r="N26" s="3" t="n">
@@ -2689,10 +2671,10 @@
       <c r="P26" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q26" s="10" t="n">
+      <c r="Q26" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="R26" s="10" t="n">
+      <c r="R26" s="9" t="n">
         <v>21.8</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2702,22 +2684,22 @@
         <v>80</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="V26" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V26" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="W26" s="10" t="n">
+      <c r="W26" s="9" t="n">
         <v>21.8</v>
       </c>
-      <c r="X26" s="15" t="n">
+      <c r="X26" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>17.6</v>
+        <v>7.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2733,25 +2715,25 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1354.4</v>
-      </c>
-      <c r="D27" s="11" t="n">
+        <v>354.8</v>
+      </c>
+      <c r="D27" s="10" t="n">
         <v>2.2</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="9" t="n">
         <v>19.4</v>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="F27" s="9" t="n">
         <v>23.8</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>18.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>2.9</v>
@@ -2759,25 +2741,25 @@
       <c r="K27" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="L27" s="10" t="n">
+      <c r="L27" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="M27" s="10" t="n">
+      <c r="M27" s="9" t="n">
         <v>18.8</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>88.5</v>
+        <v>87.5</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q27" s="10" t="n">
+      <c r="Q27" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="R27" s="10" t="n">
+      <c r="R27" s="9" t="n">
         <v>21.6</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2786,13 +2768,13 @@
       <c r="T27" s="3" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="U27" s="15" t="n">
+      <c r="U27" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V27" s="10" t="n">
+      <c r="V27" s="9" t="n">
         <v>23.2</v>
       </c>
-      <c r="W27" s="10" t="n">
+      <c r="W27" s="9" t="n">
         <v>20.8</v>
       </c>
       <c r="X27" s="3" t="n">
@@ -2823,10 +2805,10 @@
       <c r="D28" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="F28" s="10" t="n">
+      <c r="F28" s="9" t="n">
         <v>25</v>
       </c>
       <c r="G28" s="3" t="n">
@@ -2844,10 +2826,10 @@
       <c r="K28" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="L28" s="10" t="n">
+      <c r="L28" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M28" s="10" t="n">
+      <c r="M28" s="9" t="n">
         <v>19.2</v>
       </c>
       <c r="N28" s="3" t="n">
@@ -2859,10 +2841,10 @@
       <c r="P28" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q28" s="10" t="n">
+      <c r="Q28" s="9" t="n">
         <v>28.2</v>
       </c>
-      <c r="R28" s="10" t="n">
+      <c r="R28" s="9" t="n">
         <v>23</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2874,10 +2856,10 @@
       <c r="U28" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="V28" s="10" t="n">
+      <c r="V28" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="W28" s="10" t="n">
+      <c r="W28" s="9" t="n">
         <v>23.6</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2908,34 +2890,34 @@
       <c r="D29" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="9" t="n">
         <v>20.3</v>
       </c>
-      <c r="F29" s="10" t="n">
+      <c r="F29" s="9" t="n">
         <v>24.9</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.7</v>
+        <v>11.7</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L29" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L29" s="9" t="n">
         <v>20.3</v>
       </c>
-      <c r="M29" s="10" t="n">
+      <c r="M29" s="9" t="n">
         <v>19.2</v>
       </c>
-      <c r="N29" s="15" t="n">
+      <c r="N29" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="O29" s="3" t="n">
@@ -2944,10 +2926,10 @@
       <c r="P29" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q29" s="10" t="n">
+      <c r="Q29" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="10" t="n">
+      <c r="R29" s="9" t="n">
         <v>23</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2959,10 +2941,10 @@
       <c r="U29" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="V29" s="10" t="n">
+      <c r="V29" s="9" t="n">
         <v>25.5</v>
       </c>
-      <c r="W29" s="10" t="n">
+      <c r="W29" s="9" t="n">
         <v>23</v>
       </c>
       <c r="X29" s="3" t="n">
@@ -2988,22 +2970,22 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1856.4</v>
-      </c>
-      <c r="D30" s="9" t="n">
+        <v>1856</v>
+      </c>
+      <c r="D30" s="8" t="n">
         <v>150.3</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" s="8" t="n">
         <v>91.2</v>
       </c>
-      <c r="F30" s="10" t="n">
+      <c r="F30" s="9" t="n">
         <v>124.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>152.5</v>
+        <v>52.5</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>191.7</v>
+        <v>91.7</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>10</v>
@@ -3011,13 +2993,13 @@
       <c r="J30" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="K30" s="9" t="n">
+      <c r="K30" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="L30" s="10" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="M30" s="10" t="n">
+      <c r="L30" s="8" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="M30" s="9" t="n">
         <v>93.2</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3029,10 +3011,10 @@
       <c r="P30" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q30" s="10" t="n">
+      <c r="Q30" s="9" t="n">
         <v>138.5</v>
       </c>
-      <c r="R30" s="10" t="n">
+      <c r="R30" s="9" t="n">
         <v>113.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3042,12 +3024,12 @@
         <v>332.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="V30" s="10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="V30" s="9" t="n">
         <v>123.1</v>
       </c>
-      <c r="W30" s="10" t="n">
+      <c r="W30" s="9" t="n">
         <v>110.1</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3075,34 +3057,34 @@
       <c r="C31" s="3" t="n">
         <v>37.1</v>
       </c>
-      <c r="D31" s="9" t="n">
-        <v>20.1</v>
+      <c r="D31" s="8" t="n">
+        <v>30.1</v>
       </c>
       <c r="E31" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="F31" s="10" t="n">
+      <c r="F31" s="9" t="n">
         <v>24.8</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H31" s="15" t="n">
+      <c r="H31" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>13.2</v>
+        <v>3.2</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L31" s="10" t="n">
+      <c r="L31" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="M31" s="10" t="n">
+      <c r="M31" s="9" t="n">
         <v>18.6</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3114,25 +3096,25 @@
       <c r="P31" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q31" s="10" t="n">
+      <c r="Q31" s="9" t="n">
         <v>27.7</v>
       </c>
-      <c r="R31" s="10" t="n">
+      <c r="R31" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="S31" s="15" t="n">
+      <c r="S31" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>66</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="V31" s="10" t="n">
+      <c r="V31" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="W31" s="10" t="n">
+      <c r="W31" s="9" t="n">
         <v>22</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3158,39 +3140,39 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="D32" s="11" t="n">
-        <v>35.28</v>
-      </c>
-      <c r="E32" s="10" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E32" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="F32" s="11" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="G32" s="15" t="n">
+      <c r="F32" s="9" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G32" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="10" t="n">
+      <c r="L32" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M32" s="10" t="n">
+      <c r="M32" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="N32" s="15" t="n">
+      <c r="N32" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="O32" s="3" t="n">
@@ -3199,10 +3181,10 @@
       <c r="P32" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="Q32" s="10" t="n">
+      <c r="Q32" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="R32" s="10" t="n">
+      <c r="R32" s="9" t="n">
         <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3214,17 +3196,17 @@
       <c r="U32" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="V32" s="10" t="n">
+      <c r="V32" s="9" t="n">
         <v>28.2</v>
       </c>
-      <c r="W32" s="10" t="n">
+      <c r="W32" s="9" t="n">
         <v>23.7</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>11.8</v>
@@ -3243,15 +3225,15 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>397.9</v>
-      </c>
-      <c r="D33" s="3" t="n">
+        <v>397</v>
+      </c>
+      <c r="D33" s="9" t="n">
         <v>33.7</v>
       </c>
-      <c r="E33" s="10" t="n">
+      <c r="E33" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="F33" s="3" t="n">
+      <c r="F33" s="9" t="n">
         <v>26.7</v>
       </c>
       <c r="G33" s="3" t="n">
@@ -3266,13 +3248,13 @@
       <c r="J33" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="10" t="n">
+      <c r="L33" s="9" t="n">
         <v>20.9</v>
       </c>
-      <c r="M33" s="10" t="n">
+      <c r="M33" s="9" t="n">
         <v>19.5</v>
       </c>
       <c r="N33" s="3" t="n">
@@ -3284,25 +3266,25 @@
       <c r="P33" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q33" s="10" t="n">
+      <c r="Q33" s="9" t="n">
         <v>32.9</v>
       </c>
-      <c r="R33" s="10" t="n">
+      <c r="R33" s="9" t="n">
         <v>23.9</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>147.7</v>
+        <v>47.7</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="V33" s="10" t="n">
+      <c r="V33" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="W33" s="10" t="n">
+      <c r="W33" s="9" t="n">
         <v>22.8</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3312,7 +3294,7 @@
         <v>77.59999999999999</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>17.4</v>
+        <v>7.4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3328,22 +3310,22 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1362.4</v>
-      </c>
-      <c r="D34" s="3" t="n">
+        <v>362.4</v>
+      </c>
+      <c r="D34" s="9" t="n">
         <v>30.4</v>
       </c>
-      <c r="E34" s="10" t="n">
+      <c r="E34" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="F34" s="3" t="n">
+      <c r="F34" s="9" t="n">
         <v>25.3</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>2.2</v>
@@ -3351,13 +3333,13 @@
       <c r="J34" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="L34" s="10" t="n">
+      <c r="L34" s="9" t="n">
         <v>20.4</v>
       </c>
-      <c r="M34" s="10" t="n">
+      <c r="M34" s="9" t="n">
         <v>19</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -3369,10 +3351,10 @@
       <c r="P34" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q34" s="10" t="n">
+      <c r="Q34" s="9" t="n">
         <v>26.1</v>
       </c>
-      <c r="R34" s="10" t="n">
+      <c r="R34" s="9" t="n">
         <v>23.2</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3384,17 +3366,17 @@
       <c r="U34" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="V34" s="10" t="n">
+      <c r="V34" s="9" t="n">
         <v>25.5</v>
       </c>
-      <c r="W34" s="10" t="n">
+      <c r="W34" s="9" t="n">
         <v>23.3</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>5.4</v>
@@ -3415,13 +3397,13 @@
       <c r="C35" s="3" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="D35" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="E35" s="10" t="n">
+      <c r="E35" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="F35" s="3" t="n">
+      <c r="F35" s="9" t="n">
         <v>22.7</v>
       </c>
       <c r="G35" s="3" t="n">
@@ -3436,17 +3418,17 @@
       <c r="J35" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="L35" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="M35" s="10" t="n">
+      <c r="L35" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="M35" s="9" t="n">
         <v>19.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>20</v>
+        <v>21.5</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>85.40000000000001</v>
@@ -3454,10 +3436,10 @@
       <c r="P35" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q35" s="10" t="n">
+      <c r="Q35" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="R35" s="10" t="n">
+      <c r="R35" s="9" t="n">
         <v>21.2</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3469,10 +3451,10 @@
       <c r="U35" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="V35" s="10" t="n">
+      <c r="V35" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="W35" s="10" t="n">
+      <c r="W35" s="9" t="n">
         <v>20.3</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3500,19 +3482,19 @@
       <c r="C36" s="3" t="n">
         <v>398.9</v>
       </c>
-      <c r="D36" s="15" t="n">
+      <c r="D36" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="E36" s="10" t="n">
+      <c r="E36" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="F36" s="3" t="n">
+      <c r="F36" s="9" t="n">
         <v>24.3</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="H36" s="15" t="n">
+      <c r="H36" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
@@ -3521,13 +3503,13 @@
       <c r="J36" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="10" t="n">
+      <c r="L36" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M36" s="10" t="n">
+      <c r="M36" s="9" t="n">
         <v>19.4</v>
       </c>
       <c r="N36" s="3" t="n">
@@ -3539,10 +3521,10 @@
       <c r="P36" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q36" s="10" t="n">
+      <c r="Q36" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="R36" s="10" t="n">
+      <c r="R36" s="9" t="n">
         <v>23.1</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3554,10 +3536,10 @@
       <c r="U36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V36" s="10" t="n">
+      <c r="V36" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="W36" s="10" t="n">
+      <c r="W36" s="9" t="n">
         <v>22.1</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3583,19 +3565,19 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>168.3</v>
+        <v>1683.5</v>
       </c>
       <c r="D37" s="9" t="n">
         <v>150.1</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E37" s="9" t="n">
         <v>100.9</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>125.5</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>149.2</v>
+        <v>49.2</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>92.40000000000001</v>
@@ -3607,12 +3589,12 @@
         <v>15.7</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>102.8</v>
+        <v>10.2</v>
       </c>
       <c r="L37" s="9" t="n">
         <v>103.5</v>
       </c>
-      <c r="M37" s="10" t="n">
+      <c r="M37" s="9" t="n">
         <v>96.5</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3624,10 +3606,10 @@
       <c r="P37" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="Q37" s="10" t="n">
+      <c r="Q37" s="9" t="n">
         <v>139.6</v>
       </c>
-      <c r="R37" s="10" t="n">
+      <c r="R37" s="9" t="n">
         <v>115.4</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3639,10 +3621,10 @@
       <c r="U37" s="3" t="n">
         <v>65.7</v>
       </c>
-      <c r="V37" s="10" t="n">
+      <c r="V37" s="9" t="n">
         <v>126.1</v>
       </c>
-      <c r="W37" s="10" t="n">
+      <c r="W37" s="9" t="n">
         <v>112.2</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3668,12 +3650,12 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>2326.7</v>
+        <v>336.7</v>
       </c>
       <c r="D38" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="E38" s="10" t="n">
+      <c r="E38" s="9" t="n">
         <v>20.2</v>
       </c>
       <c r="F38" s="9" t="n">
@@ -3686,7 +3668,7 @@
         <v>18.5</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>2.5</v>
+        <v>22.5</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>3.1</v>
@@ -3694,11 +3676,11 @@
       <c r="K38" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L38" s="10" t="n">
+      <c r="L38" s="9" t="n">
         <v>20.7</v>
       </c>
       <c r="M38" s="9" t="n">
-        <v>1.9</v>
+        <v>19.3</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>21.4</v>
@@ -3709,10 +3691,10 @@
       <c r="P38" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q38" s="10" t="n">
+      <c r="Q38" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="R38" s="10" t="n">
+      <c r="R38" s="9" t="n">
         <v>23.1</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3724,10 +3706,10 @@
       <c r="U38" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="V38" s="10" t="n">
+      <c r="V38" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="W38" s="10" t="n">
+      <c r="W38" s="9" t="n">
         <v>22.4</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3753,7 +3735,7 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1400.8</v>
+        <v>400.8</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>31.8</v>
@@ -3761,7 +3743,7 @@
       <c r="E39" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="F39" s="10" t="n">
+      <c r="F39" s="9" t="n">
         <v>25.7</v>
       </c>
       <c r="G39" s="3" t="n">
@@ -3774,18 +3756,18 @@
         <v>2.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="10" t="n">
+      <c r="L39" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="M39" s="10" t="n">
+      <c r="M39" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="N39" s="15" t="n">
+      <c r="N39" s="3" t="n">
         <v>22</v>
       </c>
       <c r="O39" s="3" t="n">
@@ -3794,10 +3776,10 @@
       <c r="P39" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q39" s="10" t="n">
+      <c r="Q39" s="9" t="n">
         <v>30.4</v>
       </c>
-      <c r="R39" s="10" t="n">
+      <c r="R39" s="9" t="n">
         <v>23.1</v>
       </c>
       <c r="S39" s="3" t="n">
@@ -3809,10 +3791,10 @@
       <c r="U39" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="V39" s="10" t="n">
+      <c r="V39" s="9" t="n">
         <v>26.8</v>
       </c>
-      <c r="W39" s="10" t="n">
+      <c r="W39" s="9" t="n">
         <v>23.8</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3840,20 +3822,20 @@
       <c r="C40" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="D40" s="11" t="n">
-        <v>84.09999999999999</v>
+      <c r="D40" s="3" t="n">
+        <v>24.1</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="F40" s="10" t="n">
+      <c r="F40" s="9" t="n">
         <v>22.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H40" s="15" t="n">
-        <v>129</v>
+        <v>3.9</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0.4</v>
@@ -3862,12 +3844,12 @@
         <v>0.5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L40" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L40" s="9" t="n">
         <v>20.4</v>
       </c>
-      <c r="M40" s="10" t="n">
+      <c r="M40" s="9" t="n">
         <v>19.1</v>
       </c>
       <c r="N40" s="3" t="n">
@@ -3879,10 +3861,10 @@
       <c r="P40" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q40" s="10" t="n">
+      <c r="Q40" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="R40" s="10" t="n">
+      <c r="R40" s="9" t="n">
         <v>19.8</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3894,10 +3876,10 @@
       <c r="U40" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="V40" s="10" t="n">
+      <c r="V40" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W40" s="10" t="n">
+      <c r="W40" s="9" t="n">
         <v>19.6</v>
       </c>
       <c r="X40" s="3" t="n">
@@ -3923,19 +3905,19 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>244.8</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="E41" s="11" t="n">
+        <v>448.8</v>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E41" s="10" t="n">
         <v>1.9</v>
       </c>
-      <c r="F41" s="10" t="n">
+      <c r="F41" s="9" t="n">
         <v>24.5</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>19.9</v>
+        <v>9.9</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>17.4</v>
@@ -3949,10 +3931,10 @@
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="10" t="n">
+      <c r="L41" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="M41" s="10" t="n">
+      <c r="M41" s="9" t="n">
         <v>18.7</v>
       </c>
       <c r="N41" s="3" t="n">
@@ -3964,10 +3946,10 @@
       <c r="P41" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q41" s="10" t="n">
+      <c r="Q41" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="R41" s="10" t="n">
+      <c r="R41" s="9" t="n">
         <v>21.6</v>
       </c>
       <c r="S41" s="3" t="n">
@@ -3979,10 +3961,10 @@
       <c r="U41" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="V41" s="10" t="n">
+      <c r="V41" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="W41" s="10" t="n">
+      <c r="W41" s="9" t="n">
         <v>22.2</v>
       </c>
       <c r="X41" s="3" t="n">
@@ -4008,7 +3990,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>116.4</v>
+        <v>64</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>32.8</v>
@@ -4016,10 +3998,10 @@
       <c r="E42" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F42" s="10" t="n">
+      <c r="F42" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="G42" s="15" t="n">
+      <c r="G42" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -4034,10 +4016,10 @@
       <c r="K42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L42" s="10" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="M42" s="10" t="n">
+      <c r="L42" s="9" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="M42" s="9" t="n">
         <v>16.1</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -4049,25 +4031,25 @@
       <c r="P42" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q42" s="10" t="n">
+      <c r="Q42" s="9" t="n">
         <v>30.8</v>
       </c>
-      <c r="R42" s="10" t="n">
+      <c r="R42" s="9" t="n">
         <v>22.6</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="V42" s="10" t="n">
+      <c r="V42" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="W42" s="10" t="n">
+      <c r="W42" s="9" t="n">
         <v>23.8</v>
       </c>
       <c r="X42" s="3" t="n">
@@ -4093,18 +4075,18 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>2341.3</v>
+        <v>341.3</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="E43" s="11" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="F43" s="10" t="n">
+      <c r="E43" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F43" s="9" t="n">
         <v>25.3</v>
       </c>
-      <c r="G43" s="15" t="n">
+      <c r="G43" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="H43" s="3" t="n">
@@ -4119,28 +4101,28 @@
       <c r="K43" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="L43" s="10" t="n">
+      <c r="L43" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="M43" s="10" t="n">
+      <c r="M43" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="N43" s="15" t="n">
+      <c r="N43" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>188.1</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Q43" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q43" s="9" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="10" t="n">
+      <c r="R43" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="S43" s="15" t="n">
+      <c r="S43" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="T43" s="3" t="n">
@@ -4149,11 +4131,11 @@
       <c r="U43" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="V43" s="10" t="n">
+      <c r="V43" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="W43" s="10" t="n">
-        <v>22.4</v>
+      <c r="W43" s="9" t="n">
+        <v>21.4</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>8.300000000000001</v>
@@ -4162,7 +4144,7 @@
         <v>82.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>14.6</v>
+        <v>4.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4186,7 +4168,7 @@
       <c r="E44" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F44" s="10" t="n">
+      <c r="F44" s="9" t="n">
         <v>21.5</v>
       </c>
       <c r="G44" s="3" t="n">
@@ -4202,16 +4184,16 @@
         <v>0.6</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="L44" s="10" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="L44" s="9" t="n">
         <v>19.4</v>
       </c>
-      <c r="M44" s="10" t="n">
+      <c r="M44" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="N44" s="15" t="n">
-        <v>4.1</v>
+      <c r="N44" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="O44" s="3" t="n">
         <v>240.1</v>
@@ -4219,10 +4201,10 @@
       <c r="P44" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q44" s="10" t="n">
+      <c r="Q44" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="R44" s="10" t="n">
+      <c r="R44" s="9" t="n">
         <v>20.3</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4232,12 +4214,12 @@
         <v>81</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="V44" s="10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="V44" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="W44" s="10" t="n">
+      <c r="W44" s="9" t="n">
         <v>20.2</v>
       </c>
       <c r="X44" s="3" t="inlineStr"/>
@@ -4259,13 +4241,13 @@
       <c r="C45" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="D45" s="9" t="n">
+      <c r="D45" s="8" t="n">
         <v>174</v>
       </c>
-      <c r="E45" s="9" t="n">
+      <c r="E45" s="8" t="n">
         <v>113.8</v>
       </c>
-      <c r="F45" s="10" t="n">
+      <c r="F45" s="9" t="n">
         <v>144</v>
       </c>
       <c r="G45" s="3" t="n">
@@ -4280,48 +4262,48 @@
       <c r="J45" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="K45" s="9" t="n">
+      <c r="K45" s="8" t="n">
         <v>30</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>110.4</v>
-      </c>
-      <c r="M45" s="10" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="M45" s="9" t="n">
         <v>109.2</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1218.1</v>
+        <v>121.1</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>534.4</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>140.4</v>
-      </c>
-      <c r="Q45" s="10" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="Q45" s="9" t="n">
         <v>157.5</v>
       </c>
-      <c r="R45" s="10" t="n">
+      <c r="R45" s="9" t="n">
         <v>129.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>138.5</v>
+        <v>137.5</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>424</v>
+        <v>14</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>1121.5</v>
-      </c>
-      <c r="V45" s="10" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="V45" s="9" t="n">
         <v>145.5</v>
       </c>
-      <c r="W45" s="9" t="n">
-        <v>231.2</v>
+      <c r="W45" s="8" t="n">
+        <v>131.6</v>
       </c>
       <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>48390.4</v>
+        <v>489</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>5.8</v>
@@ -4340,22 +4322,22 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>311.7</v>
-      </c>
-      <c r="D46" s="9" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="D46" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="E46" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F46" s="10" t="n">
+      <c r="E46" s="8" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F46" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="G46" s="15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H46" s="15" t="n">
-        <v>167.6</v>
+      <c r="G46" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>2.2</v>
@@ -4363,26 +4345,28 @@
       <c r="J46" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="10" t="n">
+      <c r="K46" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L46" s="9" t="n">
         <v>19.4</v>
       </c>
-      <c r="M46" s="10" t="n">
+      <c r="M46" s="9" t="n">
         <v>18.2</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q46" s="10" t="n">
+      <c r="Q46" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="R46" s="10" t="n">
+      <c r="R46" s="9" t="n">
         <v>21.6</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4394,13 +4378,13 @@
       <c r="U46" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="V46" s="10" t="n">
+      <c r="V46" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="W46" s="10" t="n">
+      <c r="W46" s="9" t="n">
         <v>21.8</v>
       </c>
-      <c r="X46" s="15" t="n">
+      <c r="X46" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="Y46" s="3" t="inlineStr"/>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -35,12 +35,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
       </patternFill>
@@ -55,6 +49,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
@@ -774,13 +774,13 @@
       <c r="C4" s="3" t="n">
         <v>43.7</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="8" t="n">
         <v>31.2</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="G4" s="3" t="n">
@@ -798,10 +798,10 @@
       <c r="K4" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="L4" s="9" t="n">
+      <c r="L4" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="M4" s="9" t="n">
+      <c r="M4" s="8" t="n">
         <v>16.2</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -813,10 +813,10 @@
       <c r="P4" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q4" s="9" t="n">
+      <c r="Q4" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="R4" s="9" t="n">
+      <c r="R4" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -828,10 +828,10 @@
       <c r="U4" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="V4" s="9" t="n">
+      <c r="V4" s="8" t="n">
         <v>27.7</v>
       </c>
-      <c r="W4" s="9" t="n">
+      <c r="W4" s="8" t="n">
         <v>24</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
@@ -853,13 +853,13 @@
       <c r="C5" s="3" t="n">
         <v>62.1</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="G5" s="3" t="n">
@@ -875,10 +875,10 @@
       <c r="K5" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="L5" s="9" t="n">
+      <c r="L5" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="M5" s="9" t="n">
+      <c r="M5" s="8" t="n">
         <v>18</v>
       </c>
       <c r="N5" s="3" t="n">
@@ -890,10 +890,10 @@
       <c r="P5" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q5" s="9" t="n">
+      <c r="Q5" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="R5" s="9" t="n">
+      <c r="R5" s="8" t="n">
         <v>19.1</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -905,10 +905,10 @@
       <c r="U5" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="V5" s="9" t="n">
+      <c r="V5" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="W5" s="9" t="n">
+      <c r="W5" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -936,13 +936,13 @@
       <c r="C6" s="3" t="n">
         <v>421.6</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="8" t="n">
         <v>31.4</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="G6" s="3" t="n">
@@ -960,10 +960,10 @@
       <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="9" t="n">
+      <c r="L6" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="M6" s="8" t="n">
         <v>19</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -975,10 +975,10 @@
       <c r="P6" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q6" s="9" t="n">
+      <c r="Q6" s="8" t="n">
         <v>29.8</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="R6" s="8" t="n">
         <v>23.9</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -990,10 +990,10 @@
       <c r="U6" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="V6" s="9" t="n">
+      <c r="V6" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="W6" s="9" t="n">
+      <c r="W6" s="8" t="n">
         <v>23.2</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1021,11 +1021,11 @@
       <c r="C7" s="3" t="n">
         <v>43.7</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="E7" s="11" t="inlineStr"/>
-      <c r="F7" s="9" t="n">
+      <c r="E7" s="10" t="inlineStr"/>
+      <c r="F7" s="8" t="n">
         <v>25</v>
       </c>
       <c r="G7" s="3" t="n">
@@ -1043,10 +1043,10 @@
       <c r="K7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="9" t="n">
+      <c r="L7" s="8" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" s="9" t="n">
+      <c r="M7" s="8" t="n">
         <v>16</v>
       </c>
       <c r="N7" s="3" t="n">
@@ -1058,10 +1058,10 @@
       <c r="P7" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q7" s="9" t="n">
+      <c r="Q7" s="8" t="n">
         <v>31.9</v>
       </c>
-      <c r="R7" s="9" t="n">
+      <c r="R7" s="8" t="n">
         <v>23.9</v>
       </c>
       <c r="S7" s="3" t="n">
@@ -1073,10 +1073,10 @@
       <c r="U7" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="V7" s="9" t="n">
+      <c r="V7" s="8" t="n">
         <v>27.6</v>
       </c>
-      <c r="W7" s="9" t="n">
+      <c r="W7" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1104,13 +1104,13 @@
       <c r="C8" s="3" t="n">
         <v>297.2</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="8" t="n">
         <v>26.2</v>
       </c>
       <c r="G8" s="3" t="n">
@@ -1128,10 +1128,10 @@
       <c r="K8" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="L8" s="9" t="n">
+      <c r="L8" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="M8" s="9" t="n">
+      <c r="M8" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="N8" s="3" t="n">
@@ -1143,10 +1143,10 @@
       <c r="P8" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q8" s="9" t="n">
+      <c r="Q8" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R8" s="9" t="n">
+      <c r="R8" s="8" t="n">
         <v>26</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1158,10 +1158,10 @@
       <c r="U8" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="V8" s="9" t="n">
+      <c r="V8" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="W8" s="9" t="n">
+      <c r="W8" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1190,12 +1190,12 @@
         <v>166.6</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>252.6</v>
-      </c>
-      <c r="E9" s="8" t="n">
+        <v>152.6</v>
+      </c>
+      <c r="E9" s="11" t="n">
         <v>92.5</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="8" t="n">
         <v>122.5</v>
       </c>
       <c r="G9" s="3" t="n">
@@ -1210,28 +1210,28 @@
       <c r="J9" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="K9" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="L9" s="9" t="n">
+      <c r="K9" s="11" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="L9" s="8" t="n">
         <v>94.3</v>
       </c>
-      <c r="M9" s="9" t="n">
+      <c r="M9" s="8" t="n">
         <v>87.8</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>96.3</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>440.9</v>
+        <v>22.2</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="Q9" s="9" t="n">
+      <c r="Q9" s="8" t="n">
         <v>138.8</v>
       </c>
-      <c r="R9" s="9" t="n">
+      <c r="R9" s="8" t="n">
         <v>117.3</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1243,10 +1243,10 @@
       <c r="U9" s="3" t="n">
         <v>58.5</v>
       </c>
-      <c r="V9" s="9" t="n">
+      <c r="V9" s="8" t="n">
         <v>126.1</v>
       </c>
-      <c r="W9" s="9" t="n">
+      <c r="W9" s="8" t="n">
         <v>113</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1256,7 +1256,7 @@
         <v>402.4</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>2.8</v>
+        <v>32.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1274,13 +1274,13 @@
       <c r="C10" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="E10" s="11" t="n">
         <v>18.5</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="G10" s="3" t="n">
@@ -1298,10 +1298,10 @@
       <c r="K10" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L10" s="9" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="M10" s="9" t="n">
+      <c r="L10" s="11" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="M10" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1313,10 +1313,10 @@
       <c r="P10" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q10" s="9" t="n">
+      <c r="Q10" s="8" t="n">
         <v>27.8</v>
       </c>
-      <c r="R10" s="9" t="n">
+      <c r="R10" s="8" t="n">
         <v>23.5</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1328,10 +1328,10 @@
       <c r="U10" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="V10" s="9" t="n">
+      <c r="V10" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="W10" s="9" t="n">
+      <c r="W10" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1359,13 +1359,13 @@
       <c r="C11" s="3" t="n">
         <v>44.5</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="G11" s="3" t="n">
@@ -1383,10 +1383,10 @@
       <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="9" t="n">
+      <c r="L11" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="M11" s="9" t="n">
+      <c r="M11" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="N11" s="3" t="n">
@@ -1398,10 +1398,10 @@
       <c r="P11" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="Q11" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="R11" s="9" t="n">
+      <c r="R11" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="S11" s="3" t="n">
@@ -1413,10 +1413,10 @@
       <c r="U11" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="V11" s="9" t="n">
+      <c r="V11" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="W11" s="9" t="n">
+      <c r="W11" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1444,13 +1444,13 @@
       <c r="C12" s="3" t="n">
         <v>38.3</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="8" t="n">
         <v>28.1</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="8" t="n">
         <v>23.9</v>
       </c>
       <c r="G12" s="3" t="n">
@@ -1468,10 +1468,10 @@
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="9" t="n">
+      <c r="L12" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="M12" s="9" t="n">
+      <c r="M12" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1483,10 +1483,10 @@
       <c r="P12" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q12" s="9" t="n">
+      <c r="Q12" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="R12" s="9" t="n">
+      <c r="R12" s="8" t="n">
         <v>25.2</v>
       </c>
       <c r="S12" s="3" t="n">
@@ -1498,10 +1498,10 @@
       <c r="U12" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="V12" s="9" t="n">
+      <c r="V12" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="W12" s="9" t="n">
+      <c r="W12" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="X12" s="3" t="n">
@@ -1529,13 +1529,13 @@
       <c r="C13" s="3" t="n">
         <v>35.6</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="G13" s="3" t="n">
@@ -1553,10 +1553,10 @@
       <c r="K13" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L13" s="9" t="n">
+      <c r="L13" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="M13" s="9" t="n">
+      <c r="M13" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="N13" s="3" t="n">
@@ -1568,10 +1568,10 @@
       <c r="P13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="Q13" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="R13" s="9" t="n">
+      <c r="R13" s="8" t="n">
         <v>26.3</v>
       </c>
       <c r="S13" s="3" t="n">
@@ -1583,10 +1583,10 @@
       <c r="U13" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="V13" s="9" t="n">
+      <c r="V13" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="W13" s="9" t="n">
+      <c r="W13" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X13" s="3" t="n">
@@ -1612,15 +1612,15 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="D14" s="9" t="n">
+        <v>374</v>
+      </c>
+      <c r="D14" s="8" t="n">
         <v>32.5</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="8" t="n">
         <v>26.1</v>
       </c>
       <c r="G14" s="3" t="n">
@@ -1638,10 +1638,10 @@
       <c r="K14" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="L14" s="9" t="n">
+      <c r="L14" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="M14" s="9" t="n">
+      <c r="M14" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1653,10 +1653,10 @@
       <c r="P14" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q14" s="9" t="n">
+      <c r="Q14" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="R14" s="9" t="n">
+      <c r="R14" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="S14" s="3" t="n">
@@ -1668,10 +1668,10 @@
       <c r="U14" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="V14" s="9" t="n">
+      <c r="V14" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="W14" s="9" t="n">
+      <c r="W14" s="8" t="n">
         <v>21.1</v>
       </c>
       <c r="X14" s="3" t="n">
@@ -1699,13 +1699,13 @@
       <c r="C15" s="3" t="n">
         <v>43.3</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="G15" s="3" t="n">
@@ -1723,10 +1723,10 @@
       <c r="K15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="9" t="n">
+      <c r="L15" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="M15" s="9" t="n">
+      <c r="M15" s="8" t="n">
         <v>19.1</v>
       </c>
       <c r="N15" s="3" t="n">
@@ -1738,10 +1738,10 @@
       <c r="P15" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" s="8" t="n">
         <v>28.5</v>
       </c>
-      <c r="R15" s="9" t="n">
+      <c r="R15" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1753,10 +1753,10 @@
       <c r="U15" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="V15" s="9" t="n">
+      <c r="V15" s="8" t="n">
         <v>24.5</v>
       </c>
-      <c r="W15" s="9" t="n">
+      <c r="W15" s="8" t="n">
         <v>21.1</v>
       </c>
       <c r="X15" s="3" t="n">
@@ -1782,15 +1782,15 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>992.7</v>
-      </c>
-      <c r="D16" s="9" t="n">
+        <v>1992.6</v>
+      </c>
+      <c r="D16" s="8" t="n">
         <v>149.9</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="8" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" s="8" t="n">
         <v>124.7</v>
       </c>
       <c r="G16" s="3" t="n">
@@ -1806,10 +1806,10 @@
         <v>15.8</v>
       </c>
       <c r="K16" s="12" t="inlineStr"/>
-      <c r="L16" s="8" t="n">
+      <c r="L16" s="11" t="n">
         <v>1.9</v>
       </c>
-      <c r="M16" s="9" t="n">
+      <c r="M16" s="8" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1821,10 +1821,10 @@
       <c r="P16" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="Q16" s="9" t="n">
+      <c r="Q16" s="8" t="n">
         <v>142.8</v>
       </c>
-      <c r="R16" s="9" t="n">
+      <c r="R16" s="8" t="n">
         <v>123</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1836,10 +1836,10 @@
       <c r="U16" s="3" t="n">
         <v>53.1</v>
       </c>
-      <c r="V16" s="9" t="n">
+      <c r="V16" s="8" t="n">
         <v>120.8</v>
       </c>
-      <c r="W16" s="9" t="n">
+      <c r="W16" s="8" t="n">
         <v>115.1</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1867,13 +1867,13 @@
       <c r="C17" s="3" t="n">
         <v>39.8</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D17" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="G17" s="3" t="n">
@@ -1891,10 +1891,10 @@
       <c r="K17" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="L17" s="9" t="n">
+      <c r="L17" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="M17" s="9" t="n">
+      <c r="M17" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1906,10 +1906,10 @@
       <c r="P17" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q17" s="9" t="n">
+      <c r="Q17" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="R17" s="9" t="n">
+      <c r="R17" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1921,10 +1921,10 @@
       <c r="U17" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V17" s="9" t="n">
+      <c r="V17" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="W17" s="9" t="n">
+      <c r="W17" s="8" t="n">
         <v>23</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1952,13 +1952,13 @@
       <c r="C18" s="3" t="n">
         <v>431.1</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="G18" s="3" t="n">
@@ -1976,10 +1976,10 @@
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="9" t="n">
+      <c r="L18" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="M18" s="9" t="n">
+      <c r="M18" s="8" t="n">
         <v>17.7</v>
       </c>
       <c r="N18" s="3" t="n">
@@ -1989,12 +1989,12 @@
         <v>87</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q18" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q18" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="R18" s="9" t="n">
+      <c r="R18" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -2006,10 +2006,10 @@
       <c r="U18" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V18" s="9" t="n">
+      <c r="V18" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="W18" s="9" t="n">
+      <c r="W18" s="8" t="n">
         <v>25</v>
       </c>
       <c r="X18" s="3" t="n">
@@ -2035,15 +2035,15 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>223.4</v>
-      </c>
-      <c r="D19" s="9" t="n">
+        <v>423.4</v>
+      </c>
+      <c r="D19" s="8" t="n">
         <v>32.5</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="G19" s="3" t="n">
@@ -2061,10 +2061,10 @@
       <c r="K19" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="L19" s="9" t="n">
+      <c r="L19" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="M19" s="9" t="n">
+      <c r="M19" s="8" t="n">
         <v>18.2</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2076,10 +2076,10 @@
       <c r="P19" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q19" s="9" t="n">
+      <c r="Q19" s="8" t="n">
         <v>31.8</v>
       </c>
-      <c r="R19" s="9" t="n">
+      <c r="R19" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2091,10 +2091,10 @@
       <c r="U19" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="V19" s="9" t="n">
+      <c r="V19" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="W19" s="9" t="n">
+      <c r="W19" s="8" t="n">
         <v>23.3</v>
       </c>
       <c r="X19" s="3" t="n">
@@ -2122,13 +2122,13 @@
       <c r="C20" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="8" t="n">
         <v>23.5</v>
       </c>
       <c r="G20" s="3" t="n">
@@ -2146,10 +2146,10 @@
       <c r="K20" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="L20" s="9" t="n">
+      <c r="L20" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="M20" s="9" t="n">
+      <c r="M20" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="N20" s="3" t="n">
@@ -2161,11 +2161,11 @@
       <c r="P20" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q20" s="9" t="n">
+      <c r="Q20" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="R20" s="9" t="n">
-        <v>21.5</v>
+      <c r="R20" s="8" t="n">
+        <v>22.15</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>23.1</v>
@@ -2176,10 +2176,10 @@
       <c r="U20" s="3" t="n">
         <v>9.5</v>
       </c>
-      <c r="V20" s="9" t="n">
+      <c r="V20" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="W20" s="9" t="n">
+      <c r="W20" s="8" t="n">
         <v>20.5</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2207,13 +2207,13 @@
       <c r="C21" s="3" t="n">
         <v>43.3</v>
       </c>
-      <c r="D21" s="9" t="n">
+      <c r="D21" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="G21" s="3" t="n">
@@ -2229,12 +2229,12 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L21" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L21" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="M21" s="9" t="n">
+      <c r="M21" s="8" t="n">
         <v>17.3</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2246,25 +2246,25 @@
       <c r="P21" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q21" s="9" t="n">
+      <c r="Q21" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="R21" s="9" t="n">
+      <c r="R21" s="8" t="n">
         <v>22.2</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="V21" s="9" t="n">
+      <c r="V21" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="W21" s="9" t="n">
+      <c r="W21" s="8" t="n">
         <v>22.4</v>
       </c>
       <c r="X21" s="3" t="n">
@@ -2292,13 +2292,13 @@
       <c r="C22" s="3" t="n">
         <v>374</v>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D22" s="8" t="n">
         <v>31.8</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="G22" s="3" t="n">
@@ -2316,10 +2316,10 @@
       <c r="K22" s="3" t="n">
         <v>3.7</v>
       </c>
-      <c r="L22" s="9" t="n">
+      <c r="L22" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="M22" s="9" t="n">
+      <c r="M22" s="8" t="n">
         <v>16.2</v>
       </c>
       <c r="N22" s="3" t="n">
@@ -2331,10 +2331,10 @@
       <c r="P22" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q22" s="9" t="n">
+      <c r="Q22" s="8" t="n">
         <v>30.2</v>
       </c>
-      <c r="R22" s="9" t="n">
+      <c r="R22" s="8" t="n">
         <v>23.3</v>
       </c>
       <c r="S22" s="3" t="n">
@@ -2346,10 +2346,10 @@
       <c r="U22" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="V22" s="9" t="n">
+      <c r="V22" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="W22" s="9" t="n">
+      <c r="W22" s="8" t="n">
         <v>19.5</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2377,13 +2377,13 @@
       <c r="C23" s="3" t="n">
         <v>1925.5</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="8" t="n">
         <v>153.1</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="8" t="n">
         <v>92.8</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="8" t="n">
         <v>123</v>
       </c>
       <c r="G23" s="3" t="n">
@@ -2396,15 +2396,15 @@
         <v>11.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>125.5</v>
-      </c>
-      <c r="K23" s="8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="K23" s="11" t="n">
         <v>49.2</v>
       </c>
-      <c r="L23" s="9" t="n">
+      <c r="L23" s="8" t="n">
         <v>95.2</v>
       </c>
-      <c r="M23" s="9" t="n">
+      <c r="M23" s="8" t="n">
         <v>88.2</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2416,10 +2416,10 @@
       <c r="P23" s="3" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q23" s="9" t="n">
+      <c r="Q23" s="8" t="n">
         <v>146.2</v>
       </c>
-      <c r="R23" s="9" t="n">
+      <c r="R23" s="11" t="n">
         <v>114.3</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2431,20 +2431,20 @@
       <c r="U23" s="3" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="V23" s="9" t="n">
+      <c r="V23" s="8" t="n">
         <v>122.2</v>
       </c>
-      <c r="W23" s="9" t="n">
+      <c r="W23" s="8" t="n">
         <v>110.7</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>126.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>11</v>
+        <v>411</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>8.1</v>
+        <v>27.1</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2462,20 +2462,20 @@
       <c r="C24" s="3" t="n">
         <v>38.5</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>12</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17.6</v>
+        <v>17.2</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
@@ -2484,12 +2484,12 @@
         <v>3.1</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="M24" s="9" t="n">
+      <c r="M24" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2501,10 +2501,10 @@
       <c r="P24" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q24" s="9" t="n">
+      <c r="Q24" s="8" t="n">
         <v>29.2</v>
       </c>
-      <c r="R24" s="9" t="n">
+      <c r="R24" s="8" t="n">
         <v>22.9</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2514,12 +2514,12 @@
         <v>59</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V24" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="V24" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="W24" s="9" t="n">
+      <c r="W24" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2550,10 +2550,10 @@
       <c r="D25" s="3" t="n">
         <v>32.1</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="8" t="n">
         <v>25.7</v>
       </c>
       <c r="G25" s="3" t="n">
@@ -2569,12 +2569,12 @@
         <v>3.6</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L25" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L25" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="M25" s="9" t="n">
+      <c r="M25" s="8" t="n">
         <v>18.4</v>
       </c>
       <c r="N25" s="3" t="n">
@@ -2586,10 +2586,10 @@
       <c r="P25" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q25" s="9" t="n">
+      <c r="Q25" s="8" t="n">
         <v>31.3</v>
       </c>
-      <c r="R25" s="9" t="n">
+      <c r="R25" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2601,10 +2601,10 @@
       <c r="U25" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="V25" s="9" t="n">
+      <c r="V25" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="W25" s="9" t="n">
+      <c r="W25" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2635,17 +2635,17 @@
       <c r="D26" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1.9</v>
@@ -2656,10 +2656,10 @@
       <c r="K26" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L26" s="9" t="n">
+      <c r="L26" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M26" s="9" t="n">
+      <c r="M26" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="N26" s="3" t="n">
@@ -2671,10 +2671,10 @@
       <c r="P26" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q26" s="9" t="n">
+      <c r="Q26" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="R26" s="9" t="n">
+      <c r="R26" s="8" t="n">
         <v>21.8</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2686,10 +2686,10 @@
       <c r="U26" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="V26" s="9" t="n">
+      <c r="V26" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="W26" s="9" t="n">
+      <c r="W26" s="8" t="n">
         <v>21.8</v>
       </c>
       <c r="X26" s="3" t="n">
@@ -2717,13 +2717,13 @@
       <c r="C27" s="3" t="n">
         <v>354.8</v>
       </c>
-      <c r="D27" s="10" t="n">
+      <c r="D27" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="G27" s="3" t="n">
@@ -2741,10 +2741,10 @@
       <c r="K27" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="L27" s="9" t="n">
+      <c r="L27" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="M27" s="9" t="n">
+      <c r="M27" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="N27" s="3" t="n">
@@ -2756,10 +2756,10 @@
       <c r="P27" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q27" s="9" t="n">
+      <c r="Q27" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="R27" s="9" t="n">
+      <c r="R27" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2771,10 +2771,10 @@
       <c r="U27" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V27" s="9" t="n">
+      <c r="V27" s="8" t="n">
         <v>23.2</v>
       </c>
-      <c r="W27" s="9" t="n">
+      <c r="W27" s="8" t="n">
         <v>20.8</v>
       </c>
       <c r="X27" s="3" t="n">
@@ -2805,10 +2805,10 @@
       <c r="D28" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="8" t="n">
         <v>25</v>
       </c>
       <c r="G28" s="3" t="n">
@@ -2826,10 +2826,10 @@
       <c r="K28" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="L28" s="9" t="n">
+      <c r="L28" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="M28" s="9" t="n">
+      <c r="M28" s="8" t="n">
         <v>19.2</v>
       </c>
       <c r="N28" s="3" t="n">
@@ -2841,10 +2841,10 @@
       <c r="P28" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q28" s="9" t="n">
+      <c r="Q28" s="8" t="n">
         <v>28.2</v>
       </c>
-      <c r="R28" s="9" t="n">
+      <c r="R28" s="8" t="n">
         <v>23</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2856,10 +2856,10 @@
       <c r="U28" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="V28" s="9" t="n">
+      <c r="V28" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="W28" s="9" t="n">
+      <c r="W28" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2885,15 +2885,15 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>20.8</v>
+        <v>40.8</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="G29" s="3" t="n">
@@ -2903,7 +2903,7 @@
         <v>20.1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2.9</v>
@@ -2911,10 +2911,10 @@
       <c r="K29" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L29" s="9" t="n">
+      <c r="L29" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="M29" s="9" t="n">
+      <c r="M29" s="8" t="n">
         <v>19.2</v>
       </c>
       <c r="N29" s="3" t="n">
@@ -2926,10 +2926,10 @@
       <c r="P29" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q29" s="9" t="n">
+      <c r="Q29" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="9" t="n">
+      <c r="R29" s="8" t="n">
         <v>23</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2941,10 +2941,10 @@
       <c r="U29" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="V29" s="9" t="n">
+      <c r="V29" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="W29" s="9" t="n">
+      <c r="W29" s="8" t="n">
         <v>23</v>
       </c>
       <c r="X29" s="3" t="n">
@@ -2970,22 +2970,22 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1856</v>
-      </c>
-      <c r="D30" s="8" t="n">
+        <v>1856.4</v>
+      </c>
+      <c r="D30" s="11" t="n">
         <v>150.3</v>
       </c>
-      <c r="E30" s="8" t="n">
+      <c r="E30" s="11" t="n">
         <v>91.2</v>
       </c>
-      <c r="F30" s="9" t="n">
+      <c r="F30" s="8" t="n">
         <v>124.1</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>52.5</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>91.7</v>
+        <v>91.3</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>10</v>
@@ -2993,13 +2993,13 @@
       <c r="J30" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="K30" s="8" t="n">
+      <c r="K30" s="11" t="n">
         <v>25.4</v>
       </c>
-      <c r="L30" s="8" t="n">
+      <c r="L30" s="11" t="n">
         <v>29.6</v>
       </c>
-      <c r="M30" s="9" t="n">
+      <c r="M30" s="8" t="n">
         <v>93.2</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3011,10 +3011,10 @@
       <c r="P30" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q30" s="9" t="n">
+      <c r="Q30" s="8" t="n">
         <v>138.5</v>
       </c>
-      <c r="R30" s="9" t="n">
+      <c r="R30" s="8" t="n">
         <v>113.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3026,10 +3026,10 @@
       <c r="U30" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="V30" s="9" t="n">
+      <c r="V30" s="8" t="n">
         <v>123.1</v>
       </c>
-      <c r="W30" s="9" t="n">
+      <c r="W30" s="8" t="n">
         <v>110.1</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3057,13 +3057,13 @@
       <c r="C31" s="3" t="n">
         <v>37.1</v>
       </c>
-      <c r="D31" s="8" t="n">
+      <c r="D31" s="11" t="n">
         <v>30.1</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="G31" s="3" t="n">
@@ -3081,10 +3081,10 @@
       <c r="K31" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L31" s="9" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M31" s="9" t="n">
+      <c r="L31" s="11" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="M31" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3096,10 +3096,10 @@
       <c r="P31" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q31" s="8" t="n">
         <v>27.7</v>
       </c>
-      <c r="R31" s="9" t="n">
+      <c r="R31" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3111,10 +3111,10 @@
       <c r="U31" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="V31" s="9" t="n">
+      <c r="V31" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="W31" s="9" t="n">
+      <c r="W31" s="8" t="n">
         <v>22</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3142,13 +3142,13 @@
       <c r="C32" s="3" t="n">
         <v>43.7</v>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="D32" s="8" t="n">
         <v>32.8</v>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" s="8" t="n">
         <v>26.5</v>
       </c>
       <c r="G32" s="3" t="n">
@@ -3163,13 +3163,13 @@
       <c r="J32" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K32" s="9" t="n">
+      <c r="K32" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="9" t="n">
+      <c r="L32" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="M32" s="9" t="n">
+      <c r="M32" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="N32" s="3" t="n">
@@ -3181,10 +3181,10 @@
       <c r="P32" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="Q32" s="9" t="n">
+      <c r="Q32" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="R32" s="9" t="n">
+      <c r="R32" s="8" t="n">
         <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3196,10 +3196,10 @@
       <c r="U32" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="V32" s="9" t="n">
+      <c r="V32" s="8" t="n">
         <v>28.2</v>
       </c>
-      <c r="W32" s="9" t="n">
+      <c r="W32" s="8" t="n">
         <v>23.7</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3227,13 +3227,13 @@
       <c r="C33" s="3" t="n">
         <v>397</v>
       </c>
-      <c r="D33" s="9" t="n">
+      <c r="D33" s="8" t="n">
         <v>33.7</v>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E33" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="8" t="n">
         <v>26.7</v>
       </c>
       <c r="G33" s="3" t="n">
@@ -3248,13 +3248,13 @@
       <c r="J33" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K33" s="9" t="n">
+      <c r="K33" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="9" t="n">
+      <c r="L33" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="M33" s="9" t="n">
+      <c r="M33" s="8" t="n">
         <v>19.5</v>
       </c>
       <c r="N33" s="3" t="n">
@@ -3266,10 +3266,10 @@
       <c r="P33" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q33" s="9" t="n">
+      <c r="Q33" s="8" t="n">
         <v>32.9</v>
       </c>
-      <c r="R33" s="9" t="n">
+      <c r="R33" s="8" t="n">
         <v>23.9</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3281,10 +3281,10 @@
       <c r="U33" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="V33" s="9" t="n">
+      <c r="V33" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="W33" s="9" t="n">
+      <c r="W33" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3312,13 +3312,13 @@
       <c r="C34" s="3" t="n">
         <v>362.4</v>
       </c>
-      <c r="D34" s="9" t="n">
+      <c r="D34" s="8" t="n">
         <v>30.4</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E34" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="8" t="n">
         <v>25.3</v>
       </c>
       <c r="G34" s="3" t="n">
@@ -3333,13 +3333,13 @@
       <c r="J34" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K34" s="9" t="n">
+      <c r="K34" s="8" t="n">
         <v>1.2</v>
       </c>
-      <c r="L34" s="9" t="n">
+      <c r="L34" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="M34" s="9" t="n">
+      <c r="M34" s="8" t="n">
         <v>19</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -3351,10 +3351,10 @@
       <c r="P34" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="8" t="n">
         <v>26.1</v>
       </c>
-      <c r="R34" s="9" t="n">
+      <c r="R34" s="8" t="n">
         <v>23.2</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3366,10 +3366,10 @@
       <c r="U34" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="V34" s="9" t="n">
+      <c r="V34" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="W34" s="9" t="n">
+      <c r="W34" s="8" t="n">
         <v>23.3</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3397,13 +3397,13 @@
       <c r="C35" s="3" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="D35" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="G35" s="3" t="n">
@@ -3418,13 +3418,13 @@
       <c r="J35" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K35" s="9" t="n">
+      <c r="K35" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="L35" s="9" t="n">
+      <c r="L35" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="M35" s="9" t="n">
+      <c r="M35" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="N35" s="3" t="n">
@@ -3436,10 +3436,10 @@
       <c r="P35" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q35" s="9" t="n">
+      <c r="Q35" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="R35" s="9" t="n">
+      <c r="R35" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3451,10 +3451,10 @@
       <c r="U35" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="V35" s="9" t="n">
+      <c r="V35" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="W35" s="9" t="n">
+      <c r="W35" s="8" t="n">
         <v>20.3</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3482,13 +3482,13 @@
       <c r="C36" s="3" t="n">
         <v>398.9</v>
       </c>
-      <c r="D36" s="9" t="n">
+      <c r="D36" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="E36" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="G36" s="3" t="n">
@@ -3503,13 +3503,13 @@
       <c r="J36" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K36" s="9" t="n">
+      <c r="K36" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="9" t="n">
+      <c r="L36" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="M36" s="9" t="n">
+      <c r="M36" s="8" t="n">
         <v>19.4</v>
       </c>
       <c r="N36" s="3" t="n">
@@ -3521,10 +3521,10 @@
       <c r="P36" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q36" s="9" t="n">
+      <c r="Q36" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="R36" s="9" t="n">
+      <c r="R36" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3536,10 +3536,10 @@
       <c r="U36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V36" s="9" t="n">
+      <c r="V36" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="W36" s="9" t="n">
+      <c r="W36" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3567,13 +3567,13 @@
       <c r="C37" s="3" t="n">
         <v>1683.5</v>
       </c>
-      <c r="D37" s="9" t="n">
+      <c r="D37" s="8" t="n">
         <v>150.1</v>
       </c>
-      <c r="E37" s="9" t="n">
+      <c r="E37" s="8" t="n">
         <v>100.9</v>
       </c>
-      <c r="F37" s="9" t="n">
+      <c r="F37" s="8" t="n">
         <v>125.5</v>
       </c>
       <c r="G37" s="3" t="n">
@@ -3588,13 +3588,13 @@
       <c r="J37" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="K37" s="9" t="n">
+      <c r="K37" s="8" t="n">
         <v>10.2</v>
       </c>
-      <c r="L37" s="9" t="n">
+      <c r="L37" s="8" t="n">
         <v>103.5</v>
       </c>
-      <c r="M37" s="9" t="n">
+      <c r="M37" s="8" t="n">
         <v>96.5</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3606,10 +3606,10 @@
       <c r="P37" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="Q37" s="9" t="n">
+      <c r="Q37" s="8" t="n">
         <v>139.6</v>
       </c>
-      <c r="R37" s="9" t="n">
+      <c r="R37" s="8" t="n">
         <v>115.4</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3621,10 +3621,10 @@
       <c r="U37" s="3" t="n">
         <v>65.7</v>
       </c>
-      <c r="V37" s="9" t="n">
+      <c r="V37" s="8" t="n">
         <v>126.1</v>
       </c>
-      <c r="W37" s="9" t="n">
+      <c r="W37" s="8" t="n">
         <v>112.2</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3652,13 +3652,13 @@
       <c r="C38" s="3" t="n">
         <v>336.7</v>
       </c>
-      <c r="D38" s="9" t="n">
+      <c r="D38" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="8" t="n">
         <v>25.1</v>
       </c>
       <c r="G38" s="3" t="n">
@@ -3674,12 +3674,12 @@
         <v>3.1</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L38" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L38" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="M38" s="9" t="n">
+      <c r="M38" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3691,10 +3691,10 @@
       <c r="P38" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q38" s="9" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="R38" s="9" t="n">
+      <c r="Q38" s="11" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="R38" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3704,12 +3704,12 @@
         <v>68.7</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="V38" s="9" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="V38" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="W38" s="9" t="n">
+      <c r="W38" s="8" t="n">
         <v>22.4</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3737,13 +3737,13 @@
       <c r="C39" s="3" t="n">
         <v>400.8</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" s="8" t="n">
         <v>31.8</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F39" s="8" t="n">
         <v>25.7</v>
       </c>
       <c r="G39" s="3" t="n">
@@ -3758,13 +3758,13 @@
       <c r="J39" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="9" t="n">
+      <c r="L39" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="M39" s="9" t="n">
+      <c r="M39" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="N39" s="3" t="n">
@@ -3776,10 +3776,10 @@
       <c r="P39" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q39" s="9" t="n">
+      <c r="Q39" s="8" t="n">
         <v>30.4</v>
       </c>
-      <c r="R39" s="9" t="n">
+      <c r="R39" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="S39" s="3" t="n">
@@ -3791,10 +3791,10 @@
       <c r="U39" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="V39" s="9" t="n">
+      <c r="V39" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="W39" s="9" t="n">
+      <c r="W39" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3822,14 +3822,14 @@
       <c r="C40" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="D40" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E40" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F40" s="9" t="n">
-        <v>22.1</v>
+      <c r="F40" s="8" t="n">
+        <v>22.21</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>3.9</v>
@@ -3843,13 +3843,13 @@
       <c r="J40" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="K40" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L40" s="9" t="n">
+      <c r="K40" s="8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L40" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="M40" s="9" t="n">
+      <c r="M40" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="N40" s="3" t="n">
@@ -3861,10 +3861,10 @@
       <c r="P40" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q40" s="9" t="n">
+      <c r="Q40" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="R40" s="9" t="n">
+      <c r="R40" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3876,10 +3876,10 @@
       <c r="U40" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="V40" s="9" t="n">
+      <c r="V40" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="W40" s="9" t="n">
+      <c r="W40" s="8" t="n">
         <v>19.6</v>
       </c>
       <c r="X40" s="3" t="n">
@@ -3905,15 +3905,15 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>448.8</v>
-      </c>
-      <c r="D41" s="10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F41" s="9" t="n">
+        <v>448.2</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F41" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="G41" s="3" t="n">
@@ -3928,13 +3928,13 @@
       <c r="J41" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="9" t="n">
+      <c r="L41" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="M41" s="9" t="n">
+      <c r="M41" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="N41" s="3" t="n">
@@ -3946,25 +3946,25 @@
       <c r="P41" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q41" s="9" t="n">
+      <c r="Q41" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="R41" s="9" t="n">
+      <c r="R41" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>58.4</v>
+        <v>57.4</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="V41" s="9" t="n">
+      <c r="V41" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="W41" s="9" t="n">
+      <c r="W41" s="8" t="n">
         <v>22.2</v>
       </c>
       <c r="X41" s="3" t="n">
@@ -3990,15 +3990,15 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="D42" s="3" t="n">
+        <v>464.2</v>
+      </c>
+      <c r="D42" s="8" t="n">
         <v>32.8</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="G42" s="3" t="n">
@@ -4013,13 +4013,13 @@
       <c r="J42" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="L42" s="9" t="n">
+      <c r="L42" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="M42" s="9" t="n">
+      <c r="M42" s="3" t="n">
         <v>16.1</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -4031,10 +4031,10 @@
       <c r="P42" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q42" s="9" t="n">
+      <c r="Q42" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="R42" s="9" t="n">
+      <c r="R42" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="S42" s="3" t="n">
@@ -4046,10 +4046,10 @@
       <c r="U42" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="V42" s="9" t="n">
+      <c r="V42" s="8" t="n">
         <v>27.5</v>
       </c>
-      <c r="W42" s="9" t="n">
+      <c r="W42" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X42" s="3" t="n">
@@ -4077,13 +4077,13 @@
       <c r="C43" s="3" t="n">
         <v>341.3</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="D43" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="F43" s="9" t="n">
+      <c r="F43" s="8" t="n">
         <v>25.3</v>
       </c>
       <c r="G43" s="3" t="n">
@@ -4098,13 +4098,13 @@
       <c r="J43" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K43" s="3" t="n">
+      <c r="K43" s="8" t="n">
         <v>15.2</v>
       </c>
-      <c r="L43" s="9" t="n">
+      <c r="L43" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="M43" s="9" t="n">
+      <c r="M43" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="N43" s="3" t="n">
@@ -4116,10 +4116,10 @@
       <c r="P43" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q43" s="9" t="n">
+      <c r="Q43" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="9" t="n">
+      <c r="R43" s="8" t="n">
         <v>22.3</v>
       </c>
       <c r="S43" s="3" t="n">
@@ -4131,11 +4131,11 @@
       <c r="U43" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="V43" s="9" t="n">
+      <c r="V43" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="W43" s="9" t="n">
-        <v>21.4</v>
+      <c r="W43" s="8" t="n">
+        <v>22.4</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>8.300000000000001</v>
@@ -4162,13 +4162,13 @@
       <c r="C44" s="3" t="n">
         <v>141.6</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="D44" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="F44" s="9" t="n">
+      <c r="F44" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="G44" s="3" t="n">
@@ -4183,14 +4183,14 @@
       <c r="J44" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="K44" s="3" t="n">
+      <c r="K44" s="8" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="L44" s="9" t="n">
+      <c r="L44" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="M44" s="9" t="n">
-        <v>18.2</v>
+      <c r="M44" s="3" t="n">
+        <v>28.2</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>20.1</v>
@@ -4201,10 +4201,10 @@
       <c r="P44" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q44" s="9" t="n">
+      <c r="Q44" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="R44" s="9" t="n">
+      <c r="R44" s="8" t="n">
         <v>20.3</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4216,10 +4216,10 @@
       <c r="U44" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="V44" s="9" t="n">
+      <c r="V44" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="W44" s="9" t="n">
+      <c r="W44" s="8" t="n">
         <v>20.2</v>
       </c>
       <c r="X44" s="3" t="inlineStr"/>
@@ -4247,7 +4247,7 @@
       <c r="E45" s="8" t="n">
         <v>113.8</v>
       </c>
-      <c r="F45" s="9" t="n">
+      <c r="F45" s="8" t="n">
         <v>144</v>
       </c>
       <c r="G45" s="3" t="n">
@@ -4265,10 +4265,10 @@
       <c r="K45" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="L45" s="9" t="n">
+      <c r="L45" s="8" t="n">
         <v>116.4</v>
       </c>
-      <c r="M45" s="9" t="n">
+      <c r="M45" s="11" t="n">
         <v>109.2</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4280,30 +4280,30 @@
       <c r="P45" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="Q45" s="9" t="n">
+      <c r="Q45" s="8" t="n">
         <v>157.5</v>
       </c>
-      <c r="R45" s="9" t="n">
+      <c r="R45" s="8" t="n">
         <v>129.7</v>
       </c>
       <c r="S45" s="3" t="n">
         <v>137.5</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>14</v>
+        <v>414</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>71.5</v>
       </c>
-      <c r="V45" s="9" t="n">
+      <c r="V45" s="8" t="n">
         <v>145.5</v>
       </c>
-      <c r="W45" s="8" t="n">
+      <c r="W45" s="11" t="n">
         <v>131.6</v>
       </c>
       <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>5.8</v>
@@ -4322,15 +4322,15 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>11.7</v>
+        <v>311.7</v>
       </c>
       <c r="D46" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="E46" s="8" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F46" s="9" t="n">
+      <c r="E46" s="11" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F46" s="8" t="n">
         <v>24</v>
       </c>
       <c r="G46" s="3" t="n">
@@ -4346,12 +4346,12 @@
         <v>2.8</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="M46" s="9" t="n">
+      <c r="M46" s="11" t="n">
         <v>18.2</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4363,11 +4363,11 @@
       <c r="P46" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q46" s="9" t="n">
+      <c r="Q46" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="R46" s="9" t="n">
-        <v>21.6</v>
+      <c r="R46" s="11" t="n">
+        <v>221.6</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>22.9</v>
@@ -4378,10 +4378,10 @@
       <c r="U46" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="V46" s="9" t="n">
+      <c r="V46" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="W46" s="9" t="n">
+      <c r="W46" s="8" t="n">
         <v>21.8</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -796,7 +796,7 @@
         <v>4.2</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L4" s="8" t="n">
         <v>17.6</v>
@@ -1211,7 +1211,7 @@
         <v>15.5</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>44.2</v>
+        <v>442.5</v>
       </c>
       <c r="L9" s="8" t="n">
         <v>94.3</v>
@@ -1223,7 +1223,7 @@
         <v>96.3</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>22.2</v>
+        <v>440.9</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>12.9</v>
@@ -1296,7 +1296,7 @@
         <v>3.1</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="11" t="n">
         <v>18.2</v>
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1992.6</v>
+        <v>19.9</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>149.9</v>
@@ -1889,7 +1889,7 @@
         <v>3.2</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>20.2</v>
@@ -1958,7 +1958,7 @@
       <c r="E18" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="F18" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="G18" s="3" t="n">
@@ -1973,7 +1973,7 @@
       <c r="J18" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="8" t="n">
@@ -2043,7 +2043,7 @@
       <c r="E19" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="G19" s="3" t="n">
@@ -2058,7 +2058,7 @@
       <c r="J19" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="L19" s="8" t="n">
@@ -2128,7 +2128,7 @@
       <c r="E20" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="G20" s="3" t="n">
@@ -2138,12 +2138,12 @@
         <v>18.2</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K20" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K20" s="8" t="n">
         <v>24</v>
       </c>
       <c r="L20" s="8" t="n">
@@ -2165,7 +2165,7 @@
         <v>25.5</v>
       </c>
       <c r="R20" s="8" t="n">
-        <v>22.15</v>
+        <v>21.5</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>23.1</v>
@@ -2213,7 +2213,7 @@
       <c r="E21" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="G21" s="3" t="n">
@@ -2228,8 +2228,8 @@
       <c r="J21" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K21" s="3" t="n">
-        <v>0.6</v>
+      <c r="K21" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="L21" s="8" t="n">
         <v>18.8</v>
@@ -2298,8 +2298,8 @@
       <c r="E22" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="F22" s="8" t="n">
-        <v>24.5</v>
+      <c r="F22" s="3" t="n">
+        <v>27.5</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>14.6</v>
@@ -2313,7 +2313,7 @@
       <c r="J22" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="8" t="n">
         <v>3.7</v>
       </c>
       <c r="L22" s="8" t="n">
@@ -2383,7 +2383,7 @@
       <c r="E23" s="8" t="n">
         <v>92.8</v>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="F23" s="11" t="n">
         <v>123</v>
       </c>
       <c r="G23" s="3" t="n">
@@ -2398,7 +2398,7 @@
       <c r="J23" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="K23" s="11" t="n">
+      <c r="K23" s="8" t="n">
         <v>49.2</v>
       </c>
       <c r="L23" s="8" t="n">
@@ -2419,7 +2419,7 @@
       <c r="Q23" s="8" t="n">
         <v>146.2</v>
       </c>
-      <c r="R23" s="11" t="n">
+      <c r="R23" s="8" t="n">
         <v>114.3</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2468,14 +2468,14 @@
       <c r="E24" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F24" s="11" t="n">
         <v>24.6</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>12</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
@@ -2568,10 +2568,10 @@
       <c r="J25" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K25" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L25" s="3" t="n">
+      <c r="K25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="8" t="n">
         <v>19.5</v>
       </c>
       <c r="M25" s="8" t="n">
@@ -2614,7 +2614,7 @@
         <v>74.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2653,10 +2653,10 @@
       <c r="J26" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="L26" s="8" t="n">
         <v>19</v>
       </c>
       <c r="M26" s="8" t="n">
@@ -2738,10 +2738,10 @@
       <c r="J27" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="8" t="n">
         <v>5.3</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="L27" s="8" t="n">
         <v>20.2</v>
       </c>
       <c r="M27" s="8" t="n">
@@ -2823,10 +2823,10 @@
       <c r="J28" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="L28" s="8" t="n">
         <v>20.6</v>
       </c>
       <c r="M28" s="8" t="n">
@@ -2908,10 +2908,10 @@
       <c r="J29" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="L29" s="3" t="n">
+      <c r="L29" s="8" t="n">
         <v>20.3</v>
       </c>
       <c r="M29" s="8" t="n">
@@ -2970,7 +2970,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1856.4</v>
+        <v>185.6</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>150.3</v>
@@ -2985,7 +2985,7 @@
         <v>52.5</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>91.3</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>10</v>
@@ -2993,11 +2993,11 @@
       <c r="J30" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="K30" s="11" t="n">
+      <c r="K30" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="L30" s="11" t="n">
-        <v>29.6</v>
+      <c r="L30" s="8" t="n">
+        <v>99.59999999999999</v>
       </c>
       <c r="M30" s="8" t="n">
         <v>93.2</v>
@@ -3024,7 +3024,7 @@
         <v>332.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>6.4</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="V30" s="8" t="n">
         <v>123.1</v>
@@ -3079,7 +3079,7 @@
         <v>3.2</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="11" t="n">
         <v>19.2</v>
@@ -3170,7 +3170,7 @@
         <v>20.6</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>21.5</v>
@@ -3206,7 +3206,7 @@
         <v>26.4</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>6.9</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>11.8</v>
@@ -3428,7 +3428,7 @@
         <v>19.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>85.40000000000001</v>
@@ -3480,7 +3480,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>398.9</v>
+        <v>39.8</v>
       </c>
       <c r="D36" s="8" t="n">
         <v>28.6</v>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1683.5</v>
+        <v>168.5</v>
       </c>
       <c r="D37" s="8" t="n">
         <v>150.1</v>
@@ -3594,7 +3594,7 @@
       <c r="L37" s="8" t="n">
         <v>103.5</v>
       </c>
-      <c r="M37" s="8" t="n">
+      <c r="M37" s="11" t="n">
         <v>96.5</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3606,8 +3606,8 @@
       <c r="P37" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="Q37" s="8" t="n">
-        <v>139.6</v>
+      <c r="Q37" s="11" t="n">
+        <v>189.6</v>
       </c>
       <c r="R37" s="8" t="n">
         <v>115.4</v>
@@ -3668,13 +3668,13 @@
         <v>18.5</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>22.5</v>
+        <v>2.5</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>3.1</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L38" s="8" t="n">
         <v>20.7</v>
@@ -3691,8 +3691,8 @@
       <c r="P38" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q38" s="11" t="n">
-        <v>27.2</v>
+      <c r="Q38" s="8" t="n">
+        <v>27.9</v>
       </c>
       <c r="R38" s="8" t="n">
         <v>23.1</v>
@@ -3737,7 +3737,7 @@
       <c r="C39" s="3" t="n">
         <v>400.8</v>
       </c>
-      <c r="D39" s="8" t="n">
+      <c r="D39" s="3" t="n">
         <v>31.8</v>
       </c>
       <c r="E39" s="8" t="n">
@@ -3764,7 +3764,7 @@
       <c r="L39" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="M39" s="3" t="n">
+      <c r="M39" s="8" t="n">
         <v>19.5</v>
       </c>
       <c r="N39" s="3" t="n">
@@ -3822,14 +3822,14 @@
       <c r="C40" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="D40" s="8" t="n">
+      <c r="D40" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="E40" s="8" t="n">
         <v>20.2</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>22.21</v>
+        <v>22.1</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>3.9</v>
@@ -3849,11 +3849,11 @@
       <c r="L40" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="M40" s="3" t="n">
+      <c r="M40" s="8" t="n">
         <v>19.1</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>24.2</v>
+        <v>22.2</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>88</v>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>448.2</v>
-      </c>
-      <c r="D41" s="8" t="n">
-        <v>29.4</v>
+        <v>448.8</v>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>2.9</v>
       </c>
       <c r="E41" s="8" t="n">
         <v>19.5</v>
@@ -3934,7 +3934,7 @@
       <c r="L41" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="N41" s="3" t="n">
@@ -3956,7 +3956,7 @@
         <v>21.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>57.4</v>
+        <v>58.4</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>16.1</v>
@@ -3990,9 +3990,9 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>464.2</v>
-      </c>
-      <c r="D42" s="8" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="D42" s="3" t="n">
         <v>32.8</v>
       </c>
       <c r="E42" s="8" t="n">
@@ -4019,7 +4019,7 @@
       <c r="L42" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="M42" s="3" t="n">
+      <c r="M42" s="8" t="n">
         <v>16.1</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -4077,7 +4077,7 @@
       <c r="C43" s="3" t="n">
         <v>341.3</v>
       </c>
-      <c r="D43" s="8" t="n">
+      <c r="D43" s="3" t="n">
         <v>32</v>
       </c>
       <c r="E43" s="8" t="n">
@@ -4104,7 +4104,7 @@
       <c r="L43" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="M43" s="3" t="n">
+      <c r="M43" s="8" t="n">
         <v>17.7</v>
       </c>
       <c r="N43" s="3" t="n">
@@ -4162,7 +4162,7 @@
       <c r="C44" s="3" t="n">
         <v>141.6</v>
       </c>
-      <c r="D44" s="8" t="n">
+      <c r="D44" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="E44" s="8" t="n">
@@ -4189,8 +4189,8 @@
       <c r="L44" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="M44" s="3" t="n">
-        <v>28.2</v>
+      <c r="M44" s="8" t="n">
+        <v>18.2</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>20.1</v>
@@ -4241,7 +4241,7 @@
       <c r="C45" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="D45" s="8" t="n">
+      <c r="D45" s="11" t="n">
         <v>174</v>
       </c>
       <c r="E45" s="8" t="n">
@@ -4268,8 +4268,8 @@
       <c r="L45" s="8" t="n">
         <v>116.4</v>
       </c>
-      <c r="M45" s="11" t="n">
-        <v>109.2</v>
+      <c r="M45" s="8" t="n">
+        <v>109.3</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>121.1</v>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>5.8</v>
@@ -4324,11 +4324,11 @@
       <c r="C46" s="3" t="n">
         <v>311.7</v>
       </c>
-      <c r="D46" s="8" t="n">
+      <c r="D46" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="E46" s="11" t="n">
-        <v>18.2</v>
+      <c r="E46" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="F46" s="8" t="n">
         <v>24</v>
@@ -4346,12 +4346,12 @@
         <v>2.8</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L46" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="M46" s="11" t="n">
+      <c r="M46" s="8" t="n">
         <v>18.2</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4366,8 +4366,8 @@
       <c r="Q46" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="R46" s="11" t="n">
-        <v>221.6</v>
+      <c r="R46" s="8" t="n">
+        <v>21.6</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>22.9</v>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -150,6 +156,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -786,7 +795,7 @@
       <c r="J4" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="K4" s="3" t="n"/>
+      <c r="K4" s="10" t="n"/>
       <c r="L4" s="3" t="n">
         <v>17.6</v>
       </c>
@@ -869,7 +878,7 @@
       <c r="J5" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="10" t="n">
         <v>25.8</v>
       </c>
       <c r="L5" s="3" t="n">
@@ -952,7 +961,7 @@
         <v>2.5</v>
       </c>
       <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
@@ -1037,7 +1046,7 @@
       <c r="J7" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
@@ -1122,7 +1131,7 @@
       <c r="J8" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="10" t="n">
         <v>18.5</v>
       </c>
       <c r="L8" s="3" t="n">
@@ -1207,7 +1216,7 @@
       <c r="J9" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="10" t="n">
         <v>44.3</v>
       </c>
       <c r="L9" s="3" t="n">
@@ -1375,7 +1384,7 @@
       <c r="J11" s="3" t="n">
         <v>31.3</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
@@ -1458,7 +1467,7 @@
       <c r="J12" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
@@ -1543,7 +1552,7 @@
       <c r="J13" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="10" t="n">
         <v>0.3</v>
       </c>
       <c r="L13" s="3" t="n">
@@ -1628,7 +1637,7 @@
       <c r="J14" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="10" t="n">
         <v>5.7</v>
       </c>
       <c r="L14" s="3" t="n">
@@ -1713,7 +1722,7 @@
       <c r="J15" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
@@ -1798,7 +1807,7 @@
       <c r="J16" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="10" t="n">
         <v>6</v>
       </c>
       <c r="L16" s="3" t="n">
@@ -2385,7 +2394,7 @@
       <c r="J23" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="9" t="n">
         <v>3.7</v>
       </c>
       <c r="L23" s="3" t="n">
@@ -2980,7 +2989,7 @@
       <c r="J30" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="9" t="n">
         <v>0.2</v>
       </c>
       <c r="L30" s="3" t="n">
@@ -3150,7 +3159,7 @@
       <c r="J32" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="K32" s="3" t="n"/>
+      <c r="K32" s="12" t="n"/>
       <c r="L32" s="3" t="n">
         <v>19.9</v>
       </c>
@@ -3573,7 +3582,7 @@
       <c r="J37" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="9" t="n">
         <v>9</v>
       </c>
       <c r="L37" s="3" t="n">
@@ -4253,7 +4262,7 @@
       <c r="J45" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="L45" s="3" t="n">
